--- a/ETS2023_Test1_Final_Architecture.xlsx
+++ b/ETS2023_Test1_Final_Architecture.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28035" windowHeight="11730"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28035" windowHeight="11730" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Test_Info" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1637" uniqueCount="1331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1643" uniqueCount="1337">
   <si>
     <t>test_id</t>
   </si>
@@ -1249,9 +1249,6 @@
     <t>P3_11</t>
   </si>
   <si>
-    <t>https://link-image.com/p3_q63.jpg</t>
-  </si>
-  <si>
     <t>M-Au Welcome to The Boat Center. How may I help you?&lt;br&gt;W-Am Hi. Do you have any tickets for the Sea-Ride Special tour today? I was hoping to catch a last-minute tour.&lt;br&gt;M-Au Sorry. We're sold out. It's a really popular tour this time of year because the penguins are migrating through the area.&lt;br&gt;W-Am Oh, too bad. I'm leaving tomorrow morning, and I was really hoping to take one of your tours.&lt;br&gt;M-Au Well, the Island Exploration tour still has a couple of spots left.&lt;br&gt;W-Am Great! And that'll give me time to get something to eat before it starts. I see there's a coffee shop just down the street.</t>
   </si>
   <si>
@@ -1309,9 +1306,6 @@
     <t>P3_12</t>
   </si>
   <si>
-    <t>https://link-image.com/p3_q66.jpg</t>
-  </si>
-  <si>
     <t>M-Cn Hi. I'm here for the health and wellness conference. I parked in the event center parking area. I was wondering, is parking free for conference attendees?&lt;br&gt;W-Br No, I'm sorry. We don't provide any reimbursements for parking. But if you're willing to move your car, there's a cheaper parking area at Seventh Avenue and Vine Street. It's about a block away.&lt;br&gt;M-Cn Oh, unfortunately, I don't have time. I'm scheduled to attend the strength-training seminar that starts in fifteen minutes. But tomorrow I'll get here earlier and park at the other lot. Seventh and Vine, you said. Right?&lt;br&gt;W-Br That's correct.</t>
   </si>
   <si>
@@ -1372,9 +1366,6 @@
     <t>P3_13</t>
   </si>
   <si>
-    <t>https://link-image.com/p3_q69.jpg</t>
-  </si>
-  <si>
     <t>M-Cn Molina's Office Store. How can I help?&lt;br&gt;W-Am Hi. I've been trying to order a product on your Web site, but every time I get to the checkout screen, everything freezes, and I can't place the order.&lt;br&gt;M-Cn What are you trying to buy?&lt;br&gt;W-Am The Enzo 5000 scanner.&lt;br&gt;M-Cn Hmm. That product's currently out of stock. Can I recommend the Rhenium 60 instead? It's a popular model.&lt;br&gt;W-Am I really need the Enzo 5000-I'm an artist and I make my own prints, so I need a model that produces top-quality images.&lt;br&gt;M-Cn I see. Well, we're expecting a shipment tomorrow. If it includes the model you're looking for, I can reserve it for you.</t>
   </si>
   <si>
@@ -1915,9 +1906,6 @@
     <t>P4_09</t>
   </si>
   <si>
-    <t>https://link-image.com/p4_q96.jpg</t>
-  </si>
-  <si>
     <t>M-Cn Hi. This is Vinod Singh. I was in your store on Monday looking at refrigerators for my apartment. One of your employees showed me what you have in stock. I've decided to go with the extra-large refrigerator-the one with the stainless-steel finish, because it'll match the other appliances in my apartment. Oh, also, is there an additional charge for delivering outside of the downtown area? Please call me at 555-0130 so we can finalize the details.</t>
   </si>
   <si>
@@ -1978,9 +1966,6 @@
     <t>P4_10</t>
   </si>
   <si>
-    <t>https://link-image.com/p4_q99.jpg</t>
-  </si>
-  <si>
     <t>W-Am Good afternoon, everyone. I'd like to go over the product tests for our laptop-computer backpack, because they will require some design changes. As you know, we hired a marketing firm to test the prototype you designed among consumers. Now, we received very positive feedback overall. Consumers liked the separate computer compartment. However, many people felt that the shoulder straps were uncomfortable when the bag was full. It's important that the backpack have comfortable shoulder straps, since its purpose is to carry heavy equipment. We need to revise the design as quickly as possible, since we're scheduled to have our official product release early next year.</t>
   </si>
   <si>
@@ -2668,9 +2653,6 @@
     <t>P6_01</t>
   </si>
   <si>
-    <t>Local Barbershop Wins State Competition&lt;br&gt;By Miranda Warren&lt;br&gt;&lt;br&gt;MALENDA COUNTY (January 12)-Pat and Kenny's Barbershop, at 3949 Grand Street, has been named the best barbershop in the state by the Barber and Hairdresser's Coalition. The criteria for selection include reputation, affordability, professionalism, and accreditations. _______(132).&lt;br&gt;&lt;br&gt;Founders and owners Kenneth Webber and Patrick Miller have been best friends since childhood. _______(133) opened the shop 34 years ago. _______(134) the shop retains its old-fashioned charm, the barbers have mastered the latest styles, not just the more traditional ones. People of all ages seeking a haircut or a new style should try Pat and Kenny's Barbershop.</t>
-  </si>
-  <si>
     <t>MALENDA COUNTY (January 12)-Pat and Kenny's Barbershop, at 3949 Grand Street, has been named the best barbershop in the state by the Barber and Hairdresser's Coalition. The criteria for selection include reputation, affordability, professionalism, and accreditations.</t>
   </si>
   <si>
@@ -4013,6 +3995,42 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/bangvang1105-tech/Audio/main/ETS2023_Test1_Full.mp3</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/main/p1_01.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p1_02.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p1_03.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p1_04.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p1_05.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p1_06.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p3_63.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p3_66.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p3_69.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p4_96.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p4_99.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p6_131.png</t>
   </si>
 </sst>
 </file>
@@ -4108,7 +4126,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4130,6 +4148,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4468,7 +4492,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>1330</v>
+        <v>1324</v>
       </c>
       <c r="D2" s="2">
         <v>120</v>
@@ -4541,7 +4565,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -4552,7 +4576,9 @@
         <v>20</v>
       </c>
       <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
+      <c r="E2" s="8" t="s">
+        <v>1325</v>
+      </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2" s="5" t="s">
@@ -4574,7 +4600,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -4585,7 +4611,9 @@
         <v>27</v>
       </c>
       <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
+      <c r="E3" s="9" t="s">
+        <v>1326</v>
+      </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6" t="s">
@@ -4607,7 +4635,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -4618,7 +4646,9 @@
         <v>34</v>
       </c>
       <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
+      <c r="E4" s="8" t="s">
+        <v>1327</v>
+      </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
@@ -4640,7 +4670,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -4651,7 +4681,9 @@
         <v>41</v>
       </c>
       <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
+      <c r="E5" s="9" t="s">
+        <v>1328</v>
+      </c>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6" t="s">
@@ -4673,7 +4705,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -4684,7 +4716,9 @@
         <v>47</v>
       </c>
       <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
+      <c r="E6" s="8" t="s">
+        <v>1329</v>
+      </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
@@ -4706,7 +4740,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -4717,7 +4751,9 @@
         <v>54</v>
       </c>
       <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
+      <c r="E7" s="9" t="s">
+        <v>1330</v>
+      </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
       <c r="H7" s="6" t="s">
@@ -6645,35 +6681,33 @@
         <v>408</v>
       </c>
       <c r="D63" s="6"/>
-      <c r="E63" s="6" t="s">
+      <c r="E63" s="9"/>
+      <c r="F63" s="6" t="s">
         <v>409</v>
       </c>
-      <c r="F63" s="6" t="s">
+      <c r="G63" s="6" t="s">
         <v>410</v>
       </c>
-      <c r="G63" s="6" t="s">
+      <c r="H63" s="6" t="s">
         <v>411</v>
       </c>
-      <c r="H63" s="6" t="s">
+      <c r="I63" s="6" t="s">
         <v>412</v>
       </c>
-      <c r="I63" s="6" t="s">
+      <c r="J63" s="6" t="s">
         <v>413</v>
       </c>
-      <c r="J63" s="6" t="s">
+      <c r="K63" s="6" t="s">
         <v>414</v>
-      </c>
-      <c r="K63" s="6" t="s">
-        <v>415</v>
       </c>
       <c r="L63" s="2" t="s">
         <v>52</v>
       </c>
       <c r="M63" s="6" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
         <v>63</v>
       </c>
@@ -6684,28 +6718,30 @@
         <v>408</v>
       </c>
       <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
+      <c r="E64" s="8" t="s">
+        <v>1331</v>
+      </c>
       <c r="F64" s="5"/>
       <c r="G64" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="H64" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="H64" s="5" t="s">
+      <c r="I64" s="5" t="s">
         <v>418</v>
       </c>
-      <c r="I64" s="5" t="s">
+      <c r="J64" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="J64" s="5" t="s">
+      <c r="K64" s="5" t="s">
         <v>420</v>
-      </c>
-      <c r="K64" s="5" t="s">
-        <v>421</v>
       </c>
       <c r="L64" s="4" t="s">
         <v>25</v>
       </c>
       <c r="M64" s="5" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -6725,22 +6761,22 @@
         <v>244</v>
       </c>
       <c r="H65" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="I65" s="6" t="s">
         <v>423</v>
       </c>
-      <c r="I65" s="6" t="s">
+      <c r="J65" s="6" t="s">
         <v>424</v>
       </c>
-      <c r="J65" s="6" t="s">
+      <c r="K65" s="6" t="s">
         <v>425</v>
-      </c>
-      <c r="K65" s="6" t="s">
-        <v>426</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>39</v>
       </c>
       <c r="M65" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -6751,38 +6787,36 @@
         <v>3</v>
       </c>
       <c r="C66" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="D66" s="5"/>
+      <c r="E66" s="5"/>
+      <c r="F66" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="D66" s="5"/>
-      <c r="E66" s="5" t="s">
+      <c r="G66" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="F66" s="5" t="s">
+      <c r="H66" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="G66" s="5" t="s">
+      <c r="I66" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="H66" s="5" t="s">
+      <c r="J66" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="I66" s="5" t="s">
+      <c r="K66" s="5" t="s">
         <v>433</v>
-      </c>
-      <c r="J66" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="K66" s="5" t="s">
-        <v>435</v>
       </c>
       <c r="L66" s="4" t="s">
         <v>25</v>
       </c>
       <c r="M66" s="5" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -6790,31 +6824,33 @@
         <v>3</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D67" s="6"/>
-      <c r="E67" s="6"/>
+      <c r="E67" s="9" t="s">
+        <v>1332</v>
+      </c>
       <c r="F67" s="6"/>
       <c r="G67" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="I67" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="H67" s="6" t="s">
+      <c r="J67" s="6" t="s">
         <v>438</v>
       </c>
-      <c r="I67" s="6" t="s">
+      <c r="K67" s="6" t="s">
         <v>439</v>
-      </c>
-      <c r="J67" s="6" t="s">
-        <v>440</v>
-      </c>
-      <c r="K67" s="6" t="s">
-        <v>441</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -6825,31 +6861,31 @@
         <v>3</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="5"/>
       <c r="F68" s="5"/>
       <c r="G68" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="H68" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="I68" s="5" t="s">
         <v>443</v>
       </c>
-      <c r="H68" s="5" t="s">
+      <c r="J68" s="5" t="s">
         <v>444</v>
       </c>
-      <c r="I68" s="5" t="s">
+      <c r="K68" s="5" t="s">
         <v>445</v>
-      </c>
-      <c r="J68" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="K68" s="5" t="s">
-        <v>447</v>
       </c>
       <c r="L68" s="4" t="s">
         <v>52</v>
       </c>
       <c r="M68" s="5" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -6860,38 +6896,36 @@
         <v>3</v>
       </c>
       <c r="C69" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="G69" s="6" t="s">
         <v>449</v>
       </c>
-      <c r="D69" s="6"/>
-      <c r="E69" s="6" t="s">
+      <c r="H69" s="6" t="s">
         <v>450</v>
       </c>
-      <c r="F69" s="6" t="s">
+      <c r="I69" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="G69" s="6" t="s">
+      <c r="J69" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="H69" s="6" t="s">
+      <c r="K69" s="6" t="s">
         <v>453</v>
-      </c>
-      <c r="I69" s="6" t="s">
-        <v>454</v>
-      </c>
-      <c r="J69" s="6" t="s">
-        <v>455</v>
-      </c>
-      <c r="K69" s="6" t="s">
-        <v>456</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>39</v>
       </c>
       <c r="M69" s="6" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
         <v>69</v>
       </c>
@@ -6899,31 +6933,33 @@
         <v>3</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D70" s="5"/>
-      <c r="E70" s="5"/>
+      <c r="E70" s="8" t="s">
+        <v>1333</v>
+      </c>
       <c r="F70" s="5"/>
       <c r="G70" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="H70" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="I70" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="J70" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="H70" s="5" t="s">
+      <c r="K70" s="5" t="s">
         <v>459</v>
-      </c>
-      <c r="I70" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="J70" s="5" t="s">
-        <v>461</v>
-      </c>
-      <c r="K70" s="5" t="s">
-        <v>462</v>
       </c>
       <c r="L70" s="4" t="s">
         <v>25</v>
       </c>
       <c r="M70" s="5" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -6934,31 +6970,31 @@
         <v>3</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D71" s="6"/>
       <c r="E71" s="6"/>
       <c r="F71" s="6"/>
       <c r="G71" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="H71" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="I71" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="J71" s="6" t="s">
         <v>464</v>
       </c>
-      <c r="H71" s="6" t="s">
+      <c r="K71" s="6" t="s">
         <v>465</v>
-      </c>
-      <c r="I71" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="J71" s="6" t="s">
-        <v>467</v>
-      </c>
-      <c r="K71" s="6" t="s">
-        <v>468</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M71" s="6" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -6969,33 +7005,33 @@
         <v>4</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="D72" s="5"/>
       <c r="E72" s="5"/>
       <c r="F72" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="H72" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="I72" s="5" t="s">
         <v>471</v>
       </c>
-      <c r="G72" s="5" t="s">
+      <c r="J72" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="H72" s="5" t="s">
+      <c r="K72" s="5" t="s">
         <v>473</v>
-      </c>
-      <c r="I72" s="5" t="s">
-        <v>474</v>
-      </c>
-      <c r="J72" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="K72" s="5" t="s">
-        <v>476</v>
       </c>
       <c r="L72" s="4" t="s">
         <v>32</v>
       </c>
       <c r="M72" s="5" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -7006,31 +7042,31 @@
         <v>4</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="D73" s="6"/>
       <c r="E73" s="6"/>
       <c r="F73" s="6"/>
       <c r="G73" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="H73" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="I73" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="J73" s="6" t="s">
         <v>478</v>
       </c>
-      <c r="H73" s="6" t="s">
+      <c r="K73" s="6" t="s">
         <v>479</v>
-      </c>
-      <c r="I73" s="6" t="s">
-        <v>480</v>
-      </c>
-      <c r="J73" s="6" t="s">
-        <v>481</v>
-      </c>
-      <c r="K73" s="6" t="s">
-        <v>482</v>
       </c>
       <c r="L73" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M73" s="6" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -7041,31 +7077,31 @@
         <v>4</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="5"/>
       <c r="F74" s="5"/>
       <c r="G74" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="H74" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="I74" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="J74" s="5" t="s">
         <v>484</v>
       </c>
-      <c r="H74" s="5" t="s">
+      <c r="K74" s="5" t="s">
         <v>485</v>
-      </c>
-      <c r="I74" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="J74" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="K74" s="5" t="s">
-        <v>488</v>
       </c>
       <c r="L74" s="4" t="s">
         <v>39</v>
       </c>
       <c r="M74" s="5" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="75" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -7076,33 +7112,33 @@
         <v>4</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="D75" s="6"/>
       <c r="E75" s="6"/>
       <c r="F75" s="6" t="s">
+        <v>488</v>
+      </c>
+      <c r="G75" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="H75" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="I75" s="6" t="s">
         <v>491</v>
       </c>
-      <c r="G75" s="6" t="s">
+      <c r="J75" s="6" t="s">
         <v>492</v>
       </c>
-      <c r="H75" s="6" t="s">
+      <c r="K75" s="6" t="s">
         <v>493</v>
-      </c>
-      <c r="I75" s="6" t="s">
-        <v>494</v>
-      </c>
-      <c r="J75" s="6" t="s">
-        <v>495</v>
-      </c>
-      <c r="K75" s="6" t="s">
-        <v>496</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -7113,31 +7149,31 @@
         <v>4</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="D76" s="5"/>
       <c r="E76" s="5"/>
       <c r="F76" s="5"/>
       <c r="G76" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="H76" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="I76" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="J76" s="5" t="s">
         <v>498</v>
       </c>
-      <c r="H76" s="5" t="s">
+      <c r="K76" s="5" t="s">
         <v>499</v>
-      </c>
-      <c r="I76" s="5" t="s">
-        <v>500</v>
-      </c>
-      <c r="J76" s="5" t="s">
-        <v>501</v>
-      </c>
-      <c r="K76" s="5" t="s">
-        <v>502</v>
       </c>
       <c r="L76" s="4" t="s">
         <v>25</v>
       </c>
       <c r="M76" s="5" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="77" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -7148,31 +7184,31 @@
         <v>4</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="D77" s="6"/>
       <c r="E77" s="6"/>
       <c r="F77" s="6"/>
       <c r="G77" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="H77" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="I77" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="J77" s="6" t="s">
         <v>504</v>
       </c>
-      <c r="H77" s="6" t="s">
+      <c r="K77" s="6" t="s">
         <v>505</v>
-      </c>
-      <c r="I77" s="6" t="s">
-        <v>506</v>
-      </c>
-      <c r="J77" s="6" t="s">
-        <v>507</v>
-      </c>
-      <c r="K77" s="6" t="s">
-        <v>508</v>
       </c>
       <c r="L77" s="2" t="s">
         <v>39</v>
       </c>
       <c r="M77" s="6" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="78" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -7183,33 +7219,33 @@
         <v>4</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D78" s="5"/>
       <c r="E78" s="5"/>
       <c r="F78" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="H78" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="I78" s="5" t="s">
         <v>511</v>
       </c>
-      <c r="G78" s="5" t="s">
+      <c r="J78" s="5" t="s">
         <v>512</v>
       </c>
-      <c r="H78" s="5" t="s">
+      <c r="K78" s="5" t="s">
         <v>513</v>
-      </c>
-      <c r="I78" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="J78" s="5" t="s">
-        <v>515</v>
-      </c>
-      <c r="K78" s="5" t="s">
-        <v>516</v>
       </c>
       <c r="L78" s="4" t="s">
         <v>32</v>
       </c>
       <c r="M78" s="5" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="79" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -7220,31 +7256,31 @@
         <v>4</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D79" s="6"/>
       <c r="E79" s="6"/>
       <c r="F79" s="6"/>
       <c r="G79" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="I79" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="J79" s="6" t="s">
         <v>518</v>
       </c>
-      <c r="H79" s="6" t="s">
+      <c r="K79" s="6" t="s">
         <v>519</v>
-      </c>
-      <c r="I79" s="6" t="s">
-        <v>520</v>
-      </c>
-      <c r="J79" s="6" t="s">
-        <v>521</v>
-      </c>
-      <c r="K79" s="6" t="s">
-        <v>522</v>
       </c>
       <c r="L79" s="2" t="s">
         <v>52</v>
       </c>
       <c r="M79" s="6" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="80" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -7255,31 +7291,31 @@
         <v>4</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D80" s="5"/>
       <c r="E80" s="5"/>
       <c r="F80" s="5"/>
       <c r="G80" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="H80" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="I80" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="J80" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="H80" s="5" t="s">
+      <c r="K80" s="5" t="s">
         <v>525</v>
-      </c>
-      <c r="I80" s="5" t="s">
-        <v>526</v>
-      </c>
-      <c r="J80" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="K80" s="5" t="s">
-        <v>528</v>
       </c>
       <c r="L80" s="4" t="s">
         <v>39</v>
       </c>
       <c r="M80" s="5" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="81" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -7290,33 +7326,33 @@
         <v>4</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D81" s="6"/>
       <c r="E81" s="6"/>
       <c r="F81" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="G81" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="H81" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="I81" s="6" t="s">
         <v>531</v>
       </c>
-      <c r="G81" s="6" t="s">
+      <c r="J81" s="6" t="s">
         <v>532</v>
       </c>
-      <c r="H81" s="6" t="s">
+      <c r="K81" s="6" t="s">
         <v>533</v>
-      </c>
-      <c r="I81" s="6" t="s">
-        <v>534</v>
-      </c>
-      <c r="J81" s="6" t="s">
-        <v>535</v>
-      </c>
-      <c r="K81" s="6" t="s">
-        <v>536</v>
       </c>
       <c r="L81" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M81" s="6" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="82" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -7327,31 +7363,31 @@
         <v>4</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D82" s="5"/>
       <c r="E82" s="5"/>
       <c r="F82" s="5"/>
       <c r="G82" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="H82" s="5" t="s">
+        <v>536</v>
+      </c>
+      <c r="I82" s="5" t="s">
+        <v>537</v>
+      </c>
+      <c r="J82" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="H82" s="5" t="s">
+      <c r="K82" s="5" t="s">
         <v>539</v>
-      </c>
-      <c r="I82" s="5" t="s">
-        <v>540</v>
-      </c>
-      <c r="J82" s="5" t="s">
-        <v>541</v>
-      </c>
-      <c r="K82" s="5" t="s">
-        <v>542</v>
       </c>
       <c r="L82" s="4" t="s">
         <v>32</v>
       </c>
       <c r="M82" s="5" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -7362,31 +7398,31 @@
         <v>4</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D83" s="6"/>
       <c r="E83" s="6"/>
       <c r="F83" s="6"/>
       <c r="G83" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>542</v>
+      </c>
+      <c r="I83" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="J83" s="6" t="s">
         <v>544</v>
       </c>
-      <c r="H83" s="6" t="s">
+      <c r="K83" s="6" t="s">
         <v>545</v>
-      </c>
-      <c r="I83" s="6" t="s">
-        <v>546</v>
-      </c>
-      <c r="J83" s="6" t="s">
-        <v>547</v>
-      </c>
-      <c r="K83" s="6" t="s">
-        <v>548</v>
       </c>
       <c r="L83" s="2" t="s">
         <v>52</v>
       </c>
       <c r="M83" s="6" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="84" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -7397,33 +7433,33 @@
         <v>4</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D84" s="5"/>
       <c r="E84" s="5"/>
       <c r="F84" s="5" t="s">
+        <v>548</v>
+      </c>
+      <c r="G84" s="5" t="s">
+        <v>549</v>
+      </c>
+      <c r="H84" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="I84" s="5" t="s">
         <v>551</v>
       </c>
-      <c r="G84" s="5" t="s">
+      <c r="J84" s="5" t="s">
         <v>552</v>
       </c>
-      <c r="H84" s="5" t="s">
+      <c r="K84" s="5" t="s">
         <v>553</v>
-      </c>
-      <c r="I84" s="5" t="s">
-        <v>554</v>
-      </c>
-      <c r="J84" s="5" t="s">
-        <v>555</v>
-      </c>
-      <c r="K84" s="5" t="s">
-        <v>556</v>
       </c>
       <c r="L84" s="4" t="s">
         <v>25</v>
       </c>
       <c r="M84" s="5" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -7434,31 +7470,31 @@
         <v>4</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D85" s="6"/>
       <c r="E85" s="6"/>
       <c r="F85" s="6"/>
       <c r="G85" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>556</v>
+      </c>
+      <c r="I85" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="J85" s="6" t="s">
         <v>558</v>
       </c>
-      <c r="H85" s="6" t="s">
+      <c r="K85" s="6" t="s">
         <v>559</v>
-      </c>
-      <c r="I85" s="6" t="s">
-        <v>560</v>
-      </c>
-      <c r="J85" s="6" t="s">
-        <v>561</v>
-      </c>
-      <c r="K85" s="6" t="s">
-        <v>562</v>
       </c>
       <c r="L85" s="2" t="s">
         <v>52</v>
       </c>
       <c r="M85" s="6" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -7469,31 +7505,31 @@
         <v>4</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D86" s="5"/>
       <c r="E86" s="5"/>
       <c r="F86" s="5"/>
       <c r="G86" s="5" t="s">
+        <v>561</v>
+      </c>
+      <c r="H86" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="I86" s="5" t="s">
+        <v>563</v>
+      </c>
+      <c r="J86" s="5" t="s">
         <v>564</v>
       </c>
-      <c r="H86" s="5" t="s">
+      <c r="K86" s="5" t="s">
         <v>565</v>
-      </c>
-      <c r="I86" s="5" t="s">
-        <v>566</v>
-      </c>
-      <c r="J86" s="5" t="s">
-        <v>567</v>
-      </c>
-      <c r="K86" s="5" t="s">
-        <v>568</v>
       </c>
       <c r="L86" s="4" t="s">
         <v>52</v>
       </c>
       <c r="M86" s="5" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="87" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -7504,33 +7540,33 @@
         <v>4</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="D87" s="6"/>
       <c r="E87" s="6"/>
       <c r="F87" s="6" t="s">
+        <v>568</v>
+      </c>
+      <c r="G87" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>570</v>
+      </c>
+      <c r="I87" s="6" t="s">
         <v>571</v>
       </c>
-      <c r="G87" s="6" t="s">
+      <c r="J87" s="6" t="s">
         <v>572</v>
       </c>
-      <c r="H87" s="6" t="s">
+      <c r="K87" s="6" t="s">
         <v>573</v>
-      </c>
-      <c r="I87" s="6" t="s">
-        <v>574</v>
-      </c>
-      <c r="J87" s="6" t="s">
-        <v>575</v>
-      </c>
-      <c r="K87" s="6" t="s">
-        <v>576</v>
       </c>
       <c r="L87" s="2" t="s">
         <v>39</v>
       </c>
       <c r="M87" s="6" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -7541,31 +7577,31 @@
         <v>4</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="D88" s="5"/>
       <c r="E88" s="5"/>
       <c r="F88" s="5"/>
       <c r="G88" s="5" t="s">
+        <v>575</v>
+      </c>
+      <c r="H88" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="I88" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="J88" s="5" t="s">
         <v>578</v>
       </c>
-      <c r="H88" s="5" t="s">
+      <c r="K88" s="5" t="s">
         <v>579</v>
-      </c>
-      <c r="I88" s="5" t="s">
-        <v>580</v>
-      </c>
-      <c r="J88" s="5" t="s">
-        <v>581</v>
-      </c>
-      <c r="K88" s="5" t="s">
-        <v>582</v>
       </c>
       <c r="L88" s="4" t="s">
         <v>25</v>
       </c>
       <c r="M88" s="5" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="89" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -7576,31 +7612,31 @@
         <v>4</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="D89" s="6"/>
       <c r="E89" s="6"/>
       <c r="F89" s="6"/>
       <c r="G89" s="6" t="s">
+        <v>581</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>582</v>
+      </c>
+      <c r="I89" s="6" t="s">
+        <v>583</v>
+      </c>
+      <c r="J89" s="6" t="s">
         <v>584</v>
       </c>
-      <c r="H89" s="6" t="s">
+      <c r="K89" s="6" t="s">
         <v>585</v>
-      </c>
-      <c r="I89" s="6" t="s">
-        <v>586</v>
-      </c>
-      <c r="J89" s="6" t="s">
-        <v>587</v>
-      </c>
-      <c r="K89" s="6" t="s">
-        <v>588</v>
       </c>
       <c r="L89" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M89" s="6" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
     <row r="90" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -7611,33 +7647,33 @@
         <v>4</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="D90" s="5"/>
       <c r="E90" s="5"/>
       <c r="F90" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="G90" s="5" t="s">
+        <v>589</v>
+      </c>
+      <c r="H90" s="5" t="s">
+        <v>590</v>
+      </c>
+      <c r="I90" s="5" t="s">
         <v>591</v>
       </c>
-      <c r="G90" s="5" t="s">
+      <c r="J90" s="5" t="s">
         <v>592</v>
       </c>
-      <c r="H90" s="5" t="s">
+      <c r="K90" s="5" t="s">
         <v>593</v>
-      </c>
-      <c r="I90" s="5" t="s">
-        <v>594</v>
-      </c>
-      <c r="J90" s="5" t="s">
-        <v>595</v>
-      </c>
-      <c r="K90" s="5" t="s">
-        <v>596</v>
       </c>
       <c r="L90" s="4" t="s">
         <v>52</v>
       </c>
       <c r="M90" s="5" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
     </row>
     <row r="91" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -7648,31 +7684,31 @@
         <v>4</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="D91" s="6"/>
       <c r="E91" s="6"/>
       <c r="F91" s="6"/>
       <c r="G91" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="I91" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="J91" s="6" t="s">
         <v>598</v>
       </c>
-      <c r="H91" s="6" t="s">
+      <c r="K91" s="6" t="s">
         <v>599</v>
-      </c>
-      <c r="I91" s="6" t="s">
-        <v>600</v>
-      </c>
-      <c r="J91" s="6" t="s">
-        <v>601</v>
-      </c>
-      <c r="K91" s="6" t="s">
-        <v>602</v>
       </c>
       <c r="L91" s="2" t="s">
         <v>39</v>
       </c>
       <c r="M91" s="6" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="92" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -7683,31 +7719,31 @@
         <v>4</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="D92" s="5"/>
       <c r="E92" s="5"/>
       <c r="F92" s="5"/>
       <c r="G92" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="H92" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="I92" s="5" t="s">
+        <v>603</v>
+      </c>
+      <c r="J92" s="5" t="s">
         <v>604</v>
       </c>
-      <c r="H92" s="5" t="s">
+      <c r="K92" s="5" t="s">
         <v>605</v>
-      </c>
-      <c r="I92" s="5" t="s">
-        <v>606</v>
-      </c>
-      <c r="J92" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="K92" s="5" t="s">
-        <v>608</v>
       </c>
       <c r="L92" s="4" t="s">
         <v>25</v>
       </c>
       <c r="M92" s="5" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="93" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -7718,33 +7754,33 @@
         <v>4</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D93" s="6"/>
       <c r="E93" s="6"/>
       <c r="F93" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="G93" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="I93" s="6" t="s">
         <v>611</v>
       </c>
-      <c r="G93" s="6" t="s">
+      <c r="J93" s="6" t="s">
         <v>612</v>
       </c>
-      <c r="H93" s="6" t="s">
+      <c r="K93" s="6" t="s">
         <v>613</v>
-      </c>
-      <c r="I93" s="6" t="s">
-        <v>614</v>
-      </c>
-      <c r="J93" s="6" t="s">
-        <v>615</v>
-      </c>
-      <c r="K93" s="6" t="s">
-        <v>616</v>
       </c>
       <c r="L93" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M93" s="6" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -7755,31 +7791,31 @@
         <v>4</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D94" s="5"/>
       <c r="E94" s="5"/>
       <c r="F94" s="5"/>
       <c r="G94" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="H94" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="I94" s="5" t="s">
+        <v>617</v>
+      </c>
+      <c r="J94" s="5" t="s">
         <v>618</v>
       </c>
-      <c r="H94" s="5" t="s">
+      <c r="K94" s="5" t="s">
         <v>619</v>
-      </c>
-      <c r="I94" s="5" t="s">
-        <v>620</v>
-      </c>
-      <c r="J94" s="5" t="s">
-        <v>621</v>
-      </c>
-      <c r="K94" s="5" t="s">
-        <v>622</v>
       </c>
       <c r="L94" s="4" t="s">
         <v>32</v>
       </c>
       <c r="M94" s="5" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -7790,31 +7826,31 @@
         <v>4</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D95" s="6"/>
       <c r="E95" s="6"/>
       <c r="F95" s="6"/>
       <c r="G95" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>622</v>
+      </c>
+      <c r="I95" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="J95" s="6" t="s">
         <v>624</v>
       </c>
-      <c r="H95" s="6" t="s">
+      <c r="K95" s="6" t="s">
         <v>625</v>
-      </c>
-      <c r="I95" s="6" t="s">
-        <v>626</v>
-      </c>
-      <c r="J95" s="6" t="s">
-        <v>627</v>
-      </c>
-      <c r="K95" s="6" t="s">
-        <v>628</v>
       </c>
       <c r="L95" s="2" t="s">
         <v>39</v>
       </c>
       <c r="M95" s="6" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="96" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -7825,38 +7861,36 @@
         <v>4</v>
       </c>
       <c r="C96" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="D96" s="5"/>
+      <c r="E96" s="5"/>
+      <c r="F96" s="5" t="s">
+        <v>628</v>
+      </c>
+      <c r="G96" s="5" t="s">
+        <v>629</v>
+      </c>
+      <c r="H96" s="5" t="s">
         <v>630</v>
       </c>
-      <c r="D96" s="5"/>
-      <c r="E96" s="5" t="s">
+      <c r="I96" s="5" t="s">
         <v>631</v>
       </c>
-      <c r="F96" s="5" t="s">
+      <c r="J96" s="5" t="s">
         <v>632</v>
       </c>
-      <c r="G96" s="5" t="s">
+      <c r="K96" s="5" t="s">
         <v>633</v>
-      </c>
-      <c r="H96" s="5" t="s">
-        <v>634</v>
-      </c>
-      <c r="I96" s="5" t="s">
-        <v>635</v>
-      </c>
-      <c r="J96" s="5" t="s">
-        <v>636</v>
-      </c>
-      <c r="K96" s="5" t="s">
-        <v>637</v>
       </c>
       <c r="L96" s="4" t="s">
         <v>52</v>
       </c>
       <c r="M96" s="5" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>96</v>
       </c>
@@ -7864,31 +7898,33 @@
         <v>4</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="D97" s="6"/>
-      <c r="E97" s="6"/>
+      <c r="E97" s="9" t="s">
+        <v>1334</v>
+      </c>
       <c r="F97" s="6"/>
       <c r="G97" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="H97" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="I97" s="6" t="s">
+        <v>637</v>
+      </c>
+      <c r="J97" s="6" t="s">
+        <v>638</v>
+      </c>
+      <c r="K97" s="6" t="s">
         <v>639</v>
-      </c>
-      <c r="H97" s="6" t="s">
-        <v>640</v>
-      </c>
-      <c r="I97" s="6" t="s">
-        <v>641</v>
-      </c>
-      <c r="J97" s="6" t="s">
-        <v>642</v>
-      </c>
-      <c r="K97" s="6" t="s">
-        <v>643</v>
       </c>
       <c r="L97" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M97" s="6" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
     </row>
     <row r="98" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -7899,31 +7935,31 @@
         <v>4</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="D98" s="5"/>
       <c r="E98" s="5"/>
       <c r="F98" s="5"/>
       <c r="G98" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="H98" s="5" t="s">
+        <v>642</v>
+      </c>
+      <c r="I98" s="5" t="s">
+        <v>643</v>
+      </c>
+      <c r="J98" s="5" t="s">
+        <v>644</v>
+      </c>
+      <c r="K98" s="5" t="s">
         <v>645</v>
-      </c>
-      <c r="H98" s="5" t="s">
-        <v>646</v>
-      </c>
-      <c r="I98" s="5" t="s">
-        <v>647</v>
-      </c>
-      <c r="J98" s="5" t="s">
-        <v>648</v>
-      </c>
-      <c r="K98" s="5" t="s">
-        <v>649</v>
       </c>
       <c r="L98" s="4" t="s">
         <v>32</v>
       </c>
       <c r="M98" s="5" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
     </row>
     <row r="99" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -7934,38 +7970,36 @@
         <v>4</v>
       </c>
       <c r="C99" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="D99" s="6"/>
+      <c r="E99" s="6"/>
+      <c r="F99" s="6" t="s">
+        <v>648</v>
+      </c>
+      <c r="G99" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>649</v>
+      </c>
+      <c r="I99" s="6" t="s">
+        <v>650</v>
+      </c>
+      <c r="J99" s="6" t="s">
         <v>651</v>
       </c>
-      <c r="D99" s="6"/>
-      <c r="E99" s="6" t="s">
+      <c r="K99" s="6" t="s">
         <v>652</v>
-      </c>
-      <c r="F99" s="6" t="s">
-        <v>653</v>
-      </c>
-      <c r="G99" s="6" t="s">
-        <v>592</v>
-      </c>
-      <c r="H99" s="6" t="s">
-        <v>654</v>
-      </c>
-      <c r="I99" s="6" t="s">
-        <v>655</v>
-      </c>
-      <c r="J99" s="6" t="s">
-        <v>656</v>
-      </c>
-      <c r="K99" s="6" t="s">
-        <v>657</v>
       </c>
       <c r="L99" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M99" s="6" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A100" s="4">
         <v>99</v>
       </c>
@@ -7973,31 +8007,33 @@
         <v>4</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="D100" s="5"/>
-      <c r="E100" s="5"/>
+      <c r="E100" s="8" t="s">
+        <v>1335</v>
+      </c>
       <c r="F100" s="5"/>
       <c r="G100" s="5" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="I100" s="5" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="J100" s="5" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="K100" s="5" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="L100" s="4" t="s">
         <v>39</v>
       </c>
       <c r="M100" s="5" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
     </row>
     <row r="101" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -8008,31 +8044,31 @@
         <v>4</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="D101" s="6"/>
       <c r="E101" s="6"/>
       <c r="F101" s="6"/>
       <c r="G101" s="6" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="J101" s="6" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="K101" s="6" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="L101" s="2" t="s">
         <v>39</v>
       </c>
       <c r="M101" s="6" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
     </row>
     <row r="102" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -8043,31 +8079,31 @@
         <v>5</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="D102" s="5"/>
       <c r="E102" s="5"/>
       <c r="F102" s="5"/>
       <c r="G102" s="5" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="I102" s="5" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="J102" s="5" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="K102" s="5" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="L102" s="4" t="s">
         <v>32</v>
       </c>
       <c r="M102" s="5" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
     </row>
     <row r="103" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -8078,31 +8114,31 @@
         <v>5</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="D103" s="6"/>
       <c r="E103" s="6"/>
       <c r="F103" s="6"/>
       <c r="G103" s="6" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="I103" s="6" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="J103" s="6" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="K103" s="6" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="L103" s="2" t="s">
         <v>39</v>
       </c>
       <c r="M103" s="6" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
     </row>
     <row r="104" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -8113,31 +8149,31 @@
         <v>5</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="D104" s="5"/>
       <c r="E104" s="5"/>
       <c r="F104" s="5"/>
       <c r="G104" s="5" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="I104" s="5" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="J104" s="5" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="K104" s="5" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="L104" s="4" t="s">
         <v>52</v>
       </c>
       <c r="M104" s="5" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
     </row>
     <row r="105" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -8148,31 +8184,31 @@
         <v>5</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="D105" s="6"/>
       <c r="E105" s="6"/>
       <c r="F105" s="6"/>
       <c r="G105" s="6" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="I105" s="6" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="J105" s="6" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="K105" s="6" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="L105" s="2" t="s">
         <v>39</v>
       </c>
       <c r="M105" s="6" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
     </row>
     <row r="106" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -8183,31 +8219,31 @@
         <v>5</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="D106" s="5"/>
       <c r="E106" s="5"/>
       <c r="F106" s="5"/>
       <c r="G106" s="5" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="J106" s="5" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="K106" s="5" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="L106" s="4" t="s">
         <v>25</v>
       </c>
       <c r="M106" s="5" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
     </row>
     <row r="107" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -8218,31 +8254,31 @@
         <v>5</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="D107" s="6"/>
       <c r="E107" s="6"/>
       <c r="F107" s="6"/>
       <c r="G107" s="6" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="H107" s="6" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="I107" s="6" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="J107" s="6" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="K107" s="6" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="L107" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M107" s="6" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
     </row>
     <row r="108" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -8253,31 +8289,31 @@
         <v>5</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="D108" s="5"/>
       <c r="E108" s="5"/>
       <c r="F108" s="5"/>
       <c r="G108" s="5" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="H108" s="5" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="I108" s="5" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="J108" s="5" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="K108" s="5" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="L108" s="4" t="s">
         <v>52</v>
       </c>
       <c r="M108" s="5" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
     </row>
     <row r="109" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -8288,31 +8324,31 @@
         <v>5</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="D109" s="6"/>
       <c r="E109" s="6"/>
       <c r="F109" s="6"/>
       <c r="G109" s="6" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="I109" s="6" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="J109" s="6" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="K109" s="6" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="L109" s="2" t="s">
         <v>39</v>
       </c>
       <c r="M109" s="6" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
     </row>
     <row r="110" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -8323,31 +8359,31 @@
         <v>5</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="D110" s="5"/>
       <c r="E110" s="5"/>
       <c r="F110" s="5"/>
       <c r="G110" s="5" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="H110" s="5" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="I110" s="5" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="J110" s="5" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="K110" s="5" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="L110" s="4" t="s">
         <v>32</v>
       </c>
       <c r="M110" s="5" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
     </row>
     <row r="111" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -8358,31 +8394,31 @@
         <v>5</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="D111" s="6"/>
       <c r="E111" s="6"/>
       <c r="F111" s="6"/>
       <c r="G111" s="6" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="H111" s="6" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="I111" s="6" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="J111" s="6" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="K111" s="6" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="L111" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M111" s="6" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
     </row>
     <row r="112" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -8393,31 +8429,31 @@
         <v>5</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="D112" s="5"/>
       <c r="E112" s="5"/>
       <c r="F112" s="5"/>
       <c r="G112" s="5" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="H112" s="5" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="I112" s="5" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="J112" s="5" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="K112" s="5" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="L112" s="4" t="s">
         <v>32</v>
       </c>
       <c r="M112" s="5" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
     </row>
     <row r="113" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -8428,31 +8464,31 @@
         <v>5</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="D113" s="6"/>
       <c r="E113" s="6"/>
       <c r="F113" s="6"/>
       <c r="G113" s="6" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="H113" s="6" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="I113" s="6" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="J113" s="6" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="K113" s="6" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="L113" s="2" t="s">
         <v>39</v>
       </c>
       <c r="M113" s="6" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
     </row>
     <row r="114" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -8463,31 +8499,31 @@
         <v>5</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="D114" s="5"/>
       <c r="E114" s="5"/>
       <c r="F114" s="5"/>
       <c r="G114" s="5" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="H114" s="5" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="I114" s="5" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="J114" s="5" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="K114" s="5" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="L114" s="4" t="s">
         <v>25</v>
       </c>
       <c r="M114" s="5" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
     </row>
     <row r="115" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -8498,31 +8534,31 @@
         <v>5</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="D115" s="6"/>
       <c r="E115" s="6"/>
       <c r="F115" s="6"/>
       <c r="G115" s="6" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="H115" s="6" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="I115" s="6" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="J115" s="6" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="K115" s="6" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="L115" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M115" s="6" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
     </row>
     <row r="116" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -8533,31 +8569,31 @@
         <v>5</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="D116" s="5"/>
       <c r="E116" s="5"/>
       <c r="F116" s="5"/>
       <c r="G116" s="5" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="H116" s="5" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="I116" s="5" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="J116" s="5" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="K116" s="5" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="L116" s="4" t="s">
         <v>52</v>
       </c>
       <c r="M116" s="5" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
     </row>
     <row r="117" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -8568,31 +8604,31 @@
         <v>5</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="D117" s="6"/>
       <c r="E117" s="6"/>
       <c r="F117" s="6"/>
       <c r="G117" s="6" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="H117" s="6" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="I117" s="6" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="J117" s="6" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="K117" s="6" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="L117" s="2" t="s">
         <v>39</v>
       </c>
       <c r="M117" s="6" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
     </row>
     <row r="118" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -8603,31 +8639,31 @@
         <v>5</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="D118" s="5"/>
       <c r="E118" s="5"/>
       <c r="F118" s="5"/>
       <c r="G118" s="5" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="H118" s="5" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="I118" s="5" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="J118" s="5" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="K118" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="L118" s="4" t="s">
         <v>39</v>
       </c>
       <c r="M118" s="5" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
     </row>
     <row r="119" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -8638,31 +8674,31 @@
         <v>5</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="D119" s="6"/>
       <c r="E119" s="6"/>
       <c r="F119" s="6"/>
       <c r="G119" s="6" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="H119" s="6" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="I119" s="6" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="J119" s="6" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="K119" s="6" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="L119" s="2" t="s">
         <v>52</v>
       </c>
       <c r="M119" s="6" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
     </row>
     <row r="120" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -8673,31 +8709,31 @@
         <v>5</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="D120" s="5"/>
       <c r="E120" s="5"/>
       <c r="F120" s="5"/>
       <c r="G120" s="5" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="I120" s="5" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="J120" s="5" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="K120" s="5" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="L120" s="4" t="s">
         <v>32</v>
       </c>
       <c r="M120" s="5" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
     </row>
     <row r="121" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -8708,31 +8744,31 @@
         <v>5</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D121" s="6"/>
       <c r="E121" s="6"/>
       <c r="F121" s="6"/>
       <c r="G121" s="6" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="H121" s="6" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="I121" s="6" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="J121" s="6" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="K121" s="6" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="L121" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M121" s="6" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
     </row>
     <row r="122" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -8743,31 +8779,31 @@
         <v>5</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="D122" s="5"/>
       <c r="E122" s="5"/>
       <c r="F122" s="5"/>
       <c r="G122" s="5" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="I122" s="5" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="J122" s="5" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="K122" s="5" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="L122" s="4" t="s">
         <v>39</v>
       </c>
       <c r="M122" s="5" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
     </row>
     <row r="123" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -8778,31 +8814,31 @@
         <v>5</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="D123" s="6"/>
       <c r="E123" s="6"/>
       <c r="F123" s="6"/>
       <c r="G123" s="6" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="H123" s="6" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="I123" s="6" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="J123" s="6" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="K123" s="6" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="L123" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M123" s="6" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
     </row>
     <row r="124" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -8813,31 +8849,31 @@
         <v>5</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="D124" s="5"/>
       <c r="E124" s="5"/>
       <c r="F124" s="5"/>
       <c r="G124" s="5" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
       <c r="H124" s="5" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="I124" s="5" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="J124" s="5" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="K124" s="5" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="L124" s="4" t="s">
         <v>25</v>
       </c>
       <c r="M124" s="5" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
     </row>
     <row r="125" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -8848,31 +8884,31 @@
         <v>5</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="D125" s="6"/>
       <c r="E125" s="6"/>
       <c r="F125" s="6"/>
       <c r="G125" s="6" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="H125" s="6" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="I125" s="6" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="J125" s="6" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="K125" s="6" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="L125" s="2" t="s">
         <v>39</v>
       </c>
       <c r="M125" s="6" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
     </row>
     <row r="126" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -8883,31 +8919,31 @@
         <v>5</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="D126" s="5"/>
       <c r="E126" s="5"/>
       <c r="F126" s="5"/>
       <c r="G126" s="5" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="H126" s="5" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="I126" s="5" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="J126" s="5" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="K126" s="5" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="L126" s="4" t="s">
         <v>25</v>
       </c>
       <c r="M126" s="5" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
     </row>
     <row r="127" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -8918,31 +8954,31 @@
         <v>5</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="D127" s="6"/>
       <c r="E127" s="6"/>
       <c r="F127" s="6"/>
       <c r="G127" s="6" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="H127" s="6" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="I127" s="6" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="J127" s="6" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="K127" s="6" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
       <c r="L127" s="2" t="s">
         <v>52</v>
       </c>
       <c r="M127" s="6" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
     </row>
     <row r="128" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -8953,31 +8989,31 @@
         <v>5</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="D128" s="5"/>
       <c r="E128" s="5"/>
       <c r="F128" s="5"/>
       <c r="G128" s="5" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="H128" s="5" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="I128" s="5" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="J128" s="5" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="K128" s="5" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="L128" s="4" t="s">
         <v>39</v>
       </c>
       <c r="M128" s="5" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
     </row>
     <row r="129" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -8988,31 +9024,31 @@
         <v>5</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="D129" s="6"/>
       <c r="E129" s="6"/>
       <c r="F129" s="6"/>
       <c r="G129" s="6" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="H129" s="6" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="I129" s="6" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="J129" s="6" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="K129" s="6" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="L129" s="2" t="s">
         <v>39</v>
       </c>
       <c r="M129" s="6" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
     </row>
     <row r="130" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -9023,31 +9059,31 @@
         <v>5</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="D130" s="5"/>
       <c r="E130" s="5"/>
       <c r="F130" s="5"/>
       <c r="G130" s="5" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="H130" s="5" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="I130" s="5" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="J130" s="5" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="K130" s="5" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="L130" s="4" t="s">
         <v>32</v>
       </c>
       <c r="M130" s="5" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
     </row>
     <row r="131" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -9058,34 +9094,34 @@
         <v>5</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="D131" s="6"/>
       <c r="E131" s="6"/>
       <c r="F131" s="6"/>
       <c r="G131" s="6" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="H131" s="6" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="I131" s="6" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="J131" s="6" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="K131" s="6" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="L131" s="2" t="s">
         <v>39</v>
       </c>
       <c r="M131" s="6" t="s">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="132" spans="1:13" ht="150" x14ac:dyDescent="0.25">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A132" s="4">
         <v>131</v>
       </c>
@@ -9093,33 +9129,33 @@
         <v>6</v>
       </c>
       <c r="C132" s="4" t="s">
+        <v>876</v>
+      </c>
+      <c r="D132" s="5"/>
+      <c r="E132" s="8" t="s">
+        <v>1336</v>
+      </c>
+      <c r="F132" s="5"/>
+      <c r="G132" s="5" t="s">
+        <v>877</v>
+      </c>
+      <c r="H132" s="5" t="s">
+        <v>878</v>
+      </c>
+      <c r="I132" s="5" t="s">
+        <v>879</v>
+      </c>
+      <c r="J132" s="5" t="s">
+        <v>880</v>
+      </c>
+      <c r="K132" s="5" t="s">
         <v>881</v>
-      </c>
-      <c r="D132" s="5"/>
-      <c r="E132" s="5"/>
-      <c r="F132" s="5" t="s">
-        <v>882</v>
-      </c>
-      <c r="G132" s="5" t="s">
-        <v>883</v>
-      </c>
-      <c r="H132" s="5" t="s">
-        <v>884</v>
-      </c>
-      <c r="I132" s="5" t="s">
-        <v>885</v>
-      </c>
-      <c r="J132" s="5" t="s">
-        <v>886</v>
-      </c>
-      <c r="K132" s="5" t="s">
-        <v>887</v>
       </c>
       <c r="L132" s="4" t="s">
         <v>39</v>
       </c>
       <c r="M132" s="5" t="s">
-        <v>888</v>
+        <v>882</v>
       </c>
     </row>
     <row r="133" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -9130,31 +9166,31 @@
         <v>6</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="D133" s="6"/>
       <c r="E133" s="6"/>
       <c r="F133" s="6"/>
       <c r="G133" s="6" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="H133" s="6" t="s">
-        <v>890</v>
+        <v>884</v>
       </c>
       <c r="I133" s="6" t="s">
-        <v>891</v>
+        <v>885</v>
       </c>
       <c r="J133" s="6" t="s">
-        <v>892</v>
+        <v>886</v>
       </c>
       <c r="K133" s="6" t="s">
-        <v>893</v>
+        <v>887</v>
       </c>
       <c r="L133" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M133" s="6" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
     </row>
     <row r="134" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -9165,31 +9201,31 @@
         <v>6</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="D134" s="5"/>
       <c r="E134" s="5"/>
       <c r="F134" s="5"/>
       <c r="G134" s="5" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="H134" s="5" t="s">
-        <v>896</v>
+        <v>890</v>
       </c>
       <c r="I134" s="5" t="s">
-        <v>897</v>
+        <v>891</v>
       </c>
       <c r="J134" s="5" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="K134" s="5" t="s">
-        <v>899</v>
+        <v>893</v>
       </c>
       <c r="L134" s="4" t="s">
         <v>32</v>
       </c>
       <c r="M134" s="5" t="s">
-        <v>900</v>
+        <v>894</v>
       </c>
     </row>
     <row r="135" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -9200,31 +9236,31 @@
         <v>6</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="D135" s="6"/>
       <c r="E135" s="6"/>
       <c r="F135" s="6"/>
       <c r="G135" s="6" t="s">
-        <v>901</v>
+        <v>895</v>
       </c>
       <c r="H135" s="6" t="s">
-        <v>902</v>
+        <v>896</v>
       </c>
       <c r="I135" s="6" t="s">
-        <v>903</v>
+        <v>897</v>
       </c>
       <c r="J135" s="6" t="s">
-        <v>904</v>
+        <v>898</v>
       </c>
       <c r="K135" s="6" t="s">
-        <v>905</v>
+        <v>899</v>
       </c>
       <c r="L135" s="2" t="s">
         <v>52</v>
       </c>
       <c r="M135" s="6" t="s">
-        <v>906</v>
+        <v>900</v>
       </c>
     </row>
     <row r="136" spans="1:13" ht="150" x14ac:dyDescent="0.25">
@@ -9235,33 +9271,33 @@
         <v>6</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>907</v>
+        <v>901</v>
       </c>
       <c r="D136" s="5"/>
       <c r="E136" s="5"/>
       <c r="F136" s="5" t="s">
-        <v>908</v>
+        <v>902</v>
       </c>
       <c r="G136" s="5" t="s">
-        <v>909</v>
+        <v>903</v>
       </c>
       <c r="H136" s="5" t="s">
-        <v>910</v>
+        <v>904</v>
       </c>
       <c r="I136" s="5" t="s">
-        <v>911</v>
+        <v>905</v>
       </c>
       <c r="J136" s="5" t="s">
-        <v>912</v>
+        <v>906</v>
       </c>
       <c r="K136" s="5" t="s">
-        <v>913</v>
+        <v>907</v>
       </c>
       <c r="L136" s="4" t="s">
         <v>25</v>
       </c>
       <c r="M136" s="5" t="s">
-        <v>914</v>
+        <v>908</v>
       </c>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.25">
@@ -9272,31 +9308,31 @@
         <v>6</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>907</v>
+        <v>901</v>
       </c>
       <c r="D137" s="6"/>
       <c r="E137" s="6"/>
       <c r="F137" s="6"/>
       <c r="G137" s="6" t="s">
-        <v>915</v>
+        <v>909</v>
       </c>
       <c r="H137" s="6" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="I137" s="6" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="J137" s="6" t="s">
-        <v>918</v>
+        <v>912</v>
       </c>
       <c r="K137" s="6" t="s">
-        <v>919</v>
+        <v>913</v>
       </c>
       <c r="L137" s="2" t="s">
         <v>52</v>
       </c>
       <c r="M137" s="6" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
     </row>
     <row r="138" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -9307,31 +9343,31 @@
         <v>6</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>907</v>
+        <v>901</v>
       </c>
       <c r="D138" s="5"/>
       <c r="E138" s="5"/>
       <c r="F138" s="5"/>
       <c r="G138" s="5" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="H138" s="5" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="I138" s="5" t="s">
-        <v>922</v>
+        <v>916</v>
       </c>
       <c r="J138" s="5" t="s">
-        <v>923</v>
+        <v>917</v>
       </c>
       <c r="K138" s="5" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
       <c r="L138" s="4" t="s">
         <v>32</v>
       </c>
       <c r="M138" s="5" t="s">
-        <v>925</v>
+        <v>919</v>
       </c>
     </row>
     <row r="139" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -9342,31 +9378,31 @@
         <v>6</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>907</v>
+        <v>901</v>
       </c>
       <c r="D139" s="6"/>
       <c r="E139" s="6"/>
       <c r="F139" s="6"/>
       <c r="G139" s="6" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="H139" s="6" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="I139" s="6" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
       <c r="J139" s="6" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
       <c r="K139" s="6" t="s">
-        <v>930</v>
+        <v>924</v>
       </c>
       <c r="L139" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M139" s="6" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
     </row>
     <row r="140" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -9377,33 +9413,33 @@
         <v>6</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>932</v>
+        <v>926</v>
       </c>
       <c r="D140" s="5"/>
       <c r="E140" s="5"/>
       <c r="F140" s="5" t="s">
-        <v>933</v>
+        <v>927</v>
       </c>
       <c r="G140" s="5" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
       <c r="H140" s="5" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
       <c r="I140" s="5" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="J140" s="5" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
       <c r="K140" s="5" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="L140" s="4" t="s">
         <v>52</v>
       </c>
       <c r="M140" s="5" t="s">
-        <v>939</v>
+        <v>933</v>
       </c>
     </row>
     <row r="141" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -9414,31 +9450,31 @@
         <v>6</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>932</v>
+        <v>926</v>
       </c>
       <c r="D141" s="6"/>
       <c r="E141" s="6"/>
       <c r="F141" s="6"/>
       <c r="G141" s="6" t="s">
-        <v>940</v>
+        <v>934</v>
       </c>
       <c r="H141" s="6" t="s">
-        <v>941</v>
+        <v>935</v>
       </c>
       <c r="I141" s="6" t="s">
-        <v>942</v>
+        <v>936</v>
       </c>
       <c r="J141" s="6" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
       <c r="K141" s="6" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
       <c r="L141" s="2" t="s">
         <v>52</v>
       </c>
       <c r="M141" s="6" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
     </row>
     <row r="142" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -9449,31 +9485,31 @@
         <v>6</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>932</v>
+        <v>926</v>
       </c>
       <c r="D142" s="5"/>
       <c r="E142" s="5"/>
       <c r="F142" s="5"/>
       <c r="G142" s="5" t="s">
-        <v>946</v>
+        <v>940</v>
       </c>
       <c r="H142" s="5" t="s">
-        <v>947</v>
+        <v>941</v>
       </c>
       <c r="I142" s="5" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="J142" s="5" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="K142" s="5" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="L142" s="4" t="s">
         <v>25</v>
       </c>
       <c r="M142" s="5" t="s">
-        <v>951</v>
+        <v>945</v>
       </c>
     </row>
     <row r="143" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -9484,31 +9520,31 @@
         <v>6</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>932</v>
+        <v>926</v>
       </c>
       <c r="D143" s="6"/>
       <c r="E143" s="6"/>
       <c r="F143" s="6"/>
       <c r="G143" s="6" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="H143" s="6" t="s">
-        <v>952</v>
+        <v>946</v>
       </c>
       <c r="I143" s="6" t="s">
-        <v>953</v>
+        <v>947</v>
       </c>
       <c r="J143" s="6" t="s">
-        <v>954</v>
+        <v>948</v>
       </c>
       <c r="K143" s="6" t="s">
-        <v>955</v>
+        <v>949</v>
       </c>
       <c r="L143" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M143" s="6" t="s">
-        <v>956</v>
+        <v>950</v>
       </c>
     </row>
     <row r="144" spans="1:13" ht="150" x14ac:dyDescent="0.25">
@@ -9519,33 +9555,33 @@
         <v>6</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
       <c r="D144" s="5"/>
       <c r="E144" s="5"/>
       <c r="F144" s="5" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="G144" s="5" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
       <c r="H144" s="5" t="s">
-        <v>960</v>
+        <v>954</v>
       </c>
       <c r="I144" s="5" t="s">
-        <v>961</v>
+        <v>955</v>
       </c>
       <c r="J144" s="5" t="s">
-        <v>962</v>
+        <v>956</v>
       </c>
       <c r="K144" s="5" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="L144" s="4" t="s">
         <v>39</v>
       </c>
       <c r="M144" s="5" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
     </row>
     <row r="145" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -9556,31 +9592,31 @@
         <v>6</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
       <c r="D145" s="6"/>
       <c r="E145" s="6"/>
       <c r="F145" s="6"/>
       <c r="G145" s="6" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="H145" s="6" t="s">
-        <v>966</v>
+        <v>960</v>
       </c>
       <c r="I145" s="6" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="J145" s="6" t="s">
-        <v>968</v>
+        <v>962</v>
       </c>
       <c r="K145" s="6" t="s">
-        <v>969</v>
+        <v>963</v>
       </c>
       <c r="L145" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M145" s="6" t="s">
-        <v>970</v>
+        <v>964</v>
       </c>
     </row>
     <row r="146" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -9591,31 +9627,31 @@
         <v>6</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
       <c r="D146" s="5"/>
       <c r="E146" s="5"/>
       <c r="F146" s="5"/>
       <c r="G146" s="5" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="H146" s="5" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="I146" s="5" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="J146" s="5" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="K146" s="5" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="L146" s="4" t="s">
         <v>52</v>
       </c>
       <c r="M146" s="5" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
     </row>
     <row r="147" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -9626,31 +9662,31 @@
         <v>6</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
       <c r="D147" s="6"/>
       <c r="E147" s="6"/>
       <c r="F147" s="6"/>
       <c r="G147" s="6" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="H147" s="6" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="I147" s="6" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="J147" s="6" t="s">
-        <v>979</v>
+        <v>973</v>
       </c>
       <c r="K147" s="6" t="s">
-        <v>980</v>
+        <v>974</v>
       </c>
       <c r="L147" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M147" s="6" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
     </row>
     <row r="148" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -9661,33 +9697,33 @@
         <v>7</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="D148" s="5"/>
       <c r="E148" s="5"/>
       <c r="F148" s="5" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="H148" s="5" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="I148" s="5" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="J148" s="5" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
       <c r="K148" s="5" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
       <c r="L148" s="4" t="s">
         <v>52</v>
       </c>
       <c r="M148" s="5" t="s">
-        <v>989</v>
+        <v>983</v>
       </c>
     </row>
     <row r="149" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -9698,31 +9734,31 @@
         <v>7</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="D149" s="6"/>
       <c r="E149" s="6"/>
       <c r="F149" s="6"/>
       <c r="G149" s="6" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
       <c r="H149" s="6" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="I149" s="6" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="J149" s="6" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="K149" s="6" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
       <c r="L149" s="2" t="s">
         <v>39</v>
       </c>
       <c r="M149" s="6" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
     </row>
     <row r="150" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -9733,33 +9769,33 @@
         <v>7</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="D150" s="5"/>
       <c r="E150" s="5"/>
       <c r="F150" s="5" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="G150" s="5" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="H150" s="5" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="I150" s="5" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="J150" s="5" t="s">
-        <v>1001</v>
+        <v>995</v>
       </c>
       <c r="K150" s="5" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="L150" s="4" t="s">
         <v>39</v>
       </c>
       <c r="M150" s="5" t="s">
-        <v>1003</v>
+        <v>997</v>
       </c>
     </row>
     <row r="151" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -9770,31 +9806,31 @@
         <v>7</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="D151" s="6"/>
       <c r="E151" s="6"/>
       <c r="F151" s="6"/>
       <c r="G151" s="6" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="H151" s="6" t="s">
-        <v>1005</v>
+        <v>999</v>
       </c>
       <c r="I151" s="6" t="s">
-        <v>1006</v>
+        <v>1000</v>
       </c>
       <c r="J151" s="6" t="s">
-        <v>1007</v>
+        <v>1001</v>
       </c>
       <c r="K151" s="6" t="s">
-        <v>1008</v>
+        <v>1002</v>
       </c>
       <c r="L151" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M151" s="6" t="s">
-        <v>1009</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="152" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -9805,33 +9841,33 @@
         <v>7</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="D152" s="5"/>
       <c r="E152" s="5"/>
       <c r="F152" s="5" t="s">
-        <v>1011</v>
+        <v>1005</v>
       </c>
       <c r="G152" s="5" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="H152" s="5" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="I152" s="5" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="J152" s="5" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="K152" s="5" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="L152" s="4" t="s">
         <v>32</v>
       </c>
       <c r="M152" s="5" t="s">
-        <v>1017</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="153" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -9842,31 +9878,31 @@
         <v>7</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="D153" s="6"/>
       <c r="E153" s="6"/>
       <c r="F153" s="6"/>
       <c r="G153" s="6" t="s">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="H153" s="6" t="s">
         <v>278</v>
       </c>
       <c r="I153" s="6" t="s">
-        <v>1019</v>
+        <v>1013</v>
       </c>
       <c r="J153" s="6" t="s">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="K153" s="6" t="s">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="L153" s="2" t="s">
         <v>39</v>
       </c>
       <c r="M153" s="6" t="s">
-        <v>1022</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="154" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -9877,31 +9913,31 @@
         <v>7</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="D154" s="5"/>
       <c r="E154" s="5"/>
       <c r="F154" s="5"/>
       <c r="G154" s="5" t="s">
-        <v>1023</v>
+        <v>1017</v>
       </c>
       <c r="H154" s="5" t="s">
-        <v>1024</v>
+        <v>1018</v>
       </c>
       <c r="I154" s="5" t="s">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="J154" s="5" t="s">
-        <v>1026</v>
+        <v>1020</v>
       </c>
       <c r="K154" s="5" t="s">
-        <v>1027</v>
+        <v>1021</v>
       </c>
       <c r="L154" s="4" t="s">
         <v>25</v>
       </c>
       <c r="M154" s="5" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="155" spans="1:13" ht="150" x14ac:dyDescent="0.25">
@@ -9912,33 +9948,33 @@
         <v>7</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="D155" s="6"/>
       <c r="E155" s="6"/>
       <c r="F155" s="6" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="G155" s="6" t="s">
-        <v>1031</v>
+        <v>1025</v>
       </c>
       <c r="H155" s="6" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="I155" s="6" t="s">
-        <v>1033</v>
+        <v>1027</v>
       </c>
       <c r="J155" s="6" t="s">
-        <v>1034</v>
+        <v>1028</v>
       </c>
       <c r="K155" s="6" t="s">
-        <v>1035</v>
+        <v>1029</v>
       </c>
       <c r="L155" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M155" s="6" t="s">
-        <v>1036</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="156" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -9949,31 +9985,31 @@
         <v>7</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="D156" s="5"/>
       <c r="E156" s="5"/>
       <c r="F156" s="5"/>
       <c r="G156" s="5" t="s">
-        <v>1037</v>
+        <v>1031</v>
       </c>
       <c r="H156" s="5" t="s">
-        <v>1038</v>
+        <v>1032</v>
       </c>
       <c r="I156" s="5" t="s">
-        <v>1039</v>
+        <v>1033</v>
       </c>
       <c r="J156" s="5" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
       <c r="K156" s="5" t="s">
-        <v>1041</v>
+        <v>1035</v>
       </c>
       <c r="L156" s="4" t="s">
         <v>32</v>
       </c>
       <c r="M156" s="5" t="s">
-        <v>1042</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="157" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -9984,33 +10020,33 @@
         <v>7</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>1043</v>
+        <v>1037</v>
       </c>
       <c r="D157" s="6"/>
       <c r="E157" s="6"/>
       <c r="F157" s="6" t="s">
-        <v>1044</v>
+        <v>1038</v>
       </c>
       <c r="G157" s="6" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
       <c r="H157" s="6" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="I157" s="6" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
       <c r="J157" s="6" t="s">
-        <v>1048</v>
+        <v>1042</v>
       </c>
       <c r="K157" s="6" t="s">
-        <v>1049</v>
+        <v>1043</v>
       </c>
       <c r="L157" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M157" s="6" t="s">
-        <v>1050</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="158" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -10021,31 +10057,31 @@
         <v>7</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>1043</v>
+        <v>1037</v>
       </c>
       <c r="D158" s="5"/>
       <c r="E158" s="5"/>
       <c r="F158" s="5"/>
       <c r="G158" s="5" t="s">
-        <v>1051</v>
+        <v>1045</v>
       </c>
       <c r="H158" s="5" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
       <c r="I158" s="5" t="s">
-        <v>1053</v>
+        <v>1047</v>
       </c>
       <c r="J158" s="5" t="s">
-        <v>1054</v>
+        <v>1048</v>
       </c>
       <c r="K158" s="5" t="s">
-        <v>1055</v>
+        <v>1049</v>
       </c>
       <c r="L158" s="4" t="s">
         <v>25</v>
       </c>
       <c r="M158" s="5" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="159" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -10056,33 +10092,33 @@
         <v>7</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="D159" s="6"/>
       <c r="E159" s="6"/>
       <c r="F159" s="6" t="s">
-        <v>1058</v>
+        <v>1052</v>
       </c>
       <c r="G159" s="6" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="H159" s="6" t="s">
-        <v>1060</v>
+        <v>1054</v>
       </c>
       <c r="I159" s="6" t="s">
-        <v>1061</v>
+        <v>1055</v>
       </c>
       <c r="J159" s="6" t="s">
-        <v>1062</v>
+        <v>1056</v>
       </c>
       <c r="K159" s="6" t="s">
-        <v>1063</v>
+        <v>1057</v>
       </c>
       <c r="L159" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M159" s="6" t="s">
-        <v>1064</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="160" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -10093,31 +10129,31 @@
         <v>7</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="D160" s="5"/>
       <c r="E160" s="5"/>
       <c r="F160" s="5"/>
       <c r="G160" s="5" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
       <c r="H160" s="5" t="s">
-        <v>1066</v>
+        <v>1060</v>
       </c>
       <c r="I160" s="5" t="s">
-        <v>1067</v>
+        <v>1061</v>
       </c>
       <c r="J160" s="5" t="s">
-        <v>1068</v>
+        <v>1062</v>
       </c>
       <c r="K160" s="5" t="s">
-        <v>1069</v>
+        <v>1063</v>
       </c>
       <c r="L160" s="4" t="s">
         <v>39</v>
       </c>
       <c r="M160" s="5" t="s">
-        <v>1070</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="161" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -10128,31 +10164,31 @@
         <v>7</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="D161" s="6"/>
       <c r="E161" s="6"/>
       <c r="F161" s="6"/>
       <c r="G161" s="6" t="s">
-        <v>1071</v>
+        <v>1065</v>
       </c>
       <c r="H161" s="6" t="s">
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="I161" s="6" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="J161" s="6" t="s">
-        <v>1074</v>
+        <v>1068</v>
       </c>
       <c r="K161" s="6" t="s">
-        <v>1075</v>
+        <v>1069</v>
       </c>
       <c r="L161" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M161" s="6" t="s">
-        <v>1076</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="162" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -10163,31 +10199,31 @@
         <v>7</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="D162" s="5"/>
       <c r="E162" s="5"/>
       <c r="F162" s="5"/>
       <c r="G162" s="5" t="s">
-        <v>1077</v>
+        <v>1071</v>
       </c>
       <c r="H162" s="5" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="I162" s="5" t="s">
-        <v>1079</v>
+        <v>1073</v>
       </c>
       <c r="J162" s="5" t="s">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="K162" s="5" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
       <c r="L162" s="4" t="s">
         <v>52</v>
       </c>
       <c r="M162" s="5" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="163" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -10198,33 +10234,33 @@
         <v>7</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>1083</v>
+        <v>1077</v>
       </c>
       <c r="D163" s="6"/>
       <c r="E163" s="6"/>
       <c r="F163" s="6" t="s">
-        <v>1084</v>
+        <v>1078</v>
       </c>
       <c r="G163" s="6" t="s">
-        <v>1085</v>
+        <v>1079</v>
       </c>
       <c r="H163" s="6" t="s">
-        <v>1086</v>
+        <v>1080</v>
       </c>
       <c r="I163" s="6" t="s">
-        <v>1087</v>
+        <v>1081</v>
       </c>
       <c r="J163" s="6" t="s">
-        <v>1088</v>
+        <v>1082</v>
       </c>
       <c r="K163" s="6" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="L163" s="2" t="s">
         <v>52</v>
       </c>
       <c r="M163" s="6" t="s">
-        <v>1090</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="164" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -10235,31 +10271,31 @@
         <v>7</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>1083</v>
+        <v>1077</v>
       </c>
       <c r="D164" s="5"/>
       <c r="E164" s="5"/>
       <c r="F164" s="5"/>
       <c r="G164" s="5" t="s">
-        <v>1091</v>
+        <v>1085</v>
       </c>
       <c r="H164" s="5" t="s">
-        <v>1092</v>
+        <v>1086</v>
       </c>
       <c r="I164" s="5" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="J164" s="5" t="s">
-        <v>1094</v>
+        <v>1088</v>
       </c>
       <c r="K164" s="5" t="s">
-        <v>1095</v>
+        <v>1089</v>
       </c>
       <c r="L164" s="4" t="s">
         <v>39</v>
       </c>
       <c r="M164" s="5" t="s">
-        <v>1096</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="165" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -10270,31 +10306,31 @@
         <v>7</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>1083</v>
+        <v>1077</v>
       </c>
       <c r="D165" s="6"/>
       <c r="E165" s="6"/>
       <c r="F165" s="6"/>
       <c r="G165" s="6" t="s">
-        <v>1097</v>
+        <v>1091</v>
       </c>
       <c r="H165" s="6" t="s">
-        <v>1098</v>
+        <v>1092</v>
       </c>
       <c r="I165" s="6" t="s">
-        <v>1099</v>
+        <v>1093</v>
       </c>
       <c r="J165" s="6" t="s">
-        <v>1100</v>
+        <v>1094</v>
       </c>
       <c r="K165" s="6" t="s">
-        <v>1101</v>
+        <v>1095</v>
       </c>
       <c r="L165" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M165" s="6" t="s">
-        <v>1102</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="166" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -10305,31 +10341,31 @@
         <v>7</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>1083</v>
+        <v>1077</v>
       </c>
       <c r="D166" s="5"/>
       <c r="E166" s="5"/>
       <c r="F166" s="5"/>
       <c r="G166" s="5" t="s">
-        <v>1103</v>
+        <v>1097</v>
       </c>
       <c r="H166" s="5" t="s">
-        <v>1104</v>
+        <v>1098</v>
       </c>
       <c r="I166" s="5" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="J166" s="5" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="K166" s="5" t="s">
-        <v>1107</v>
+        <v>1101</v>
       </c>
       <c r="L166" s="4" t="s">
         <v>25</v>
       </c>
       <c r="M166" s="5" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="167" spans="1:13" ht="165" x14ac:dyDescent="0.25">
@@ -10340,33 +10376,33 @@
         <v>7</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>1109</v>
+        <v>1103</v>
       </c>
       <c r="D167" s="6"/>
       <c r="E167" s="6"/>
       <c r="F167" s="6" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
       <c r="G167" s="6" t="s">
-        <v>1111</v>
+        <v>1105</v>
       </c>
       <c r="H167" s="6" t="s">
-        <v>1112</v>
+        <v>1106</v>
       </c>
       <c r="I167" s="6" t="s">
-        <v>1113</v>
+        <v>1107</v>
       </c>
       <c r="J167" s="6" t="s">
-        <v>1114</v>
+        <v>1108</v>
       </c>
       <c r="K167" s="6" t="s">
-        <v>1115</v>
+        <v>1109</v>
       </c>
       <c r="L167" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M167" s="6" t="s">
-        <v>1116</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="168" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -10377,31 +10413,31 @@
         <v>7</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>1109</v>
+        <v>1103</v>
       </c>
       <c r="D168" s="5"/>
       <c r="E168" s="5"/>
       <c r="F168" s="5"/>
       <c r="G168" s="5" t="s">
-        <v>1117</v>
+        <v>1111</v>
       </c>
       <c r="H168" s="5" t="s">
-        <v>1118</v>
+        <v>1112</v>
       </c>
       <c r="I168" s="5" t="s">
-        <v>1119</v>
+        <v>1113</v>
       </c>
       <c r="J168" s="5" t="s">
-        <v>1120</v>
+        <v>1114</v>
       </c>
       <c r="K168" s="5" t="s">
-        <v>1121</v>
+        <v>1115</v>
       </c>
       <c r="L168" s="4" t="s">
         <v>52</v>
       </c>
       <c r="M168" s="5" t="s">
-        <v>1122</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="169" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -10412,31 +10448,31 @@
         <v>7</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>1109</v>
+        <v>1103</v>
       </c>
       <c r="D169" s="6"/>
       <c r="E169" s="6"/>
       <c r="F169" s="6"/>
       <c r="G169" s="6" t="s">
-        <v>1123</v>
+        <v>1117</v>
       </c>
       <c r="H169" s="6" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
       <c r="I169" s="6" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
       <c r="J169" s="6" t="s">
-        <v>1126</v>
+        <v>1120</v>
       </c>
       <c r="K169" s="6" t="s">
-        <v>1127</v>
+        <v>1121</v>
       </c>
       <c r="L169" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M169" s="6" t="s">
-        <v>1128</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="170" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -10447,33 +10483,33 @@
         <v>7</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>1129</v>
+        <v>1123</v>
       </c>
       <c r="D170" s="5"/>
       <c r="E170" s="5"/>
       <c r="F170" s="5" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>1131</v>
+        <v>1125</v>
       </c>
       <c r="H170" s="5" t="s">
-        <v>1132</v>
+        <v>1126</v>
       </c>
       <c r="I170" s="5" t="s">
-        <v>1133</v>
+        <v>1127</v>
       </c>
       <c r="J170" s="5" t="s">
-        <v>1134</v>
+        <v>1128</v>
       </c>
       <c r="K170" s="5" t="s">
-        <v>1135</v>
+        <v>1129</v>
       </c>
       <c r="L170" s="4" t="s">
         <v>52</v>
       </c>
       <c r="M170" s="5" t="s">
-        <v>1136</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="171" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -10484,31 +10520,31 @@
         <v>7</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>1129</v>
+        <v>1123</v>
       </c>
       <c r="D171" s="6"/>
       <c r="E171" s="6"/>
       <c r="F171" s="6"/>
       <c r="G171" s="6" t="s">
-        <v>1137</v>
+        <v>1131</v>
       </c>
       <c r="H171" s="6" t="s">
-        <v>1138</v>
+        <v>1132</v>
       </c>
       <c r="I171" s="6" t="s">
-        <v>1139</v>
+        <v>1133</v>
       </c>
       <c r="J171" s="6" t="s">
-        <v>1140</v>
+        <v>1134</v>
       </c>
       <c r="K171" s="6" t="s">
-        <v>1141</v>
+        <v>1135</v>
       </c>
       <c r="L171" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M171" s="6" t="s">
-        <v>1142</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="172" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -10519,31 +10555,31 @@
         <v>7</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>1129</v>
+        <v>1123</v>
       </c>
       <c r="D172" s="5"/>
       <c r="E172" s="5"/>
       <c r="F172" s="5"/>
       <c r="G172" s="5" t="s">
-        <v>1143</v>
+        <v>1137</v>
       </c>
       <c r="H172" s="5" t="s">
-        <v>1144</v>
+        <v>1138</v>
       </c>
       <c r="I172" s="5" t="s">
-        <v>1145</v>
+        <v>1139</v>
       </c>
       <c r="J172" s="5" t="s">
-        <v>1146</v>
+        <v>1140</v>
       </c>
       <c r="K172" s="5" t="s">
-        <v>1147</v>
+        <v>1141</v>
       </c>
       <c r="L172" s="4" t="s">
         <v>32</v>
       </c>
       <c r="M172" s="5" t="s">
-        <v>1148</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="173" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -10554,33 +10590,33 @@
         <v>7</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>1149</v>
+        <v>1143</v>
       </c>
       <c r="D173" s="6"/>
       <c r="E173" s="6"/>
       <c r="F173" s="6" t="s">
-        <v>1150</v>
+        <v>1144</v>
       </c>
       <c r="G173" s="6" t="s">
-        <v>1151</v>
+        <v>1145</v>
       </c>
       <c r="H173" s="6" t="s">
-        <v>1152</v>
+        <v>1146</v>
       </c>
       <c r="I173" s="6" t="s">
-        <v>1153</v>
+        <v>1147</v>
       </c>
       <c r="J173" s="6" t="s">
-        <v>1154</v>
+        <v>1148</v>
       </c>
       <c r="K173" s="6" t="s">
-        <v>1155</v>
+        <v>1149</v>
       </c>
       <c r="L173" s="2" t="s">
         <v>39</v>
       </c>
       <c r="M173" s="6" t="s">
-        <v>1156</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="174" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -10591,31 +10627,31 @@
         <v>7</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>1149</v>
+        <v>1143</v>
       </c>
       <c r="D174" s="5"/>
       <c r="E174" s="5"/>
       <c r="F174" s="5"/>
       <c r="G174" s="5" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="H174" s="5" t="s">
-        <v>1158</v>
+        <v>1152</v>
       </c>
       <c r="I174" s="5" t="s">
-        <v>1159</v>
+        <v>1153</v>
       </c>
       <c r="J174" s="5" t="s">
-        <v>1160</v>
+        <v>1154</v>
       </c>
       <c r="K174" s="5" t="s">
-        <v>1161</v>
+        <v>1155</v>
       </c>
       <c r="L174" s="4" t="s">
         <v>32</v>
       </c>
       <c r="M174" s="5" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="175" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -10626,31 +10662,31 @@
         <v>7</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>1149</v>
+        <v>1143</v>
       </c>
       <c r="D175" s="6"/>
       <c r="E175" s="6"/>
       <c r="F175" s="6"/>
       <c r="G175" s="6" t="s">
-        <v>1163</v>
+        <v>1157</v>
       </c>
       <c r="H175" s="6" t="s">
-        <v>1164</v>
+        <v>1158</v>
       </c>
       <c r="I175" s="6" t="s">
-        <v>1165</v>
+        <v>1159</v>
       </c>
       <c r="J175" s="6" t="s">
-        <v>1166</v>
+        <v>1160</v>
       </c>
       <c r="K175" s="6" t="s">
-        <v>1167</v>
+        <v>1161</v>
       </c>
       <c r="L175" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M175" s="6" t="s">
-        <v>1168</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="176" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -10661,31 +10697,31 @@
         <v>7</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>1149</v>
+        <v>1143</v>
       </c>
       <c r="D176" s="5"/>
       <c r="E176" s="5"/>
       <c r="F176" s="5"/>
       <c r="G176" s="5" t="s">
-        <v>1169</v>
+        <v>1163</v>
       </c>
       <c r="H176" s="5" t="s">
-        <v>1144</v>
+        <v>1138</v>
       </c>
       <c r="I176" s="5" t="s">
-        <v>1145</v>
+        <v>1139</v>
       </c>
       <c r="J176" s="5" t="s">
-        <v>1146</v>
+        <v>1140</v>
       </c>
       <c r="K176" s="5" t="s">
-        <v>1147</v>
+        <v>1141</v>
       </c>
       <c r="L176" s="4" t="s">
         <v>52</v>
       </c>
       <c r="M176" s="5" t="s">
-        <v>1170</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="177" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -10696,33 +10732,33 @@
         <v>7</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>1171</v>
+        <v>1165</v>
       </c>
       <c r="D177" s="6"/>
       <c r="E177" s="6"/>
       <c r="F177" s="6" t="s">
-        <v>1172</v>
+        <v>1166</v>
       </c>
       <c r="G177" s="6" t="s">
-        <v>1173</v>
+        <v>1167</v>
       </c>
       <c r="H177" s="6" t="s">
-        <v>1174</v>
+        <v>1168</v>
       </c>
       <c r="I177" s="6" t="s">
-        <v>1175</v>
+        <v>1169</v>
       </c>
       <c r="J177" s="6" t="s">
-        <v>1176</v>
+        <v>1170</v>
       </c>
       <c r="K177" s="6" t="s">
-        <v>1177</v>
+        <v>1171</v>
       </c>
       <c r="L177" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M177" s="6" t="s">
-        <v>1178</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="178" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -10733,31 +10769,31 @@
         <v>7</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>1171</v>
+        <v>1165</v>
       </c>
       <c r="D178" s="5"/>
       <c r="E178" s="5"/>
       <c r="F178" s="5"/>
       <c r="G178" s="5" t="s">
-        <v>1179</v>
+        <v>1173</v>
       </c>
       <c r="H178" s="5" t="s">
-        <v>1180</v>
+        <v>1174</v>
       </c>
       <c r="I178" s="5" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="J178" s="5" t="s">
-        <v>1182</v>
+        <v>1176</v>
       </c>
       <c r="K178" s="5" t="s">
-        <v>1183</v>
+        <v>1177</v>
       </c>
       <c r="L178" s="4" t="s">
         <v>52</v>
       </c>
       <c r="M178" s="5" t="s">
-        <v>1184</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="179" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -10768,31 +10804,31 @@
         <v>7</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>1171</v>
+        <v>1165</v>
       </c>
       <c r="D179" s="6"/>
       <c r="E179" s="6"/>
       <c r="F179" s="6"/>
       <c r="G179" s="6" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
       <c r="H179" s="6" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="I179" s="6" t="s">
-        <v>1187</v>
+        <v>1181</v>
       </c>
       <c r="J179" s="6" t="s">
-        <v>1188</v>
+        <v>1182</v>
       </c>
       <c r="K179" s="6" t="s">
-        <v>1189</v>
+        <v>1183</v>
       </c>
       <c r="L179" s="2" t="s">
         <v>39</v>
       </c>
       <c r="M179" s="6" t="s">
-        <v>1190</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="180" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -10803,31 +10839,31 @@
         <v>7</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>1171</v>
+        <v>1165</v>
       </c>
       <c r="D180" s="5"/>
       <c r="E180" s="5"/>
       <c r="F180" s="5"/>
       <c r="G180" s="5" t="s">
-        <v>1191</v>
+        <v>1185</v>
       </c>
       <c r="H180" s="5" t="s">
-        <v>1192</v>
+        <v>1186</v>
       </c>
       <c r="I180" s="5" t="s">
-        <v>1193</v>
+        <v>1187</v>
       </c>
       <c r="J180" s="5" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="K180" s="5" t="s">
-        <v>1195</v>
+        <v>1189</v>
       </c>
       <c r="L180" s="4" t="s">
         <v>25</v>
       </c>
       <c r="M180" s="5" t="s">
-        <v>1196</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="181" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -10838,31 +10874,31 @@
         <v>7</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>1171</v>
+        <v>1165</v>
       </c>
       <c r="D181" s="6"/>
       <c r="E181" s="6"/>
       <c r="F181" s="6"/>
       <c r="G181" s="6" t="s">
-        <v>1197</v>
+        <v>1191</v>
       </c>
       <c r="H181" s="6" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="I181" s="6" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="J181" s="6" t="s">
-        <v>1200</v>
+        <v>1194</v>
       </c>
       <c r="K181" s="6" t="s">
-        <v>1201</v>
+        <v>1195</v>
       </c>
       <c r="L181" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M181" s="6" t="s">
-        <v>1202</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="182" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -10873,33 +10909,33 @@
         <v>7</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>1203</v>
+        <v>1197</v>
       </c>
       <c r="D182" s="5"/>
       <c r="E182" s="5"/>
       <c r="F182" s="5" t="s">
-        <v>1204</v>
+        <v>1198</v>
       </c>
       <c r="G182" s="5" t="s">
-        <v>1205</v>
+        <v>1199</v>
       </c>
       <c r="H182" s="5" t="s">
-        <v>1206</v>
+        <v>1200</v>
       </c>
       <c r="I182" s="5" t="s">
-        <v>1207</v>
+        <v>1201</v>
       </c>
       <c r="J182" s="5" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
       <c r="K182" s="5" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="L182" s="4" t="s">
         <v>52</v>
       </c>
       <c r="M182" s="5" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="183" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -10910,31 +10946,31 @@
         <v>7</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>1203</v>
+        <v>1197</v>
       </c>
       <c r="D183" s="6"/>
       <c r="E183" s="6"/>
       <c r="F183" s="6"/>
       <c r="G183" s="6" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="H183" s="6" t="s">
-        <v>1212</v>
+        <v>1206</v>
       </c>
       <c r="I183" s="6" t="s">
-        <v>1213</v>
+        <v>1207</v>
       </c>
       <c r="J183" s="6" t="s">
-        <v>1214</v>
+        <v>1208</v>
       </c>
       <c r="K183" s="6" t="s">
-        <v>1215</v>
+        <v>1209</v>
       </c>
       <c r="L183" s="2" t="s">
         <v>39</v>
       </c>
       <c r="M183" s="6" t="s">
-        <v>1216</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="184" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -10945,31 +10981,31 @@
         <v>7</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>1203</v>
+        <v>1197</v>
       </c>
       <c r="D184" s="5"/>
       <c r="E184" s="5"/>
       <c r="F184" s="5"/>
       <c r="G184" s="5" t="s">
-        <v>1217</v>
+        <v>1211</v>
       </c>
       <c r="H184" s="5" t="s">
-        <v>1218</v>
+        <v>1212</v>
       </c>
       <c r="I184" s="5" t="s">
-        <v>1219</v>
+        <v>1213</v>
       </c>
       <c r="J184" s="5" t="s">
-        <v>1220</v>
+        <v>1214</v>
       </c>
       <c r="K184" s="5" t="s">
-        <v>1221</v>
+        <v>1215</v>
       </c>
       <c r="L184" s="4" t="s">
         <v>39</v>
       </c>
       <c r="M184" s="5" t="s">
-        <v>1222</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="185" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -10980,31 +11016,31 @@
         <v>7</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>1203</v>
+        <v>1197</v>
       </c>
       <c r="D185" s="6"/>
       <c r="E185" s="6"/>
       <c r="F185" s="6"/>
       <c r="G185" s="6" t="s">
-        <v>1223</v>
+        <v>1217</v>
       </c>
       <c r="H185" s="6" t="s">
-        <v>1224</v>
+        <v>1218</v>
       </c>
       <c r="I185" s="6" t="s">
-        <v>1225</v>
+        <v>1219</v>
       </c>
       <c r="J185" s="6" t="s">
-        <v>1226</v>
+        <v>1220</v>
       </c>
       <c r="K185" s="6" t="s">
-        <v>1227</v>
+        <v>1221</v>
       </c>
       <c r="L185" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M185" s="6" t="s">
-        <v>1228</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="186" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -11015,31 +11051,31 @@
         <v>7</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>1203</v>
+        <v>1197</v>
       </c>
       <c r="D186" s="5"/>
       <c r="E186" s="5"/>
       <c r="F186" s="5"/>
       <c r="G186" s="5" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="H186" s="5" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="I186" s="5" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
       <c r="J186" s="5" t="s">
-        <v>1232</v>
+        <v>1226</v>
       </c>
       <c r="K186" s="5" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="L186" s="4" t="s">
         <v>25</v>
       </c>
       <c r="M186" s="5" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="187" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -11050,33 +11086,33 @@
         <v>7</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="D187" s="6"/>
       <c r="E187" s="6"/>
       <c r="F187" s="6" t="s">
-        <v>1236</v>
+        <v>1230</v>
       </c>
       <c r="G187" s="6" t="s">
-        <v>1237</v>
+        <v>1231</v>
       </c>
       <c r="H187" s="6" t="s">
-        <v>1238</v>
+        <v>1232</v>
       </c>
       <c r="I187" s="6" t="s">
-        <v>1239</v>
+        <v>1233</v>
       </c>
       <c r="J187" s="6" t="s">
-        <v>1240</v>
+        <v>1234</v>
       </c>
       <c r="K187" s="6" t="s">
-        <v>1241</v>
+        <v>1235</v>
       </c>
       <c r="L187" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M187" s="6" t="s">
-        <v>1242</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="188" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -11087,31 +11123,31 @@
         <v>7</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="D188" s="5"/>
       <c r="E188" s="5"/>
       <c r="F188" s="5"/>
       <c r="G188" s="5" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="H188" s="5" t="s">
-        <v>1243</v>
+        <v>1237</v>
       </c>
       <c r="I188" s="5" t="s">
-        <v>1244</v>
+        <v>1238</v>
       </c>
       <c r="J188" s="5" t="s">
-        <v>1245</v>
+        <v>1239</v>
       </c>
       <c r="K188" s="5" t="s">
-        <v>1246</v>
+        <v>1240</v>
       </c>
       <c r="L188" s="4" t="s">
         <v>52</v>
       </c>
       <c r="M188" s="5" t="s">
-        <v>1247</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="189" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -11122,31 +11158,31 @@
         <v>7</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="D189" s="6"/>
       <c r="E189" s="6"/>
       <c r="F189" s="6"/>
       <c r="G189" s="6" t="s">
-        <v>1248</v>
+        <v>1242</v>
       </c>
       <c r="H189" s="6" t="s">
-        <v>1249</v>
+        <v>1243</v>
       </c>
       <c r="I189" s="6" t="s">
-        <v>1250</v>
+        <v>1244</v>
       </c>
       <c r="J189" s="6" t="s">
-        <v>1251</v>
+        <v>1245</v>
       </c>
       <c r="K189" s="6" t="s">
-        <v>1252</v>
+        <v>1246</v>
       </c>
       <c r="L189" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M189" s="6" t="s">
-        <v>1253</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="190" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -11157,31 +11193,31 @@
         <v>7</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="D190" s="5"/>
       <c r="E190" s="5"/>
       <c r="F190" s="5"/>
       <c r="G190" s="5" t="s">
-        <v>1254</v>
+        <v>1248</v>
       </c>
       <c r="H190" s="5" t="s">
-        <v>1255</v>
+        <v>1249</v>
       </c>
       <c r="I190" s="5" t="s">
-        <v>1256</v>
+        <v>1250</v>
       </c>
       <c r="J190" s="5" t="s">
-        <v>1257</v>
+        <v>1251</v>
       </c>
       <c r="K190" s="5" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="L190" s="4" t="s">
         <v>39</v>
       </c>
       <c r="M190" s="5" t="s">
-        <v>1259</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="191" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -11192,31 +11228,31 @@
         <v>7</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="D191" s="6"/>
       <c r="E191" s="6"/>
       <c r="F191" s="6"/>
       <c r="G191" s="6" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
       <c r="H191" s="6" t="s">
-        <v>1261</v>
+        <v>1255</v>
       </c>
       <c r="I191" s="6" t="s">
-        <v>1262</v>
+        <v>1256</v>
       </c>
       <c r="J191" s="6" t="s">
-        <v>1263</v>
+        <v>1257</v>
       </c>
       <c r="K191" s="6" t="s">
-        <v>1264</v>
+        <v>1258</v>
       </c>
       <c r="L191" s="2" t="s">
         <v>52</v>
       </c>
       <c r="M191" s="6" t="s">
-        <v>1265</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="192" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -11227,33 +11263,33 @@
         <v>7</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>1266</v>
+        <v>1260</v>
       </c>
       <c r="D192" s="5"/>
       <c r="E192" s="5"/>
       <c r="F192" s="5" t="s">
-        <v>1267</v>
+        <v>1261</v>
       </c>
       <c r="G192" s="5" t="s">
-        <v>1268</v>
+        <v>1262</v>
       </c>
       <c r="H192" s="5" t="s">
-        <v>1269</v>
+        <v>1263</v>
       </c>
       <c r="I192" s="5" t="s">
-        <v>1270</v>
+        <v>1264</v>
       </c>
       <c r="J192" s="5" t="s">
-        <v>1271</v>
+        <v>1265</v>
       </c>
       <c r="K192" s="5" t="s">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="L192" s="4" t="s">
         <v>39</v>
       </c>
       <c r="M192" s="5" t="s">
-        <v>1273</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="193" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -11264,31 +11300,31 @@
         <v>7</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>1266</v>
+        <v>1260</v>
       </c>
       <c r="D193" s="6"/>
       <c r="E193" s="6"/>
       <c r="F193" s="6"/>
       <c r="G193" s="6" t="s">
-        <v>1274</v>
+        <v>1268</v>
       </c>
       <c r="H193" s="6" t="s">
-        <v>1275</v>
+        <v>1269</v>
       </c>
       <c r="I193" s="6" t="s">
-        <v>1276</v>
+        <v>1270</v>
       </c>
       <c r="J193" s="6" t="s">
-        <v>1277</v>
+        <v>1271</v>
       </c>
       <c r="K193" s="6" t="s">
-        <v>1278</v>
+        <v>1272</v>
       </c>
       <c r="L193" s="2" t="s">
         <v>39</v>
       </c>
       <c r="M193" s="6" t="s">
-        <v>1279</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="194" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -11299,31 +11335,31 @@
         <v>7</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>1266</v>
+        <v>1260</v>
       </c>
       <c r="D194" s="5"/>
       <c r="E194" s="5"/>
       <c r="F194" s="5"/>
       <c r="G194" s="5" t="s">
-        <v>1280</v>
+        <v>1274</v>
       </c>
       <c r="H194" s="5" t="s">
-        <v>1281</v>
+        <v>1275</v>
       </c>
       <c r="I194" s="5" t="s">
-        <v>1282</v>
+        <v>1276</v>
       </c>
       <c r="J194" s="5" t="s">
-        <v>1283</v>
+        <v>1277</v>
       </c>
       <c r="K194" s="5" t="s">
-        <v>1284</v>
+        <v>1278</v>
       </c>
       <c r="L194" s="4" t="s">
         <v>25</v>
       </c>
       <c r="M194" s="5" t="s">
-        <v>1285</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="195" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -11334,31 +11370,31 @@
         <v>7</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>1266</v>
+        <v>1260</v>
       </c>
       <c r="D195" s="6"/>
       <c r="E195" s="6"/>
       <c r="F195" s="6"/>
       <c r="G195" s="6" t="s">
-        <v>1286</v>
+        <v>1280</v>
       </c>
       <c r="H195" s="6" t="s">
-        <v>1287</v>
+        <v>1281</v>
       </c>
       <c r="I195" s="6" t="s">
-        <v>1288</v>
+        <v>1282</v>
       </c>
       <c r="J195" s="6" t="s">
-        <v>1289</v>
+        <v>1283</v>
       </c>
       <c r="K195" s="6" t="s">
-        <v>1290</v>
+        <v>1284</v>
       </c>
       <c r="L195" s="2" t="s">
         <v>52</v>
       </c>
       <c r="M195" s="6" t="s">
-        <v>1291</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="196" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -11369,31 +11405,31 @@
         <v>7</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>1266</v>
+        <v>1260</v>
       </c>
       <c r="D196" s="5"/>
       <c r="E196" s="5"/>
       <c r="F196" s="5"/>
       <c r="G196" s="5" t="s">
-        <v>1292</v>
+        <v>1286</v>
       </c>
       <c r="H196" s="5" t="s">
-        <v>1293</v>
+        <v>1287</v>
       </c>
       <c r="I196" s="5" t="s">
-        <v>1294</v>
+        <v>1288</v>
       </c>
       <c r="J196" s="5" t="s">
-        <v>1295</v>
+        <v>1289</v>
       </c>
       <c r="K196" s="5" t="s">
-        <v>1296</v>
+        <v>1290</v>
       </c>
       <c r="L196" s="4" t="s">
         <v>25</v>
       </c>
       <c r="M196" s="5" t="s">
-        <v>1297</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="197" spans="1:13" ht="270" x14ac:dyDescent="0.25">
@@ -11404,33 +11440,33 @@
         <v>7</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>1298</v>
+        <v>1292</v>
       </c>
       <c r="D197" s="6"/>
       <c r="E197" s="6"/>
       <c r="F197" s="6" t="s">
-        <v>1299</v>
+        <v>1293</v>
       </c>
       <c r="G197" s="6" t="s">
-        <v>1300</v>
+        <v>1294</v>
       </c>
       <c r="H197" s="6" t="s">
-        <v>1301</v>
+        <v>1295</v>
       </c>
       <c r="I197" s="6" t="s">
-        <v>1302</v>
+        <v>1296</v>
       </c>
       <c r="J197" s="6" t="s">
-        <v>1303</v>
+        <v>1297</v>
       </c>
       <c r="K197" s="6" t="s">
-        <v>1304</v>
+        <v>1298</v>
       </c>
       <c r="L197" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M197" s="6" t="s">
-        <v>1305</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="198" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -11441,31 +11477,31 @@
         <v>7</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>1298</v>
+        <v>1292</v>
       </c>
       <c r="D198" s="5"/>
       <c r="E198" s="5"/>
       <c r="F198" s="5"/>
       <c r="G198" s="5" t="s">
-        <v>1306</v>
+        <v>1300</v>
       </c>
       <c r="H198" s="5" t="s">
-        <v>1307</v>
+        <v>1301</v>
       </c>
       <c r="I198" s="5" t="s">
-        <v>1308</v>
+        <v>1302</v>
       </c>
       <c r="J198" s="5" t="s">
-        <v>1309</v>
+        <v>1303</v>
       </c>
       <c r="K198" s="5" t="s">
-        <v>1310</v>
+        <v>1304</v>
       </c>
       <c r="L198" s="4" t="s">
         <v>52</v>
       </c>
       <c r="M198" s="5" t="s">
-        <v>1311</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="199" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -11476,31 +11512,31 @@
         <v>7</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>1298</v>
+        <v>1292</v>
       </c>
       <c r="D199" s="6"/>
       <c r="E199" s="6"/>
       <c r="F199" s="6"/>
       <c r="G199" s="6" t="s">
-        <v>1312</v>
+        <v>1306</v>
       </c>
       <c r="H199" s="6" t="s">
-        <v>1313</v>
+        <v>1307</v>
       </c>
       <c r="I199" s="6" t="s">
-        <v>1314</v>
+        <v>1308</v>
       </c>
       <c r="J199" s="6" t="s">
-        <v>1315</v>
+        <v>1309</v>
       </c>
       <c r="K199" s="6" t="s">
-        <v>1316</v>
+        <v>1310</v>
       </c>
       <c r="L199" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M199" s="6" t="s">
-        <v>1317</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="200" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -11511,31 +11547,31 @@
         <v>7</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>1298</v>
+        <v>1292</v>
       </c>
       <c r="D200" s="5"/>
       <c r="E200" s="5"/>
       <c r="F200" s="5"/>
       <c r="G200" s="5" t="s">
-        <v>1318</v>
+        <v>1312</v>
       </c>
       <c r="H200" s="5" t="s">
-        <v>1319</v>
+        <v>1313</v>
       </c>
       <c r="I200" s="5" t="s">
-        <v>1320</v>
+        <v>1314</v>
       </c>
       <c r="J200" s="5" t="s">
-        <v>1321</v>
+        <v>1315</v>
       </c>
       <c r="K200" s="5" t="s">
-        <v>1322</v>
+        <v>1316</v>
       </c>
       <c r="L200" s="4" t="s">
         <v>39</v>
       </c>
       <c r="M200" s="5" t="s">
-        <v>1323</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="201" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -11546,34 +11582,47 @@
         <v>7</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>1298</v>
+        <v>1292</v>
       </c>
       <c r="D201" s="6"/>
       <c r="E201" s="6"/>
       <c r="F201" s="6"/>
       <c r="G201" s="6" t="s">
-        <v>1324</v>
+        <v>1318</v>
       </c>
       <c r="H201" s="6" t="s">
-        <v>1325</v>
+        <v>1319</v>
       </c>
       <c r="I201" s="6" t="s">
-        <v>1326</v>
+        <v>1320</v>
       </c>
       <c r="J201" s="6" t="s">
-        <v>1327</v>
+        <v>1321</v>
       </c>
       <c r="K201" s="6" t="s">
-        <v>1328</v>
+        <v>1322</v>
       </c>
       <c r="L201" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M201" s="6" t="s">
-        <v>1329</v>
+        <v>1323</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E64" r:id="rId7"/>
+    <hyperlink ref="E67" r:id="rId8"/>
+    <hyperlink ref="E97" r:id="rId9"/>
+    <hyperlink ref="E100" r:id="rId10"/>
+    <hyperlink ref="E132" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ETS2023_Test1_Final_Architecture.xlsx
+++ b/ETS2023_Test1_Final_Architecture.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28035" windowHeight="11730" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28035" windowHeight="11730"/>
   </bookViews>
   <sheets>
     <sheet name="Test_Info" sheetId="1" r:id="rId1"/>
@@ -2728,9 +2728,6 @@
     <t>P6_02</t>
   </si>
   <si>
-    <t>Gasgo Propane Tank Exchange&lt;br&gt;&lt;br&gt;You have chosen a safe and _______(135) way to obtain fuel for your stoves, grills, heaters, fireplaces, or other devices. Simply follow the directions _______(136).&lt;br&gt;&lt;br&gt;When your tank runs out of propane, take it to our store and leave it on one of the clearly marked green shelves outside the store. _______(137). Then, pay the cashier inside the store for a fresh tank of propane. Next, the cashier or another staff member will accompany you to the outdoor exchange area. The staff person will give you a full tank to take home and provide help if you have multiple tanks to carry. Follow the instructions on the tank to connect it to your device.&lt;br&gt;&lt;br&gt;Be sure to visit us again when you need a _______(138).</t>
-  </si>
-  <si>
     <t>You have chosen a safe and _______ way to obtain fuel...</t>
   </si>
   <si>
@@ -2803,9 +2800,6 @@
     <t>P6_03</t>
   </si>
   <si>
-    <t>To: Technicarn Enterprises Customers&lt;br&gt;From: Technicarn Enterprises Customer Service&lt;br&gt;Date: 10 September&lt;br&gt;Subject: Serving You&lt;br&gt;&lt;br&gt;Dear Valued Customer:&lt;br&gt;We want your _______(139) with Technicarn Enterprises to be easy and enjoyable. To that end, we are pleased to announce our newly designed Web site, with enhanced customer-friendly features.&lt;br&gt;&lt;br&gt;Our new Web site provides answers to your questions 24 hours a day, every day of the year. On our home page, you can get information about system setup, or you can troubleshoot by visiting _______(140) the Internet Issues or TV and Streaming Issues pages. _______(141), you can find detailed information concerning account management, access, billing, and payment.&lt;br&gt;&lt;br&gt;Please explore the new Web site at your earliest convenience: www.technicarnenterprises.com. _______(142). As always, thank you for allowing us to serve you.</t>
-  </si>
-  <si>
     <t>We want your _______ with Technicarn Enterprises to be easy and enjoyable.</t>
   </si>
   <si>
@@ -2878,9 +2872,6 @@
     <t>P6_04</t>
   </si>
   <si>
-    <t>Garner City Transport Cares About the Environment&lt;br&gt;&lt;br&gt;Beginning May 1, the sale and use of paper tickets and transit passes will be _______(143) on all Garner City Transport bus and subway lines. This change applies to single-ride tickets _______(144) to weekly and monthly passes. Eliminating paper benefits the environment and leads to less litter.&lt;br&gt;&lt;br&gt;Riders can download the free Garner City Transport app. With the app, they can add money their accounts, purchase tickets, plan _______(145), and track arrival and departure times.&lt;br&gt;&lt;br&gt;Alternatively, passengers can purchase a rechargeable transit card at any station. Value can be added to the card via the Garner City Transport Web site at www.garnercitytransport.org. _______(146).</t>
-  </si>
-  <si>
     <t>Beginning May 1, the sale and use of paper tickets and transit passes will be _______ on all Garner City Transport bus and subway lines.</t>
   </si>
   <si>
@@ -2953,9 +2944,6 @@
     <t>P7_01</t>
   </si>
   <si>
-    <t>Harbis Stationery Store Clearance Sale&lt;br&gt;Prices indicated are for in-store purchases only.&lt;br&gt;500 Pinstone Street / SHEFFIELD / S12HN&lt;br&gt;&lt;br&gt;Seasonal items&lt;br&gt;- Box of ten preprinted seasonal cards (25% off): £ 8.99&lt;br&gt;- Box of five customizable seasonal cards or invitations (50% off): £ 11.99&lt;br&gt;&lt;br&gt;All school supplies 10% off&lt;br&gt;- Box of 24 pens: £ 1.79&lt;br&gt;- Desk lamp: £ 19.99&lt;br&gt;- Wireless mouse: £ 17.99&lt;br&gt;- Backpack: £ 29.99&lt;br&gt;&lt;br&gt;Visit Harbis Stationery at www.harbisstationery.uk</t>
-  </si>
-  <si>
     <t>What is indicated about Harbis Stationery Store?</t>
   </si>
   <si>
@@ -2995,9 +2983,6 @@
     <t>P7_02</t>
   </si>
   <si>
-    <t>To: Wenbin Peng &lt;wpeng@chenconstruction.com&gt;&lt;br&gt;From: Toshi Auto Group &lt;cs@toshiautogroup.com&gt;&lt;br&gt;Date: February 26&lt;br&gt;Subject: Your leased vehicle&lt;br&gt;&lt;br&gt;Dear Mr. Peng:&lt;br&gt;As you know, Toshi Auto Group handles all the service needs for cars leased by employees of Chen Construction. According to our records, you took possession of your leased car on March 1 of last year. Your car is now due for its required annual service and maintenance check. To book your appointment, please call us at (215) 555-0109 or visit us online at www.toshiautogroup.com/serviceappointments.&lt;br&gt;&lt;br&gt;Sincerely,&lt;br&gt;Toshi Auto Group Customer Service</t>
-  </si>
-  <si>
     <t>What is the purpose of the e-mail?</t>
   </si>
   <si>
@@ -3037,9 +3022,6 @@
     <t>P7_03</t>
   </si>
   <si>
-    <t>LONDON (2 February)-On Thursday, Tillford Press announced the launch of its new imprint, Tillford Exalt. This new line will feature books promoting healthy lifestyles, memoirs with uplifting messages, and volumes that provide guidance for special occasions such as birthdays and weddings...&lt;br&gt;Already contracted to write memoirs are the award-winning actress Alexia Leoz, London-based conductor and composer Seung-Hyun Bae, and celebrity cook Lain Lai. Ms. Lai's story of her life and career will be the first to be launched. It is set for release in December.&lt;br&gt;...Tillford Press is based in Manchester. It has offices in New York, Toronto, and Sydney, but its publications are sold throughout the world.</t>
-  </si>
-  <si>
     <t>What is the main purpose of the article?</t>
   </si>
   <si>
@@ -3094,9 +3076,6 @@
     <t>P7_04</t>
   </si>
   <si>
-    <t>Greg Skagen (8:58 A.M.) Hi, Brenda. I'm here in the warehouse. All of my trainees have arrived, but I noticed the power door at Loading Dock B is acting up.&lt;br&gt;Brenda Sadauskas (8:59 A.M.) Again?&lt;br&gt;Greg Skagen (8:59 A.M.) When I push the button to open it, it raises all the way up but then drops back down to the closed position after about 30 seconds.&lt;br&gt;Brenda Sadauskas (9:00 A.M.) I'll come down with the maintenance technicians. Why don't you bring your trainees to my area? You can teach them how to create shipping labels and then have them pack and label this morning's shipments.&lt;br&gt;Greg Skagen (9:02 A.M.) Yes, that works.&lt;br&gt;Brenda Sadauskas (9:03 A.M.) Thanks. Then you could show them the loading dock operations in the afternoon.</t>
-  </si>
-  <si>
     <t>What problem does Mr. Skagen mention?</t>
   </si>
   <si>
@@ -3136,9 +3115,6 @@
     <t>P7_05</t>
   </si>
   <si>
-    <t>SERVICE REQUEST FORM&lt;br&gt;Requester Name: Elenora Deckow&lt;br&gt;Requester Office: Room 718&lt;br&gt;Service Location: Room 500&lt;br&gt;Service Type: Repair&lt;br&gt;Description of Request:&lt;br&gt;There is a problem with the television audio. When I played an online video, the image was fine, but I could not hear anything. I checked all the settings, and I was able to hear the same video on other televisions with no problem. I'm supposed to deliver a product demonstration for a client in room 500 next Monday, so I would greatly appreciate it if the issue can be fixed by this Friday.</t>
-  </si>
-  <si>
     <t>Why was the form submitted?</t>
   </si>
   <si>
@@ -3178,9 +3154,6 @@
     <t>P7_06</t>
   </si>
   <si>
-    <t>Ella Glatt (11:34 A.M.) Hi. I know this is a busy day, but I wanted to know whether anyone from the finance team could come to the marketing meeting.&lt;br&gt;Stef Goldberg (11:35 A.M.) Hi, Ella. I wish I could, but it starts at 2:00. I need to be at a different meeting at 2:30.&lt;br&gt;Ella Glatt (11:36 A.M.) Oh, right. I forgot you were going to the executive board meeting.&lt;br&gt;Daniel Seidal (11:36 A.M.) I'm also supposed to go to the 2:30 meeting. Is it essential that one of us attend the marketing meeting?&lt;br&gt;Ella Glatt (11:37 A.M.) Well, it would be helpful to have someone from the finance department there, at least for 15 minutes or so.&lt;br&gt;Bill Iverman (11:38 A.M.) The quarterly reports just came in, and Daniel, Stef, and I need to review them by the end of the day.&lt;br&gt;Daniel Seidal (11:41 A.M.) That's true! But I could come from 2:00 to 2:15. That's all I can commit to.&lt;br&gt;Ella Glatt (11:43 A.M.) Sounds great. We just need one of you to clarify a few quick points about the budget for the next advertising campaign.</t>
-  </si>
-  <si>
     <t>At what time will the executive board meeting begin?</t>
   </si>
   <si>
@@ -3256,9 +3229,6 @@
     <t>P7_07</t>
   </si>
   <si>
-    <t>To: amal.abboud@bunzifoundation.org&lt;br&gt;From: maria_mcfarland@myemail.com&lt;br&gt;Date: Thursday, August 22&lt;br&gt;Subject: Project Coordinator Position&lt;br&gt;Attachment: résumé_m.mcfarland.pdf&lt;br&gt;&lt;br&gt;Dear Mr. Abboud,&lt;br&gt;My friend Josiah Wilkins told me that you are seeking a project coordinator for your company. I have a degree in business administration and am attaching my résumé as I think I am an excellent fit for your needs. As you will see, I have experience using several cloud-based project-management programs.&lt;br&gt;&lt;br&gt;My current role as project coordinator for an international engineering firm... has afforded me ample experience managing teams, schedules, and budgets. While I enjoy the kind of work I do, it has become clear to me that I need motivation from a strong mission. The goal of your company to create sustainable housing projects is something that I strongly support and would be delighted to work on.&lt;br&gt;&lt;br&gt;Through my work and volunteer activities, I have spent many months abroad in various countries throughout Asia and the Middle East. This seems particularly relevant to mention, as I am comfortable leading geographically and culturally diverse teams.</t>
-  </si>
-  <si>
     <t>What does Ms. McFarland mention about Mr. Wilkins?</t>
   </si>
   <si>
@@ -3334,9 +3304,6 @@
     <t>P7_08</t>
   </si>
   <si>
-    <t>About Our Company&lt;br&gt;Trexdale Supply specializes in designing, producing, and installing furniture for all types of scientific laboratories. We provide a range of fully assembled cabinets, workstations, benches, and more... Our lab furniture is available in a wide variety of sizes.&lt;br&gt;&lt;br&gt;Our business offers products as well as design-consulting services. For start-up labs, we have a team of consulting specialists available to evaluate your facility's specific needs and assist you in arranging your space... Recently, for example, we were chosen by a major producer of biofuels to provide expert help in changing the layout of a research laboratory to maximize available space.&lt;br&gt;&lt;br&gt;Please visit the "Lab Planning" section of this Web site if you are interested in learning more... There, you can fill out an interest form to contact one of our consultants.</t>
-  </si>
-  <si>
     <t>What does Trexdale Supply make?</t>
   </si>
   <si>
@@ -3394,9 +3361,6 @@
     <t>P7_09</t>
   </si>
   <si>
-    <t>PRODUCT DEMONSTRATORS NEEDED!&lt;br&gt;Are you outgoing and enthusiastic?- [1]. Do you enjoy talking to all types of people? Put your personality and communication skills to work! - [2] -. BBD Staffing is seeking to hire in-store product demonstrators to promote our clients' merchandise to shoppers. - [3]. As a member of our team, you will demonstrate a wide range of small kitchen appliances and tools in grocery stores and other retail venues.&lt;br&gt;&lt;br&gt;For some products, you will be required to prepare simple recipes. You will also need to answer shoppers' questions. Thus, it is essential that you can become familiar with clients' products and provide key information to consumers. Because many of the demonstrations require working with food, candidates must have a Professional Food Handler certificate. - [4] -.&lt;br&gt;&lt;br&gt;To apply, upload a video of no more than one minute in length telling us why you would be a successful product demonstrator at www.bbdstaffing.com/applications.</t>
-  </si>
-  <si>
     <t>What work experience would best qualify a candidate for the position?</t>
   </si>
   <si>
@@ -3454,9 +3418,6 @@
     <t>P7_10</t>
   </si>
   <si>
-    <t>Gorman Unveils Newest Smartphone Model&lt;br&gt;&lt;br&gt;LONDON (20 April)-Gorman Mobile unveiled its newest smartphone to an eager reception at the annual Technobrit Conference. The Pro Phone 4, which includes 512 GB of storage, a 7-inch screen display, and an optional stylus pen, will hit the shelves on 11 June. Unlike its predecessor the Pro Phone 3-it features a larger screen, an ultrawide camera lens, and 8K-resolution filming capability.&lt;br&gt;&lt;br&gt;[1]. The £999 starting price is £100 more than that of the previous model. Add-ons, such as the stylus pen, protective case, and wireless headphones, cost an additional £39, £59, and £79, respectively. Gorman Product Manager Ian Hill doesn't believe the price increase will dissuade customers.&lt;br&gt;&lt;br&gt;[2] - "The Pro Phone 4 is a game changer in terms of its picture quality and sleek design." said Hill. "Improvements were based on direct customer feedback..."&lt;br&gt;&lt;br&gt;[3] -. One similarity that the Pro Phone 4 has with previous models is the charger...&lt;br&gt;&lt;br&gt;"We want to afford our customers the ability to reuse elements of the other Gorman devices they've already purchased," said Hill. "Why add to the overload of cables already in circulation?" - [4]-</t>
-  </si>
-  <si>
     <t>What is the purpose of the article?</t>
   </si>
   <si>
@@ -3520,9 +3481,6 @@
     <t>P7_11</t>
   </si>
   <si>
-    <t>WORK ORDER: 7549&lt;br&gt;Requester: Xi, Gina&lt;br&gt;Date Entered: Wednesday, 9 April&lt;br&gt;Type: Technology end-user request&lt;br&gt;Technician Assigned: Arnold, Sam&lt;br&gt;Description: Is it possible to remove the new layers of security on my voice mail in the new phone system? I really don't want to use a password, and I certainly don't want to change it every month. I don't need a high degree of security because my work is not confidential. If someone else gained access to my messages, it wouldn't do much harm.&lt;br&gt;&lt;br&gt;E-mail&lt;br&gt;To: Gina Xi&lt;br&gt;From: Sam Arnold&lt;br&gt;Subject: Tech support request 7549&lt;br&gt;Hello, Ms. Xi. This is in reference to your work order 7549 related to the new phone system... I understand that you do not feel that a high degree of security is needed for your voice-mail settings, but the new system does require you to have a password to retrieve your voice mail. However, company policy allows me to change the settings for employees who do not work with confidential material. I can update the security settings so that you do not have to reset the password on a regular basis... If you still feel comfortable with that level of risk, let me know, and I will change the settings so that your password never expires.</t>
-  </si>
-  <si>
     <t>What does Ms. Xi's request indicate about the company?</t>
   </si>
   <si>
@@ -3616,9 +3574,6 @@
     <t>P7_12</t>
   </si>
   <si>
-    <t>E-mail&lt;br&gt;To: Linda Hanshu&lt;br&gt;From: Cliff Merson&lt;br&gt;Subject: Lighting Issue&lt;br&gt;I want to check on the issue we discussed about lighting in the latest chapter of Titan Adventure. In past versions of the game, getting the reflections and lighting in green and blue areas correct has been a particular challenge... As the new release, Neptune's Voyage, is primarily an underwater adventure, addressing this problem is crucial. You said you would take charge of this, and I hope to hear that you have found a solution... The team was hoping to have one last rendering of the lighting for the game by October 10...&lt;br&gt;&lt;br&gt;Review of Titan Adventure: Neptune's Voyage&lt;br&gt;By Leo Weber, April 1&lt;br&gt;This new installment of Titan Adventure will surprise and delight both new players and old aficionados... This newest version also corrects the green and blue image rendering that was sometimes a problem in earlier installments of Titan Adventure. Neptune's Voyage launches May 5 on Rimerko Clutch and FS5. It is available in English, Korean, Japanese, French, and Spanish.</t>
-  </si>
-  <si>
     <t>In the e-mail, what is suggested about Mr. Merson?</t>
   </si>
   <si>
@@ -3712,9 +3667,6 @@
     <t>P7_13</t>
   </si>
   <si>
-    <t>Wonder Ridge Radio Broadcast Schedule&lt;br&gt;Noon-4 P.M. AFTERNOON JAZZ. Music from traditional jazz to jazz fusion. Host: Malachi Mzee&lt;br&gt;4 P.M.-7 P.M. FOLK FRENZY. Folk music from around the world. Host: Penny Ariza&lt;br&gt;7 P.M.-10 P.M. JOSIE'S JOINT. Modern sounds selected by our station's own music director. Host: Josie Jones&lt;br&gt;&lt;br&gt;E-mail: To the folks at Wonder Ridge Radio:&lt;br&gt;As I was driving last week... Suddenly, my car was filled with a song that I hadn't heard in many years. It was traditional music from France, where my grandmother was born... I never expected to hear it on the radio here in Wonder Ridge. Thanks for this experience... Pierre Fabre&lt;br&gt;&lt;br&gt;Job Opening: Programming Assistant&lt;br&gt;Responsibilities: Conducting background research on interviewees. Keeping up-to-date on news... Updating the station's Web site and program host biography pages. Using scheduling software to update the broadcast schedule...</t>
-  </si>
-  <si>
     <t>According to the schedule, who is Ms. Jones?</t>
   </si>
   <si>
@@ -3805,9 +3757,6 @@
     <t>P7_14</t>
   </si>
   <si>
-    <t>Instructions for Requesting Records&lt;br&gt;1. Create an account in the Records Center Web portal. Currently, all requests must be made through the portal.&lt;br&gt;2. Use the drop-down menu to locate the department from which you are seeking information and submit your request. You will receive a confirmation e-mail with a reference number.&lt;br&gt;3. The department staff will locate the requested records and contact you when they are available... If you prefer to pick them up in person, you must make an appointment with the department staff.&lt;br&gt;&lt;br&gt;E-Mail Message&lt;br&gt;To: Joo-Hee Park &lt;jhpark@coa.net&gt;&lt;br&gt;From: Keith Brandenberg &lt;kbrandenberg@mailcurrent.com&gt;&lt;br&gt;Dear Ms. Park... I have a question about the fee. Apparently, I am being charged $300 for my documents. I do not understand why the fee is so high... I am only requesting two maps of the city's underground pipelines, which will inform our firm's current work advising the city on wastewater management.&lt;br&gt;&lt;br&gt;Sign: City of Abilene Administrative Building&lt;br&gt;First-Floor Directory:&lt;br&gt;IT Services - Room 100&lt;br&gt;Parks and Recreation - Room 101&lt;br&gt;Transportation - Room 102&lt;br&gt;Wastewater - Room 103</t>
-  </si>
-  <si>
     <t>What do the instructions indicate about records requests?</t>
   </si>
   <si>
@@ -3901,9 +3850,6 @@
     <t>P7_15</t>
   </si>
   <si>
-    <t>Review: Famous Actor, First Book&lt;br&gt;Fans of Simon Eklund will be delighted with his autobiography, The Theatre Lights Dimmed, the first book he has written in his storied career as an actor. It provides wonderful insight into his career, starting with his first roles in cinema in his native Sweden, moving into his work in France and Italy, and finishing with his recent theatre work in the U.K... -Uma Joshi&lt;br&gt;&lt;br&gt;E-mail 1&lt;br&gt;To: Edith Hocking | From: Uma Joshi | Date: 2 March&lt;br&gt;Thank you for agreeing to arrange an interview with Mr. Eklund for me. I think this will be a great follow-up to my recent piece. In a helpful coincidence, I will be visiting his home country next month to address a journalists' convention. I am the featured speaker and will discuss the benefits of diversity in journalism.&lt;br&gt;&lt;br&gt;E-mail 2&lt;br&gt;To: Uma Joshi | From: Maria Cazalla&lt;br&gt;We are all very excited about your interview next month with Mr. Eklund. He enjoys all your writing for Top News U.K.-the news stories, interviews, and, of course, your recent article about The Theatre Lights Dimmed! I just wanted to finalize a few details with you. We have arranged transportation for you from your hotel to Mr. Eklund's house and then back to the hotel. Please let me know how many people there will be in your group, because Mr. Eklund would like you all to stay for lunch.</t>
-  </si>
-  <si>
     <t>What does the review mention about Mr. Eklund?</t>
   </si>
   <si>
@@ -3994,9 +3940,6 @@
     <t>Giải thích: Maria viết trong email thứ 2 rằng: Ông Eklund thích tất cả bài viết của bà, và tất nhiên là CẢ bài báo/review gần đây về cuốn tự truyện của ông ấy ('your recent article about The Theatre Lights Dimmed!') -&gt; Ông ấy hài lòng với bài review của Joshi.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/bangvang1105-tech/Audio/main/ETS2023_Test1_Full.mp3</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/main/p1_01.png</t>
   </si>
   <si>
@@ -4031,6 +3974,63 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p6_131.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p6_135.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p6_139.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p6_143.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_147.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_149.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_151.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_154.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_156.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_158.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_162.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_166.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_169.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_172.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_176(1).png | https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_176(2).png </t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_181(1).png | https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_181(2).png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_186(1).png | https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_186(2).png | https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_186(3).png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_191(1).png | https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_191(2).png | https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_191(3).png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_196(1).png | https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_196(2).png | https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_196(3).png</t>
+  </si>
+  <si>
+    <t>https://github.com/bangvang1105-tech/Audio-Test-1-ETS-2023/raw/refs/heads/main/Test%201%20ETS%202023.mp3</t>
   </si>
 </sst>
 </file>
@@ -4492,7 +4492,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>1324</v>
+        <v>1336</v>
       </c>
       <c r="D2" s="2">
         <v>120</v>
@@ -4577,7 +4577,7 @@
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="8" t="s">
-        <v>1325</v>
+        <v>1306</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="9" t="s">
-        <v>1326</v>
+        <v>1307</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="8" t="s">
-        <v>1327</v>
+        <v>1308</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="9" t="s">
-        <v>1328</v>
+        <v>1309</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="8" t="s">
-        <v>1329</v>
+        <v>1310</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="9" t="s">
-        <v>1330</v>
+        <v>1311</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="D64" s="5"/>
       <c r="E64" s="8" t="s">
-        <v>1331</v>
+        <v>1312</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="5" t="s">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="D67" s="6"/>
       <c r="E67" s="9" t="s">
-        <v>1332</v>
+        <v>1313</v>
       </c>
       <c r="F67" s="6"/>
       <c r="G67" s="6" t="s">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="D70" s="5"/>
       <c r="E70" s="8" t="s">
-        <v>1333</v>
+        <v>1314</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="5" t="s">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="D97" s="6"/>
       <c r="E97" s="9" t="s">
-        <v>1334</v>
+        <v>1315</v>
       </c>
       <c r="F97" s="6"/>
       <c r="G97" s="6" t="s">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="D100" s="5"/>
       <c r="E100" s="8" t="s">
-        <v>1335</v>
+        <v>1316</v>
       </c>
       <c r="F100" s="5"/>
       <c r="G100" s="5" t="s">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="D132" s="5"/>
       <c r="E132" s="8" t="s">
-        <v>1336</v>
+        <v>1317</v>
       </c>
       <c r="F132" s="5"/>
       <c r="G132" s="5" t="s">
@@ -9263,7 +9263,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="136" spans="1:13" ht="150" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A136" s="4">
         <v>135</v>
       </c>
@@ -9274,30 +9274,30 @@
         <v>901</v>
       </c>
       <c r="D136" s="5"/>
-      <c r="E136" s="5"/>
-      <c r="F136" s="5" t="s">
+      <c r="E136" s="8" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F136" s="5"/>
+      <c r="G136" s="5" t="s">
         <v>902</v>
       </c>
-      <c r="G136" s="5" t="s">
+      <c r="H136" s="5" t="s">
         <v>903</v>
       </c>
-      <c r="H136" s="5" t="s">
+      <c r="I136" s="5" t="s">
         <v>904</v>
       </c>
-      <c r="I136" s="5" t="s">
+      <c r="J136" s="5" t="s">
         <v>905</v>
       </c>
-      <c r="J136" s="5" t="s">
+      <c r="K136" s="5" t="s">
         <v>906</v>
-      </c>
-      <c r="K136" s="5" t="s">
-        <v>907</v>
       </c>
       <c r="L136" s="4" t="s">
         <v>25</v>
       </c>
       <c r="M136" s="5" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.25">
@@ -9314,25 +9314,25 @@
       <c r="E137" s="6"/>
       <c r="F137" s="6"/>
       <c r="G137" s="6" t="s">
+        <v>908</v>
+      </c>
+      <c r="H137" s="6" t="s">
         <v>909</v>
       </c>
-      <c r="H137" s="6" t="s">
+      <c r="I137" s="6" t="s">
         <v>910</v>
       </c>
-      <c r="I137" s="6" t="s">
+      <c r="J137" s="6" t="s">
         <v>911</v>
       </c>
-      <c r="J137" s="6" t="s">
+      <c r="K137" s="6" t="s">
         <v>912</v>
-      </c>
-      <c r="K137" s="6" t="s">
-        <v>913</v>
       </c>
       <c r="L137" s="2" t="s">
         <v>52</v>
       </c>
       <c r="M137" s="6" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="138" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -9352,22 +9352,22 @@
         <v>883</v>
       </c>
       <c r="H138" s="5" t="s">
+        <v>914</v>
+      </c>
+      <c r="I138" s="5" t="s">
         <v>915</v>
       </c>
-      <c r="I138" s="5" t="s">
+      <c r="J138" s="5" t="s">
         <v>916</v>
       </c>
-      <c r="J138" s="5" t="s">
+      <c r="K138" s="5" t="s">
         <v>917</v>
-      </c>
-      <c r="K138" s="5" t="s">
-        <v>918</v>
       </c>
       <c r="L138" s="4" t="s">
         <v>32</v>
       </c>
       <c r="M138" s="5" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="139" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -9384,28 +9384,28 @@
       <c r="E139" s="6"/>
       <c r="F139" s="6"/>
       <c r="G139" s="6" t="s">
+        <v>919</v>
+      </c>
+      <c r="H139" s="6" t="s">
         <v>920</v>
       </c>
-      <c r="H139" s="6" t="s">
+      <c r="I139" s="6" t="s">
         <v>921</v>
       </c>
-      <c r="I139" s="6" t="s">
+      <c r="J139" s="6" t="s">
         <v>922</v>
       </c>
-      <c r="J139" s="6" t="s">
+      <c r="K139" s="6" t="s">
         <v>923</v>
-      </c>
-      <c r="K139" s="6" t="s">
-        <v>924</v>
       </c>
       <c r="L139" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M139" s="6" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="140" spans="1:13" ht="180" x14ac:dyDescent="0.25">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A140" s="4">
         <v>139</v>
       </c>
@@ -9413,33 +9413,33 @@
         <v>6</v>
       </c>
       <c r="C140" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="D140" s="5"/>
+      <c r="E140" s="8" t="s">
+        <v>1319</v>
+      </c>
+      <c r="F140" s="5"/>
+      <c r="G140" s="5" t="s">
         <v>926</v>
       </c>
-      <c r="D140" s="5"/>
-      <c r="E140" s="5"/>
-      <c r="F140" s="5" t="s">
+      <c r="H140" s="5" t="s">
         <v>927</v>
       </c>
-      <c r="G140" s="5" t="s">
+      <c r="I140" s="5" t="s">
         <v>928</v>
       </c>
-      <c r="H140" s="5" t="s">
+      <c r="J140" s="5" t="s">
         <v>929</v>
       </c>
-      <c r="I140" s="5" t="s">
+      <c r="K140" s="5" t="s">
         <v>930</v>
-      </c>
-      <c r="J140" s="5" t="s">
-        <v>931</v>
-      </c>
-      <c r="K140" s="5" t="s">
-        <v>932</v>
       </c>
       <c r="L140" s="4" t="s">
         <v>52</v>
       </c>
       <c r="M140" s="5" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="141" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -9450,31 +9450,31 @@
         <v>6</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D141" s="6"/>
       <c r="E141" s="6"/>
       <c r="F141" s="6"/>
       <c r="G141" s="6" t="s">
+        <v>932</v>
+      </c>
+      <c r="H141" s="6" t="s">
+        <v>933</v>
+      </c>
+      <c r="I141" s="6" t="s">
         <v>934</v>
       </c>
-      <c r="H141" s="6" t="s">
+      <c r="J141" s="6" t="s">
         <v>935</v>
       </c>
-      <c r="I141" s="6" t="s">
+      <c r="K141" s="6" t="s">
         <v>936</v>
-      </c>
-      <c r="J141" s="6" t="s">
-        <v>937</v>
-      </c>
-      <c r="K141" s="6" t="s">
-        <v>938</v>
       </c>
       <c r="L141" s="2" t="s">
         <v>52</v>
       </c>
       <c r="M141" s="6" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
     </row>
     <row r="142" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -9485,31 +9485,31 @@
         <v>6</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D142" s="5"/>
       <c r="E142" s="5"/>
       <c r="F142" s="5"/>
       <c r="G142" s="5" t="s">
+        <v>938</v>
+      </c>
+      <c r="H142" s="5" t="s">
+        <v>939</v>
+      </c>
+      <c r="I142" s="5" t="s">
         <v>940</v>
       </c>
-      <c r="H142" s="5" t="s">
+      <c r="J142" s="5" t="s">
         <v>941</v>
       </c>
-      <c r="I142" s="5" t="s">
+      <c r="K142" s="5" t="s">
         <v>942</v>
-      </c>
-      <c r="J142" s="5" t="s">
-        <v>943</v>
-      </c>
-      <c r="K142" s="5" t="s">
-        <v>944</v>
       </c>
       <c r="L142" s="4" t="s">
         <v>25</v>
       </c>
       <c r="M142" s="5" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
     </row>
     <row r="143" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -9520,7 +9520,7 @@
         <v>6</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D143" s="6"/>
       <c r="E143" s="6"/>
@@ -9529,25 +9529,25 @@
         <v>883</v>
       </c>
       <c r="H143" s="6" t="s">
+        <v>944</v>
+      </c>
+      <c r="I143" s="6" t="s">
+        <v>945</v>
+      </c>
+      <c r="J143" s="6" t="s">
         <v>946</v>
       </c>
-      <c r="I143" s="6" t="s">
+      <c r="K143" s="6" t="s">
         <v>947</v>
-      </c>
-      <c r="J143" s="6" t="s">
-        <v>948</v>
-      </c>
-      <c r="K143" s="6" t="s">
-        <v>949</v>
       </c>
       <c r="L143" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M143" s="6" t="s">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="144" spans="1:13" ht="150" x14ac:dyDescent="0.25">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A144" s="4">
         <v>143</v>
       </c>
@@ -9555,33 +9555,33 @@
         <v>6</v>
       </c>
       <c r="C144" s="4" t="s">
+        <v>949</v>
+      </c>
+      <c r="D144" s="5"/>
+      <c r="E144" s="8" t="s">
+        <v>1320</v>
+      </c>
+      <c r="F144" s="5"/>
+      <c r="G144" s="5" t="s">
+        <v>950</v>
+      </c>
+      <c r="H144" s="5" t="s">
         <v>951</v>
       </c>
-      <c r="D144" s="5"/>
-      <c r="E144" s="5"/>
-      <c r="F144" s="5" t="s">
+      <c r="I144" s="5" t="s">
         <v>952</v>
       </c>
-      <c r="G144" s="5" t="s">
+      <c r="J144" s="5" t="s">
         <v>953</v>
       </c>
-      <c r="H144" s="5" t="s">
+      <c r="K144" s="5" t="s">
         <v>954</v>
-      </c>
-      <c r="I144" s="5" t="s">
-        <v>955</v>
-      </c>
-      <c r="J144" s="5" t="s">
-        <v>956</v>
-      </c>
-      <c r="K144" s="5" t="s">
-        <v>957</v>
       </c>
       <c r="L144" s="4" t="s">
         <v>39</v>
       </c>
       <c r="M144" s="5" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
     </row>
     <row r="145" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -9592,31 +9592,31 @@
         <v>6</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="D145" s="6"/>
       <c r="E145" s="6"/>
       <c r="F145" s="6"/>
       <c r="G145" s="6" t="s">
+        <v>956</v>
+      </c>
+      <c r="H145" s="6" t="s">
+        <v>957</v>
+      </c>
+      <c r="I145" s="6" t="s">
+        <v>958</v>
+      </c>
+      <c r="J145" s="6" t="s">
         <v>959</v>
       </c>
-      <c r="H145" s="6" t="s">
+      <c r="K145" s="6" t="s">
         <v>960</v>
-      </c>
-      <c r="I145" s="6" t="s">
-        <v>961</v>
-      </c>
-      <c r="J145" s="6" t="s">
-        <v>962</v>
-      </c>
-      <c r="K145" s="6" t="s">
-        <v>963</v>
       </c>
       <c r="L145" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M145" s="6" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
     </row>
     <row r="146" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -9627,31 +9627,31 @@
         <v>6</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="D146" s="5"/>
       <c r="E146" s="5"/>
       <c r="F146" s="5"/>
       <c r="G146" s="5" t="s">
+        <v>962</v>
+      </c>
+      <c r="H146" s="5" t="s">
+        <v>963</v>
+      </c>
+      <c r="I146" s="5" t="s">
+        <v>964</v>
+      </c>
+      <c r="J146" s="5" t="s">
         <v>965</v>
       </c>
-      <c r="H146" s="5" t="s">
+      <c r="K146" s="5" t="s">
         <v>966</v>
-      </c>
-      <c r="I146" s="5" t="s">
-        <v>967</v>
-      </c>
-      <c r="J146" s="5" t="s">
-        <v>968</v>
-      </c>
-      <c r="K146" s="5" t="s">
-        <v>969</v>
       </c>
       <c r="L146" s="4" t="s">
         <v>52</v>
       </c>
       <c r="M146" s="5" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
     </row>
     <row r="147" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -9662,7 +9662,7 @@
         <v>6</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="D147" s="6"/>
       <c r="E147" s="6"/>
@@ -9671,25 +9671,25 @@
         <v>883</v>
       </c>
       <c r="H147" s="6" t="s">
+        <v>968</v>
+      </c>
+      <c r="I147" s="6" t="s">
+        <v>969</v>
+      </c>
+      <c r="J147" s="6" t="s">
+        <v>970</v>
+      </c>
+      <c r="K147" s="6" t="s">
         <v>971</v>
-      </c>
-      <c r="I147" s="6" t="s">
-        <v>972</v>
-      </c>
-      <c r="J147" s="6" t="s">
-        <v>973</v>
-      </c>
-      <c r="K147" s="6" t="s">
-        <v>974</v>
       </c>
       <c r="L147" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M147" s="6" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="148" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A148" s="4">
         <v>147</v>
       </c>
@@ -9697,33 +9697,33 @@
         <v>7</v>
       </c>
       <c r="C148" s="4" t="s">
+        <v>973</v>
+      </c>
+      <c r="D148" s="5"/>
+      <c r="E148" s="8" t="s">
+        <v>1321</v>
+      </c>
+      <c r="F148" s="5"/>
+      <c r="G148" s="5" t="s">
+        <v>974</v>
+      </c>
+      <c r="H148" s="5" t="s">
+        <v>975</v>
+      </c>
+      <c r="I148" s="5" t="s">
         <v>976</v>
       </c>
-      <c r="D148" s="5"/>
-      <c r="E148" s="5"/>
-      <c r="F148" s="5" t="s">
+      <c r="J148" s="5" t="s">
         <v>977</v>
       </c>
-      <c r="G148" s="5" t="s">
+      <c r="K148" s="5" t="s">
         <v>978</v>
-      </c>
-      <c r="H148" s="5" t="s">
-        <v>979</v>
-      </c>
-      <c r="I148" s="5" t="s">
-        <v>980</v>
-      </c>
-      <c r="J148" s="5" t="s">
-        <v>981</v>
-      </c>
-      <c r="K148" s="5" t="s">
-        <v>982</v>
       </c>
       <c r="L148" s="4" t="s">
         <v>52</v>
       </c>
       <c r="M148" s="5" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
     </row>
     <row r="149" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -9734,34 +9734,34 @@
         <v>7</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="D149" s="6"/>
       <c r="E149" s="6"/>
       <c r="F149" s="6"/>
       <c r="G149" s="6" t="s">
+        <v>980</v>
+      </c>
+      <c r="H149" s="6" t="s">
+        <v>981</v>
+      </c>
+      <c r="I149" s="6" t="s">
+        <v>982</v>
+      </c>
+      <c r="J149" s="6" t="s">
+        <v>983</v>
+      </c>
+      <c r="K149" s="6" t="s">
         <v>984</v>
-      </c>
-      <c r="H149" s="6" t="s">
-        <v>985</v>
-      </c>
-      <c r="I149" s="6" t="s">
-        <v>986</v>
-      </c>
-      <c r="J149" s="6" t="s">
-        <v>987</v>
-      </c>
-      <c r="K149" s="6" t="s">
-        <v>988</v>
       </c>
       <c r="L149" s="2" t="s">
         <v>39</v>
       </c>
       <c r="M149" s="6" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="150" spans="1:13" ht="135" x14ac:dyDescent="0.25">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A150" s="4">
         <v>149</v>
       </c>
@@ -9769,33 +9769,33 @@
         <v>7</v>
       </c>
       <c r="C150" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="D150" s="5"/>
+      <c r="E150" s="8" t="s">
+        <v>1322</v>
+      </c>
+      <c r="F150" s="5"/>
+      <c r="G150" s="5" t="s">
+        <v>987</v>
+      </c>
+      <c r="H150" s="5" t="s">
+        <v>988</v>
+      </c>
+      <c r="I150" s="5" t="s">
+        <v>989</v>
+      </c>
+      <c r="J150" s="5" t="s">
         <v>990</v>
       </c>
-      <c r="D150" s="5"/>
-      <c r="E150" s="5"/>
-      <c r="F150" s="5" t="s">
+      <c r="K150" s="5" t="s">
         <v>991</v>
-      </c>
-      <c r="G150" s="5" t="s">
-        <v>992</v>
-      </c>
-      <c r="H150" s="5" t="s">
-        <v>993</v>
-      </c>
-      <c r="I150" s="5" t="s">
-        <v>994</v>
-      </c>
-      <c r="J150" s="5" t="s">
-        <v>995</v>
-      </c>
-      <c r="K150" s="5" t="s">
-        <v>996</v>
       </c>
       <c r="L150" s="4" t="s">
         <v>39</v>
       </c>
       <c r="M150" s="5" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
     </row>
     <row r="151" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -9806,34 +9806,34 @@
         <v>7</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="D151" s="6"/>
       <c r="E151" s="6"/>
       <c r="F151" s="6"/>
       <c r="G151" s="6" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="H151" s="6" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="I151" s="6" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="J151" s="6" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="K151" s="6" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="L151" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M151" s="6" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="152" spans="1:13" ht="135" x14ac:dyDescent="0.25">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A152" s="4">
         <v>151</v>
       </c>
@@ -9841,33 +9841,33 @@
         <v>7</v>
       </c>
       <c r="C152" s="4" t="s">
+        <v>999</v>
+      </c>
+      <c r="D152" s="5"/>
+      <c r="E152" s="8" t="s">
+        <v>1323</v>
+      </c>
+      <c r="F152" s="5"/>
+      <c r="G152" s="5" t="s">
+        <v>1000</v>
+      </c>
+      <c r="H152" s="5" t="s">
+        <v>1001</v>
+      </c>
+      <c r="I152" s="5" t="s">
+        <v>1002</v>
+      </c>
+      <c r="J152" s="5" t="s">
+        <v>1003</v>
+      </c>
+      <c r="K152" s="5" t="s">
         <v>1004</v>
-      </c>
-      <c r="D152" s="5"/>
-      <c r="E152" s="5"/>
-      <c r="F152" s="5" t="s">
-        <v>1005</v>
-      </c>
-      <c r="G152" s="5" t="s">
-        <v>1006</v>
-      </c>
-      <c r="H152" s="5" t="s">
-        <v>1007</v>
-      </c>
-      <c r="I152" s="5" t="s">
-        <v>1008</v>
-      </c>
-      <c r="J152" s="5" t="s">
-        <v>1009</v>
-      </c>
-      <c r="K152" s="5" t="s">
-        <v>1010</v>
       </c>
       <c r="L152" s="4" t="s">
         <v>32</v>
       </c>
       <c r="M152" s="5" t="s">
-        <v>1011</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="153" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -9878,31 +9878,31 @@
         <v>7</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="D153" s="6"/>
       <c r="E153" s="6"/>
       <c r="F153" s="6"/>
       <c r="G153" s="6" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="H153" s="6" t="s">
         <v>278</v>
       </c>
       <c r="I153" s="6" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="J153" s="6" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="K153" s="6" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="L153" s="2" t="s">
         <v>39</v>
       </c>
       <c r="M153" s="6" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="154" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -9913,34 +9913,34 @@
         <v>7</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="D154" s="5"/>
       <c r="E154" s="5"/>
       <c r="F154" s="5"/>
       <c r="G154" s="5" t="s">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="H154" s="5" t="s">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="I154" s="5" t="s">
-        <v>1019</v>
+        <v>1013</v>
       </c>
       <c r="J154" s="5" t="s">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="K154" s="5" t="s">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="L154" s="4" t="s">
         <v>25</v>
       </c>
       <c r="M154" s="5" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="155" spans="1:13" ht="150" x14ac:dyDescent="0.25">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
         <v>154</v>
       </c>
@@ -9948,33 +9948,33 @@
         <v>7</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>1023</v>
+        <v>1017</v>
       </c>
       <c r="D155" s="6"/>
-      <c r="E155" s="6"/>
-      <c r="F155" s="6" t="s">
-        <v>1024</v>
-      </c>
+      <c r="E155" s="9" t="s">
+        <v>1324</v>
+      </c>
+      <c r="F155" s="6"/>
       <c r="G155" s="6" t="s">
-        <v>1025</v>
+        <v>1018</v>
       </c>
       <c r="H155" s="6" t="s">
-        <v>1026</v>
+        <v>1019</v>
       </c>
       <c r="I155" s="6" t="s">
-        <v>1027</v>
+        <v>1020</v>
       </c>
       <c r="J155" s="6" t="s">
-        <v>1028</v>
+        <v>1021</v>
       </c>
       <c r="K155" s="6" t="s">
-        <v>1029</v>
+        <v>1022</v>
       </c>
       <c r="L155" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M155" s="6" t="s">
-        <v>1030</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="156" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -9985,34 +9985,34 @@
         <v>7</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>1023</v>
+        <v>1017</v>
       </c>
       <c r="D156" s="5"/>
       <c r="E156" s="5"/>
       <c r="F156" s="5"/>
       <c r="G156" s="5" t="s">
-        <v>1031</v>
+        <v>1024</v>
       </c>
       <c r="H156" s="5" t="s">
-        <v>1032</v>
+        <v>1025</v>
       </c>
       <c r="I156" s="5" t="s">
-        <v>1033</v>
+        <v>1026</v>
       </c>
       <c r="J156" s="5" t="s">
-        <v>1034</v>
+        <v>1027</v>
       </c>
       <c r="K156" s="5" t="s">
-        <v>1035</v>
+        <v>1028</v>
       </c>
       <c r="L156" s="4" t="s">
         <v>32</v>
       </c>
       <c r="M156" s="5" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="157" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <v>156</v>
       </c>
@@ -10020,33 +10020,33 @@
         <v>7</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>1037</v>
+        <v>1030</v>
       </c>
       <c r="D157" s="6"/>
-      <c r="E157" s="6"/>
-      <c r="F157" s="6" t="s">
-        <v>1038</v>
-      </c>
+      <c r="E157" s="9" t="s">
+        <v>1325</v>
+      </c>
+      <c r="F157" s="6"/>
       <c r="G157" s="6" t="s">
-        <v>1039</v>
+        <v>1031</v>
       </c>
       <c r="H157" s="6" t="s">
-        <v>1040</v>
+        <v>1032</v>
       </c>
       <c r="I157" s="6" t="s">
-        <v>1041</v>
+        <v>1033</v>
       </c>
       <c r="J157" s="6" t="s">
-        <v>1042</v>
+        <v>1034</v>
       </c>
       <c r="K157" s="6" t="s">
-        <v>1043</v>
+        <v>1035</v>
       </c>
       <c r="L157" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M157" s="6" t="s">
-        <v>1044</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="158" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -10057,34 +10057,34 @@
         <v>7</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>1037</v>
+        <v>1030</v>
       </c>
       <c r="D158" s="5"/>
       <c r="E158" s="5"/>
       <c r="F158" s="5"/>
       <c r="G158" s="5" t="s">
-        <v>1045</v>
+        <v>1037</v>
       </c>
       <c r="H158" s="5" t="s">
-        <v>1046</v>
+        <v>1038</v>
       </c>
       <c r="I158" s="5" t="s">
-        <v>1047</v>
+        <v>1039</v>
       </c>
       <c r="J158" s="5" t="s">
-        <v>1048</v>
+        <v>1040</v>
       </c>
       <c r="K158" s="5" t="s">
-        <v>1049</v>
+        <v>1041</v>
       </c>
       <c r="L158" s="4" t="s">
         <v>25</v>
       </c>
       <c r="M158" s="5" t="s">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="159" spans="1:13" ht="195" x14ac:dyDescent="0.25">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
         <v>158</v>
       </c>
@@ -10092,33 +10092,33 @@
         <v>7</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>1051</v>
+        <v>1043</v>
       </c>
       <c r="D159" s="6"/>
-      <c r="E159" s="6"/>
-      <c r="F159" s="6" t="s">
-        <v>1052</v>
-      </c>
+      <c r="E159" s="9" t="s">
+        <v>1326</v>
+      </c>
+      <c r="F159" s="6"/>
       <c r="G159" s="6" t="s">
-        <v>1053</v>
+        <v>1044</v>
       </c>
       <c r="H159" s="6" t="s">
-        <v>1054</v>
+        <v>1045</v>
       </c>
       <c r="I159" s="6" t="s">
-        <v>1055</v>
+        <v>1046</v>
       </c>
       <c r="J159" s="6" t="s">
-        <v>1056</v>
+        <v>1047</v>
       </c>
       <c r="K159" s="6" t="s">
-        <v>1057</v>
+        <v>1048</v>
       </c>
       <c r="L159" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M159" s="6" t="s">
-        <v>1058</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="160" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -10129,31 +10129,31 @@
         <v>7</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>1051</v>
+        <v>1043</v>
       </c>
       <c r="D160" s="5"/>
       <c r="E160" s="5"/>
       <c r="F160" s="5"/>
       <c r="G160" s="5" t="s">
-        <v>1059</v>
+        <v>1050</v>
       </c>
       <c r="H160" s="5" t="s">
-        <v>1060</v>
+        <v>1051</v>
       </c>
       <c r="I160" s="5" t="s">
-        <v>1061</v>
+        <v>1052</v>
       </c>
       <c r="J160" s="5" t="s">
-        <v>1062</v>
+        <v>1053</v>
       </c>
       <c r="K160" s="5" t="s">
-        <v>1063</v>
+        <v>1054</v>
       </c>
       <c r="L160" s="4" t="s">
         <v>39</v>
       </c>
       <c r="M160" s="5" t="s">
-        <v>1064</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="161" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -10164,31 +10164,31 @@
         <v>7</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>1051</v>
+        <v>1043</v>
       </c>
       <c r="D161" s="6"/>
       <c r="E161" s="6"/>
       <c r="F161" s="6"/>
       <c r="G161" s="6" t="s">
-        <v>1065</v>
+        <v>1056</v>
       </c>
       <c r="H161" s="6" t="s">
-        <v>1066</v>
+        <v>1057</v>
       </c>
       <c r="I161" s="6" t="s">
-        <v>1067</v>
+        <v>1058</v>
       </c>
       <c r="J161" s="6" t="s">
-        <v>1068</v>
+        <v>1059</v>
       </c>
       <c r="K161" s="6" t="s">
-        <v>1069</v>
+        <v>1060</v>
       </c>
       <c r="L161" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M161" s="6" t="s">
-        <v>1070</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="162" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -10199,34 +10199,34 @@
         <v>7</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>1051</v>
+        <v>1043</v>
       </c>
       <c r="D162" s="5"/>
       <c r="E162" s="5"/>
       <c r="F162" s="5"/>
       <c r="G162" s="5" t="s">
-        <v>1071</v>
+        <v>1062</v>
       </c>
       <c r="H162" s="5" t="s">
-        <v>1072</v>
+        <v>1063</v>
       </c>
       <c r="I162" s="5" t="s">
-        <v>1073</v>
+        <v>1064</v>
       </c>
       <c r="J162" s="5" t="s">
-        <v>1074</v>
+        <v>1065</v>
       </c>
       <c r="K162" s="5" t="s">
-        <v>1075</v>
+        <v>1066</v>
       </c>
       <c r="L162" s="4" t="s">
         <v>52</v>
       </c>
       <c r="M162" s="5" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="163" spans="1:13" ht="255" x14ac:dyDescent="0.25">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
         <v>162</v>
       </c>
@@ -10234,33 +10234,33 @@
         <v>7</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>1077</v>
+        <v>1068</v>
       </c>
       <c r="D163" s="6"/>
-      <c r="E163" s="6"/>
-      <c r="F163" s="6" t="s">
-        <v>1078</v>
-      </c>
+      <c r="E163" s="9" t="s">
+        <v>1327</v>
+      </c>
+      <c r="F163" s="6"/>
       <c r="G163" s="6" t="s">
-        <v>1079</v>
+        <v>1069</v>
       </c>
       <c r="H163" s="6" t="s">
-        <v>1080</v>
+        <v>1070</v>
       </c>
       <c r="I163" s="6" t="s">
-        <v>1081</v>
+        <v>1071</v>
       </c>
       <c r="J163" s="6" t="s">
-        <v>1082</v>
+        <v>1072</v>
       </c>
       <c r="K163" s="6" t="s">
-        <v>1083</v>
+        <v>1073</v>
       </c>
       <c r="L163" s="2" t="s">
         <v>52</v>
       </c>
       <c r="M163" s="6" t="s">
-        <v>1084</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="164" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -10271,31 +10271,31 @@
         <v>7</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>1077</v>
+        <v>1068</v>
       </c>
       <c r="D164" s="5"/>
       <c r="E164" s="5"/>
       <c r="F164" s="5"/>
       <c r="G164" s="5" t="s">
-        <v>1085</v>
+        <v>1075</v>
       </c>
       <c r="H164" s="5" t="s">
-        <v>1086</v>
+        <v>1076</v>
       </c>
       <c r="I164" s="5" t="s">
-        <v>1087</v>
+        <v>1077</v>
       </c>
       <c r="J164" s="5" t="s">
-        <v>1088</v>
+        <v>1078</v>
       </c>
       <c r="K164" s="5" t="s">
-        <v>1089</v>
+        <v>1079</v>
       </c>
       <c r="L164" s="4" t="s">
         <v>39</v>
       </c>
       <c r="M164" s="5" t="s">
-        <v>1090</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="165" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -10306,31 +10306,31 @@
         <v>7</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>1077</v>
+        <v>1068</v>
       </c>
       <c r="D165" s="6"/>
       <c r="E165" s="6"/>
       <c r="F165" s="6"/>
       <c r="G165" s="6" t="s">
-        <v>1091</v>
+        <v>1081</v>
       </c>
       <c r="H165" s="6" t="s">
-        <v>1092</v>
+        <v>1082</v>
       </c>
       <c r="I165" s="6" t="s">
-        <v>1093</v>
+        <v>1083</v>
       </c>
       <c r="J165" s="6" t="s">
-        <v>1094</v>
+        <v>1084</v>
       </c>
       <c r="K165" s="6" t="s">
-        <v>1095</v>
+        <v>1085</v>
       </c>
       <c r="L165" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M165" s="6" t="s">
-        <v>1096</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="166" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -10341,34 +10341,34 @@
         <v>7</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>1077</v>
+        <v>1068</v>
       </c>
       <c r="D166" s="5"/>
       <c r="E166" s="5"/>
       <c r="F166" s="5"/>
       <c r="G166" s="5" t="s">
-        <v>1097</v>
+        <v>1087</v>
       </c>
       <c r="H166" s="5" t="s">
-        <v>1098</v>
+        <v>1088</v>
       </c>
       <c r="I166" s="5" t="s">
-        <v>1099</v>
+        <v>1089</v>
       </c>
       <c r="J166" s="5" t="s">
-        <v>1100</v>
+        <v>1090</v>
       </c>
       <c r="K166" s="5" t="s">
-        <v>1101</v>
+        <v>1091</v>
       </c>
       <c r="L166" s="4" t="s">
         <v>25</v>
       </c>
       <c r="M166" s="5" t="s">
-        <v>1102</v>
-      </c>
-    </row>
-    <row r="167" spans="1:13" ht="165" x14ac:dyDescent="0.25">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
         <v>166</v>
       </c>
@@ -10376,33 +10376,33 @@
         <v>7</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>1103</v>
+        <v>1093</v>
       </c>
       <c r="D167" s="6"/>
-      <c r="E167" s="6"/>
-      <c r="F167" s="6" t="s">
-        <v>1104</v>
-      </c>
+      <c r="E167" s="9" t="s">
+        <v>1328</v>
+      </c>
+      <c r="F167" s="6"/>
       <c r="G167" s="6" t="s">
-        <v>1105</v>
+        <v>1094</v>
       </c>
       <c r="H167" s="6" t="s">
-        <v>1106</v>
+        <v>1095</v>
       </c>
       <c r="I167" s="6" t="s">
-        <v>1107</v>
+        <v>1096</v>
       </c>
       <c r="J167" s="6" t="s">
-        <v>1108</v>
+        <v>1097</v>
       </c>
       <c r="K167" s="6" t="s">
-        <v>1109</v>
+        <v>1098</v>
       </c>
       <c r="L167" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M167" s="6" t="s">
-        <v>1110</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="168" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -10413,31 +10413,31 @@
         <v>7</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>1103</v>
+        <v>1093</v>
       </c>
       <c r="D168" s="5"/>
       <c r="E168" s="5"/>
       <c r="F168" s="5"/>
       <c r="G168" s="5" t="s">
-        <v>1111</v>
+        <v>1100</v>
       </c>
       <c r="H168" s="5" t="s">
-        <v>1112</v>
+        <v>1101</v>
       </c>
       <c r="I168" s="5" t="s">
-        <v>1113</v>
+        <v>1102</v>
       </c>
       <c r="J168" s="5" t="s">
-        <v>1114</v>
+        <v>1103</v>
       </c>
       <c r="K168" s="5" t="s">
-        <v>1115</v>
+        <v>1104</v>
       </c>
       <c r="L168" s="4" t="s">
         <v>52</v>
       </c>
       <c r="M168" s="5" t="s">
-        <v>1116</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="169" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -10448,34 +10448,34 @@
         <v>7</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>1103</v>
+        <v>1093</v>
       </c>
       <c r="D169" s="6"/>
       <c r="E169" s="6"/>
       <c r="F169" s="6"/>
       <c r="G169" s="6" t="s">
-        <v>1117</v>
+        <v>1106</v>
       </c>
       <c r="H169" s="6" t="s">
-        <v>1118</v>
+        <v>1107</v>
       </c>
       <c r="I169" s="6" t="s">
-        <v>1119</v>
+        <v>1108</v>
       </c>
       <c r="J169" s="6" t="s">
-        <v>1120</v>
+        <v>1109</v>
       </c>
       <c r="K169" s="6" t="s">
-        <v>1121</v>
+        <v>1110</v>
       </c>
       <c r="L169" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M169" s="6" t="s">
-        <v>1122</v>
-      </c>
-    </row>
-    <row r="170" spans="1:13" ht="195" x14ac:dyDescent="0.25">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A170" s="4">
         <v>169</v>
       </c>
@@ -10483,33 +10483,33 @@
         <v>7</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>1123</v>
+        <v>1112</v>
       </c>
       <c r="D170" s="5"/>
-      <c r="E170" s="5"/>
-      <c r="F170" s="5" t="s">
-        <v>1124</v>
-      </c>
+      <c r="E170" s="8" t="s">
+        <v>1329</v>
+      </c>
+      <c r="F170" s="5"/>
       <c r="G170" s="5" t="s">
-        <v>1125</v>
+        <v>1113</v>
       </c>
       <c r="H170" s="5" t="s">
-        <v>1126</v>
+        <v>1114</v>
       </c>
       <c r="I170" s="5" t="s">
-        <v>1127</v>
+        <v>1115</v>
       </c>
       <c r="J170" s="5" t="s">
-        <v>1128</v>
+        <v>1116</v>
       </c>
       <c r="K170" s="5" t="s">
-        <v>1129</v>
+        <v>1117</v>
       </c>
       <c r="L170" s="4" t="s">
         <v>52</v>
       </c>
       <c r="M170" s="5" t="s">
-        <v>1130</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="171" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -10520,31 +10520,31 @@
         <v>7</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>1123</v>
+        <v>1112</v>
       </c>
       <c r="D171" s="6"/>
       <c r="E171" s="6"/>
       <c r="F171" s="6"/>
       <c r="G171" s="6" t="s">
-        <v>1131</v>
+        <v>1119</v>
       </c>
       <c r="H171" s="6" t="s">
-        <v>1132</v>
+        <v>1120</v>
       </c>
       <c r="I171" s="6" t="s">
-        <v>1133</v>
+        <v>1121</v>
       </c>
       <c r="J171" s="6" t="s">
-        <v>1134</v>
+        <v>1122</v>
       </c>
       <c r="K171" s="6" t="s">
-        <v>1135</v>
+        <v>1123</v>
       </c>
       <c r="L171" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M171" s="6" t="s">
-        <v>1136</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="172" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -10555,34 +10555,34 @@
         <v>7</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>1123</v>
+        <v>1112</v>
       </c>
       <c r="D172" s="5"/>
       <c r="E172" s="5"/>
       <c r="F172" s="5"/>
       <c r="G172" s="5" t="s">
-        <v>1137</v>
+        <v>1125</v>
       </c>
       <c r="H172" s="5" t="s">
-        <v>1138</v>
+        <v>1126</v>
       </c>
       <c r="I172" s="5" t="s">
-        <v>1139</v>
+        <v>1127</v>
       </c>
       <c r="J172" s="5" t="s">
-        <v>1140</v>
+        <v>1128</v>
       </c>
       <c r="K172" s="5" t="s">
-        <v>1141</v>
+        <v>1129</v>
       </c>
       <c r="L172" s="4" t="s">
         <v>32</v>
       </c>
       <c r="M172" s="5" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="173" spans="1:13" ht="240" x14ac:dyDescent="0.25">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
         <v>172</v>
       </c>
@@ -10590,33 +10590,33 @@
         <v>7</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>1143</v>
+        <v>1131</v>
       </c>
       <c r="D173" s="6"/>
-      <c r="E173" s="6"/>
-      <c r="F173" s="6" t="s">
-        <v>1144</v>
-      </c>
+      <c r="E173" s="9" t="s">
+        <v>1330</v>
+      </c>
+      <c r="F173" s="6"/>
       <c r="G173" s="6" t="s">
-        <v>1145</v>
+        <v>1132</v>
       </c>
       <c r="H173" s="6" t="s">
-        <v>1146</v>
+        <v>1133</v>
       </c>
       <c r="I173" s="6" t="s">
-        <v>1147</v>
+        <v>1134</v>
       </c>
       <c r="J173" s="6" t="s">
-        <v>1148</v>
+        <v>1135</v>
       </c>
       <c r="K173" s="6" t="s">
-        <v>1149</v>
+        <v>1136</v>
       </c>
       <c r="L173" s="2" t="s">
         <v>39</v>
       </c>
       <c r="M173" s="6" t="s">
-        <v>1150</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="174" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -10627,31 +10627,31 @@
         <v>7</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>1143</v>
+        <v>1131</v>
       </c>
       <c r="D174" s="5"/>
       <c r="E174" s="5"/>
       <c r="F174" s="5"/>
       <c r="G174" s="5" t="s">
-        <v>1151</v>
+        <v>1138</v>
       </c>
       <c r="H174" s="5" t="s">
-        <v>1152</v>
+        <v>1139</v>
       </c>
       <c r="I174" s="5" t="s">
-        <v>1153</v>
+        <v>1140</v>
       </c>
       <c r="J174" s="5" t="s">
-        <v>1154</v>
+        <v>1141</v>
       </c>
       <c r="K174" s="5" t="s">
-        <v>1155</v>
+        <v>1142</v>
       </c>
       <c r="L174" s="4" t="s">
         <v>32</v>
       </c>
       <c r="M174" s="5" t="s">
-        <v>1156</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="175" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -10662,31 +10662,31 @@
         <v>7</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>1143</v>
+        <v>1131</v>
       </c>
       <c r="D175" s="6"/>
       <c r="E175" s="6"/>
       <c r="F175" s="6"/>
       <c r="G175" s="6" t="s">
-        <v>1157</v>
+        <v>1144</v>
       </c>
       <c r="H175" s="6" t="s">
-        <v>1158</v>
+        <v>1145</v>
       </c>
       <c r="I175" s="6" t="s">
-        <v>1159</v>
+        <v>1146</v>
       </c>
       <c r="J175" s="6" t="s">
-        <v>1160</v>
+        <v>1147</v>
       </c>
       <c r="K175" s="6" t="s">
-        <v>1161</v>
+        <v>1148</v>
       </c>
       <c r="L175" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M175" s="6" t="s">
-        <v>1162</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="176" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -10697,34 +10697,34 @@
         <v>7</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>1143</v>
+        <v>1131</v>
       </c>
       <c r="D176" s="5"/>
       <c r="E176" s="5"/>
       <c r="F176" s="5"/>
       <c r="G176" s="5" t="s">
-        <v>1163</v>
+        <v>1150</v>
       </c>
       <c r="H176" s="5" t="s">
-        <v>1138</v>
+        <v>1126</v>
       </c>
       <c r="I176" s="5" t="s">
-        <v>1139</v>
+        <v>1127</v>
       </c>
       <c r="J176" s="5" t="s">
-        <v>1140</v>
+        <v>1128</v>
       </c>
       <c r="K176" s="5" t="s">
-        <v>1141</v>
+        <v>1129</v>
       </c>
       <c r="L176" s="4" t="s">
         <v>52</v>
       </c>
       <c r="M176" s="5" t="s">
-        <v>1164</v>
-      </c>
-    </row>
-    <row r="177" spans="1:13" ht="240" x14ac:dyDescent="0.25">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="177" spans="1:13" ht="150" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
         <v>176</v>
       </c>
@@ -10732,33 +10732,33 @@
         <v>7</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>1165</v>
+        <v>1152</v>
       </c>
       <c r="D177" s="6"/>
-      <c r="E177" s="6"/>
-      <c r="F177" s="6" t="s">
-        <v>1166</v>
-      </c>
+      <c r="E177" s="6" t="s">
+        <v>1331</v>
+      </c>
+      <c r="F177" s="6"/>
       <c r="G177" s="6" t="s">
-        <v>1167</v>
+        <v>1153</v>
       </c>
       <c r="H177" s="6" t="s">
-        <v>1168</v>
+        <v>1154</v>
       </c>
       <c r="I177" s="6" t="s">
-        <v>1169</v>
+        <v>1155</v>
       </c>
       <c r="J177" s="6" t="s">
-        <v>1170</v>
+        <v>1156</v>
       </c>
       <c r="K177" s="6" t="s">
-        <v>1171</v>
+        <v>1157</v>
       </c>
       <c r="L177" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M177" s="6" t="s">
-        <v>1172</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="178" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -10769,31 +10769,31 @@
         <v>7</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>1165</v>
+        <v>1152</v>
       </c>
       <c r="D178" s="5"/>
       <c r="E178" s="5"/>
       <c r="F178" s="5"/>
       <c r="G178" s="5" t="s">
-        <v>1173</v>
+        <v>1159</v>
       </c>
       <c r="H178" s="5" t="s">
-        <v>1174</v>
+        <v>1160</v>
       </c>
       <c r="I178" s="5" t="s">
-        <v>1175</v>
+        <v>1161</v>
       </c>
       <c r="J178" s="5" t="s">
-        <v>1176</v>
+        <v>1162</v>
       </c>
       <c r="K178" s="5" t="s">
-        <v>1177</v>
+        <v>1163</v>
       </c>
       <c r="L178" s="4" t="s">
         <v>52</v>
       </c>
       <c r="M178" s="5" t="s">
-        <v>1178</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="179" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -10804,31 +10804,31 @@
         <v>7</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>1165</v>
+        <v>1152</v>
       </c>
       <c r="D179" s="6"/>
       <c r="E179" s="6"/>
       <c r="F179" s="6"/>
       <c r="G179" s="6" t="s">
-        <v>1179</v>
+        <v>1165</v>
       </c>
       <c r="H179" s="6" t="s">
-        <v>1180</v>
+        <v>1166</v>
       </c>
       <c r="I179" s="6" t="s">
-        <v>1181</v>
+        <v>1167</v>
       </c>
       <c r="J179" s="6" t="s">
-        <v>1182</v>
+        <v>1168</v>
       </c>
       <c r="K179" s="6" t="s">
-        <v>1183</v>
+        <v>1169</v>
       </c>
       <c r="L179" s="2" t="s">
         <v>39</v>
       </c>
       <c r="M179" s="6" t="s">
-        <v>1184</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="180" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -10839,31 +10839,31 @@
         <v>7</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>1165</v>
+        <v>1152</v>
       </c>
       <c r="D180" s="5"/>
       <c r="E180" s="5"/>
       <c r="F180" s="5"/>
       <c r="G180" s="5" t="s">
-        <v>1185</v>
+        <v>1171</v>
       </c>
       <c r="H180" s="5" t="s">
-        <v>1186</v>
+        <v>1172</v>
       </c>
       <c r="I180" s="5" t="s">
-        <v>1187</v>
+        <v>1173</v>
       </c>
       <c r="J180" s="5" t="s">
-        <v>1188</v>
+        <v>1174</v>
       </c>
       <c r="K180" s="5" t="s">
-        <v>1189</v>
+        <v>1175</v>
       </c>
       <c r="L180" s="4" t="s">
         <v>25</v>
       </c>
       <c r="M180" s="5" t="s">
-        <v>1190</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="181" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -10874,34 +10874,34 @@
         <v>7</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>1165</v>
+        <v>1152</v>
       </c>
       <c r="D181" s="6"/>
       <c r="E181" s="6"/>
       <c r="F181" s="6"/>
       <c r="G181" s="6" t="s">
-        <v>1191</v>
+        <v>1177</v>
       </c>
       <c r="H181" s="6" t="s">
-        <v>1192</v>
+        <v>1178</v>
       </c>
       <c r="I181" s="6" t="s">
-        <v>1193</v>
+        <v>1179</v>
       </c>
       <c r="J181" s="6" t="s">
-        <v>1194</v>
+        <v>1180</v>
       </c>
       <c r="K181" s="6" t="s">
-        <v>1195</v>
+        <v>1181</v>
       </c>
       <c r="L181" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M181" s="6" t="s">
-        <v>1196</v>
-      </c>
-    </row>
-    <row r="182" spans="1:13" ht="210" x14ac:dyDescent="0.25">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="182" spans="1:13" ht="150" x14ac:dyDescent="0.25">
       <c r="A182" s="4">
         <v>181</v>
       </c>
@@ -10909,33 +10909,33 @@
         <v>7</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>1197</v>
+        <v>1183</v>
       </c>
       <c r="D182" s="5"/>
-      <c r="E182" s="5"/>
-      <c r="F182" s="5" t="s">
-        <v>1198</v>
-      </c>
+      <c r="E182" s="5" t="s">
+        <v>1332</v>
+      </c>
+      <c r="F182" s="5"/>
       <c r="G182" s="5" t="s">
-        <v>1199</v>
+        <v>1184</v>
       </c>
       <c r="H182" s="5" t="s">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="I182" s="5" t="s">
-        <v>1201</v>
+        <v>1186</v>
       </c>
       <c r="J182" s="5" t="s">
-        <v>1202</v>
+        <v>1187</v>
       </c>
       <c r="K182" s="5" t="s">
-        <v>1203</v>
+        <v>1188</v>
       </c>
       <c r="L182" s="4" t="s">
         <v>52</v>
       </c>
       <c r="M182" s="5" t="s">
-        <v>1204</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="183" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -10946,31 +10946,31 @@
         <v>7</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>1197</v>
+        <v>1183</v>
       </c>
       <c r="D183" s="6"/>
       <c r="E183" s="6"/>
       <c r="F183" s="6"/>
       <c r="G183" s="6" t="s">
-        <v>1205</v>
+        <v>1190</v>
       </c>
       <c r="H183" s="6" t="s">
-        <v>1206</v>
+        <v>1191</v>
       </c>
       <c r="I183" s="6" t="s">
-        <v>1207</v>
+        <v>1192</v>
       </c>
       <c r="J183" s="6" t="s">
-        <v>1208</v>
+        <v>1193</v>
       </c>
       <c r="K183" s="6" t="s">
-        <v>1209</v>
+        <v>1194</v>
       </c>
       <c r="L183" s="2" t="s">
         <v>39</v>
       </c>
       <c r="M183" s="6" t="s">
-        <v>1210</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="184" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -10981,31 +10981,31 @@
         <v>7</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>1197</v>
+        <v>1183</v>
       </c>
       <c r="D184" s="5"/>
       <c r="E184" s="5"/>
       <c r="F184" s="5"/>
       <c r="G184" s="5" t="s">
-        <v>1211</v>
+        <v>1196</v>
       </c>
       <c r="H184" s="5" t="s">
-        <v>1212</v>
+        <v>1197</v>
       </c>
       <c r="I184" s="5" t="s">
-        <v>1213</v>
+        <v>1198</v>
       </c>
       <c r="J184" s="5" t="s">
-        <v>1214</v>
+        <v>1199</v>
       </c>
       <c r="K184" s="5" t="s">
-        <v>1215</v>
+        <v>1200</v>
       </c>
       <c r="L184" s="4" t="s">
         <v>39</v>
       </c>
       <c r="M184" s="5" t="s">
-        <v>1216</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="185" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -11016,31 +11016,31 @@
         <v>7</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>1197</v>
+        <v>1183</v>
       </c>
       <c r="D185" s="6"/>
       <c r="E185" s="6"/>
       <c r="F185" s="6"/>
       <c r="G185" s="6" t="s">
-        <v>1217</v>
+        <v>1202</v>
       </c>
       <c r="H185" s="6" t="s">
-        <v>1218</v>
+        <v>1203</v>
       </c>
       <c r="I185" s="6" t="s">
-        <v>1219</v>
+        <v>1204</v>
       </c>
       <c r="J185" s="6" t="s">
-        <v>1220</v>
+        <v>1205</v>
       </c>
       <c r="K185" s="6" t="s">
-        <v>1221</v>
+        <v>1206</v>
       </c>
       <c r="L185" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M185" s="6" t="s">
-        <v>1222</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="186" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -11051,34 +11051,34 @@
         <v>7</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>1197</v>
+        <v>1183</v>
       </c>
       <c r="D186" s="5"/>
       <c r="E186" s="5"/>
       <c r="F186" s="5"/>
       <c r="G186" s="5" t="s">
-        <v>1223</v>
+        <v>1208</v>
       </c>
       <c r="H186" s="5" t="s">
-        <v>1224</v>
+        <v>1209</v>
       </c>
       <c r="I186" s="5" t="s">
-        <v>1225</v>
+        <v>1210</v>
       </c>
       <c r="J186" s="5" t="s">
-        <v>1226</v>
+        <v>1211</v>
       </c>
       <c r="K186" s="5" t="s">
-        <v>1227</v>
+        <v>1212</v>
       </c>
       <c r="L186" s="4" t="s">
         <v>25</v>
       </c>
       <c r="M186" s="5" t="s">
-        <v>1228</v>
-      </c>
-    </row>
-    <row r="187" spans="1:13" ht="180" x14ac:dyDescent="0.25">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="187" spans="1:13" ht="225" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
         <v>186</v>
       </c>
@@ -11086,33 +11086,33 @@
         <v>7</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>1229</v>
+        <v>1214</v>
       </c>
       <c r="D187" s="6"/>
-      <c r="E187" s="6"/>
-      <c r="F187" s="6" t="s">
-        <v>1230</v>
-      </c>
+      <c r="E187" s="6" t="s">
+        <v>1333</v>
+      </c>
+      <c r="F187" s="6"/>
       <c r="G187" s="6" t="s">
-        <v>1231</v>
+        <v>1215</v>
       </c>
       <c r="H187" s="6" t="s">
-        <v>1232</v>
+        <v>1216</v>
       </c>
       <c r="I187" s="6" t="s">
-        <v>1233</v>
+        <v>1217</v>
       </c>
       <c r="J187" s="6" t="s">
-        <v>1234</v>
+        <v>1218</v>
       </c>
       <c r="K187" s="6" t="s">
-        <v>1235</v>
+        <v>1219</v>
       </c>
       <c r="L187" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M187" s="6" t="s">
-        <v>1236</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="188" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -11123,31 +11123,31 @@
         <v>7</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>1229</v>
+        <v>1214</v>
       </c>
       <c r="D188" s="5"/>
       <c r="E188" s="5"/>
       <c r="F188" s="5"/>
       <c r="G188" s="5" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="H188" s="5" t="s">
-        <v>1237</v>
+        <v>1221</v>
       </c>
       <c r="I188" s="5" t="s">
-        <v>1238</v>
+        <v>1222</v>
       </c>
       <c r="J188" s="5" t="s">
-        <v>1239</v>
+        <v>1223</v>
       </c>
       <c r="K188" s="5" t="s">
-        <v>1240</v>
+        <v>1224</v>
       </c>
       <c r="L188" s="4" t="s">
         <v>52</v>
       </c>
       <c r="M188" s="5" t="s">
-        <v>1241</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="189" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -11158,31 +11158,31 @@
         <v>7</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>1229</v>
+        <v>1214</v>
       </c>
       <c r="D189" s="6"/>
       <c r="E189" s="6"/>
       <c r="F189" s="6"/>
       <c r="G189" s="6" t="s">
-        <v>1242</v>
+        <v>1226</v>
       </c>
       <c r="H189" s="6" t="s">
-        <v>1243</v>
+        <v>1227</v>
       </c>
       <c r="I189" s="6" t="s">
-        <v>1244</v>
+        <v>1228</v>
       </c>
       <c r="J189" s="6" t="s">
-        <v>1245</v>
+        <v>1229</v>
       </c>
       <c r="K189" s="6" t="s">
-        <v>1246</v>
+        <v>1230</v>
       </c>
       <c r="L189" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M189" s="6" t="s">
-        <v>1247</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="190" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -11193,31 +11193,31 @@
         <v>7</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>1229</v>
+        <v>1214</v>
       </c>
       <c r="D190" s="5"/>
       <c r="E190" s="5"/>
       <c r="F190" s="5"/>
       <c r="G190" s="5" t="s">
-        <v>1248</v>
+        <v>1232</v>
       </c>
       <c r="H190" s="5" t="s">
-        <v>1249</v>
+        <v>1233</v>
       </c>
       <c r="I190" s="5" t="s">
-        <v>1250</v>
+        <v>1234</v>
       </c>
       <c r="J190" s="5" t="s">
-        <v>1251</v>
+        <v>1235</v>
       </c>
       <c r="K190" s="5" t="s">
-        <v>1252</v>
+        <v>1236</v>
       </c>
       <c r="L190" s="4" t="s">
         <v>39</v>
       </c>
       <c r="M190" s="5" t="s">
-        <v>1253</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="191" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -11228,34 +11228,34 @@
         <v>7</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>1229</v>
+        <v>1214</v>
       </c>
       <c r="D191" s="6"/>
       <c r="E191" s="6"/>
       <c r="F191" s="6"/>
       <c r="G191" s="6" t="s">
-        <v>1254</v>
+        <v>1238</v>
       </c>
       <c r="H191" s="6" t="s">
-        <v>1255</v>
+        <v>1239</v>
       </c>
       <c r="I191" s="6" t="s">
-        <v>1256</v>
+        <v>1240</v>
       </c>
       <c r="J191" s="6" t="s">
-        <v>1257</v>
+        <v>1241</v>
       </c>
       <c r="K191" s="6" t="s">
-        <v>1258</v>
+        <v>1242</v>
       </c>
       <c r="L191" s="2" t="s">
         <v>52</v>
       </c>
       <c r="M191" s="6" t="s">
-        <v>1259</v>
-      </c>
-    </row>
-    <row r="192" spans="1:13" ht="240" x14ac:dyDescent="0.25">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="192" spans="1:13" ht="225" x14ac:dyDescent="0.25">
       <c r="A192" s="4">
         <v>191</v>
       </c>
@@ -11263,33 +11263,33 @@
         <v>7</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>1260</v>
+        <v>1244</v>
       </c>
       <c r="D192" s="5"/>
-      <c r="E192" s="5"/>
-      <c r="F192" s="5" t="s">
-        <v>1261</v>
-      </c>
+      <c r="E192" s="5" t="s">
+        <v>1334</v>
+      </c>
+      <c r="F192" s="5"/>
       <c r="G192" s="5" t="s">
-        <v>1262</v>
+        <v>1245</v>
       </c>
       <c r="H192" s="5" t="s">
-        <v>1263</v>
+        <v>1246</v>
       </c>
       <c r="I192" s="5" t="s">
-        <v>1264</v>
+        <v>1247</v>
       </c>
       <c r="J192" s="5" t="s">
-        <v>1265</v>
+        <v>1248</v>
       </c>
       <c r="K192" s="5" t="s">
-        <v>1266</v>
+        <v>1249</v>
       </c>
       <c r="L192" s="4" t="s">
         <v>39</v>
       </c>
       <c r="M192" s="5" t="s">
-        <v>1267</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="193" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -11300,31 +11300,31 @@
         <v>7</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>1260</v>
+        <v>1244</v>
       </c>
       <c r="D193" s="6"/>
       <c r="E193" s="6"/>
       <c r="F193" s="6"/>
       <c r="G193" s="6" t="s">
-        <v>1268</v>
+        <v>1251</v>
       </c>
       <c r="H193" s="6" t="s">
-        <v>1269</v>
+        <v>1252</v>
       </c>
       <c r="I193" s="6" t="s">
-        <v>1270</v>
+        <v>1253</v>
       </c>
       <c r="J193" s="6" t="s">
-        <v>1271</v>
+        <v>1254</v>
       </c>
       <c r="K193" s="6" t="s">
-        <v>1272</v>
+        <v>1255</v>
       </c>
       <c r="L193" s="2" t="s">
         <v>39</v>
       </c>
       <c r="M193" s="6" t="s">
-        <v>1273</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="194" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -11335,31 +11335,31 @@
         <v>7</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>1260</v>
+        <v>1244</v>
       </c>
       <c r="D194" s="5"/>
       <c r="E194" s="5"/>
       <c r="F194" s="5"/>
       <c r="G194" s="5" t="s">
-        <v>1274</v>
+        <v>1257</v>
       </c>
       <c r="H194" s="5" t="s">
-        <v>1275</v>
+        <v>1258</v>
       </c>
       <c r="I194" s="5" t="s">
-        <v>1276</v>
+        <v>1259</v>
       </c>
       <c r="J194" s="5" t="s">
-        <v>1277</v>
+        <v>1260</v>
       </c>
       <c r="K194" s="5" t="s">
-        <v>1278</v>
+        <v>1261</v>
       </c>
       <c r="L194" s="4" t="s">
         <v>25</v>
       </c>
       <c r="M194" s="5" t="s">
-        <v>1279</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="195" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -11370,31 +11370,31 @@
         <v>7</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>1260</v>
+        <v>1244</v>
       </c>
       <c r="D195" s="6"/>
       <c r="E195" s="6"/>
       <c r="F195" s="6"/>
       <c r="G195" s="6" t="s">
-        <v>1280</v>
+        <v>1263</v>
       </c>
       <c r="H195" s="6" t="s">
-        <v>1281</v>
+        <v>1264</v>
       </c>
       <c r="I195" s="6" t="s">
-        <v>1282</v>
+        <v>1265</v>
       </c>
       <c r="J195" s="6" t="s">
-        <v>1283</v>
+        <v>1266</v>
       </c>
       <c r="K195" s="6" t="s">
-        <v>1284</v>
+        <v>1267</v>
       </c>
       <c r="L195" s="2" t="s">
         <v>52</v>
       </c>
       <c r="M195" s="6" t="s">
-        <v>1285</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="196" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -11405,34 +11405,34 @@
         <v>7</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>1260</v>
+        <v>1244</v>
       </c>
       <c r="D196" s="5"/>
       <c r="E196" s="5"/>
       <c r="F196" s="5"/>
       <c r="G196" s="5" t="s">
-        <v>1286</v>
+        <v>1269</v>
       </c>
       <c r="H196" s="5" t="s">
-        <v>1287</v>
+        <v>1270</v>
       </c>
       <c r="I196" s="5" t="s">
-        <v>1288</v>
+        <v>1271</v>
       </c>
       <c r="J196" s="5" t="s">
-        <v>1289</v>
+        <v>1272</v>
       </c>
       <c r="K196" s="5" t="s">
-        <v>1290</v>
+        <v>1273</v>
       </c>
       <c r="L196" s="4" t="s">
         <v>25</v>
       </c>
       <c r="M196" s="5" t="s">
-        <v>1291</v>
-      </c>
-    </row>
-    <row r="197" spans="1:13" ht="270" x14ac:dyDescent="0.25">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="197" spans="1:13" ht="225" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
         <v>196</v>
       </c>
@@ -11440,33 +11440,33 @@
         <v>7</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>1292</v>
+        <v>1275</v>
       </c>
       <c r="D197" s="6"/>
-      <c r="E197" s="6"/>
-      <c r="F197" s="6" t="s">
-        <v>1293</v>
-      </c>
+      <c r="E197" s="6" t="s">
+        <v>1335</v>
+      </c>
+      <c r="F197" s="6"/>
       <c r="G197" s="6" t="s">
-        <v>1294</v>
+        <v>1276</v>
       </c>
       <c r="H197" s="6" t="s">
-        <v>1295</v>
+        <v>1277</v>
       </c>
       <c r="I197" s="6" t="s">
-        <v>1296</v>
+        <v>1278</v>
       </c>
       <c r="J197" s="6" t="s">
-        <v>1297</v>
+        <v>1279</v>
       </c>
       <c r="K197" s="6" t="s">
-        <v>1298</v>
+        <v>1280</v>
       </c>
       <c r="L197" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M197" s="6" t="s">
-        <v>1299</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="198" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -11477,31 +11477,31 @@
         <v>7</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>1292</v>
+        <v>1275</v>
       </c>
       <c r="D198" s="5"/>
       <c r="E198" s="5"/>
       <c r="F198" s="5"/>
       <c r="G198" s="5" t="s">
-        <v>1300</v>
+        <v>1282</v>
       </c>
       <c r="H198" s="5" t="s">
-        <v>1301</v>
+        <v>1283</v>
       </c>
       <c r="I198" s="5" t="s">
-        <v>1302</v>
+        <v>1284</v>
       </c>
       <c r="J198" s="5" t="s">
-        <v>1303</v>
+        <v>1285</v>
       </c>
       <c r="K198" s="5" t="s">
-        <v>1304</v>
+        <v>1286</v>
       </c>
       <c r="L198" s="4" t="s">
         <v>52</v>
       </c>
       <c r="M198" s="5" t="s">
-        <v>1305</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="199" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -11512,31 +11512,31 @@
         <v>7</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>1292</v>
+        <v>1275</v>
       </c>
       <c r="D199" s="6"/>
       <c r="E199" s="6"/>
       <c r="F199" s="6"/>
       <c r="G199" s="6" t="s">
-        <v>1306</v>
+        <v>1288</v>
       </c>
       <c r="H199" s="6" t="s">
-        <v>1307</v>
+        <v>1289</v>
       </c>
       <c r="I199" s="6" t="s">
-        <v>1308</v>
+        <v>1290</v>
       </c>
       <c r="J199" s="6" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
       <c r="K199" s="6" t="s">
-        <v>1310</v>
+        <v>1292</v>
       </c>
       <c r="L199" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M199" s="6" t="s">
-        <v>1311</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="200" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -11547,31 +11547,31 @@
         <v>7</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>1292</v>
+        <v>1275</v>
       </c>
       <c r="D200" s="5"/>
       <c r="E200" s="5"/>
       <c r="F200" s="5"/>
       <c r="G200" s="5" t="s">
-        <v>1312</v>
+        <v>1294</v>
       </c>
       <c r="H200" s="5" t="s">
-        <v>1313</v>
+        <v>1295</v>
       </c>
       <c r="I200" s="5" t="s">
-        <v>1314</v>
+        <v>1296</v>
       </c>
       <c r="J200" s="5" t="s">
-        <v>1315</v>
+        <v>1297</v>
       </c>
       <c r="K200" s="5" t="s">
-        <v>1316</v>
+        <v>1298</v>
       </c>
       <c r="L200" s="4" t="s">
         <v>39</v>
       </c>
       <c r="M200" s="5" t="s">
-        <v>1317</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="201" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -11582,31 +11582,31 @@
         <v>7</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>1292</v>
+        <v>1275</v>
       </c>
       <c r="D201" s="6"/>
       <c r="E201" s="6"/>
       <c r="F201" s="6"/>
       <c r="G201" s="6" t="s">
-        <v>1318</v>
+        <v>1300</v>
       </c>
       <c r="H201" s="6" t="s">
-        <v>1319</v>
+        <v>1301</v>
       </c>
       <c r="I201" s="6" t="s">
-        <v>1320</v>
+        <v>1302</v>
       </c>
       <c r="J201" s="6" t="s">
-        <v>1321</v>
+        <v>1303</v>
       </c>
       <c r="K201" s="6" t="s">
-        <v>1322</v>
+        <v>1304</v>
       </c>
       <c r="L201" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M201" s="6" t="s">
-        <v>1323</v>
+        <v>1305</v>
       </c>
     </row>
   </sheetData>
@@ -11622,6 +11622,19 @@
     <hyperlink ref="E97" r:id="rId9"/>
     <hyperlink ref="E100" r:id="rId10"/>
     <hyperlink ref="E132" r:id="rId11"/>
+    <hyperlink ref="E136" r:id="rId12"/>
+    <hyperlink ref="E140" r:id="rId13"/>
+    <hyperlink ref="E144" r:id="rId14"/>
+    <hyperlink ref="E148" r:id="rId15"/>
+    <hyperlink ref="E150" r:id="rId16"/>
+    <hyperlink ref="E152" r:id="rId17"/>
+    <hyperlink ref="E155" r:id="rId18"/>
+    <hyperlink ref="E157" r:id="rId19"/>
+    <hyperlink ref="E159" r:id="rId20"/>
+    <hyperlink ref="E163" r:id="rId21"/>
+    <hyperlink ref="E167" r:id="rId22"/>
+    <hyperlink ref="E170" r:id="rId23"/>
+    <hyperlink ref="E173" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ETS2023_Test1_Final_Architecture.xlsx
+++ b/ETS2023_Test1_Final_Architecture.xlsx
@@ -4030,7 +4030,7 @@
     <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_196(1).png | https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_196(2).png | https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_196(3).png</t>
   </si>
   <si>
-    <t>https://github.com/bangvang1105-tech/Audio-Test-1-ETS-2023/raw/refs/heads/main/Test%201%20ETS%202023.mp3</t>
+    <t>https://drive.google.com/file/d/14yGl8HQLGWVQRJ9wKb3tllrgH0prTzdC/view?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -4502,9 +4502,6 @@
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/ETS2023_Test1_Final_Architecture.xlsx
+++ b/ETS2023_Test1_Final_Architecture.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28035" windowHeight="11730"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28035" windowHeight="11730" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Test_Info" sheetId="1" r:id="rId1"/>
@@ -3940,97 +3940,97 @@
     <t>Giải thích: Maria viết trong email thứ 2 rằng: Ông Eklund thích tất cả bài viết của bà, và tất nhiên là CẢ bài báo/review gần đây về cuốn tự truyện của ông ấy ('your recent article about The Theatre Lights Dimmed!') -&gt; Ông ấy hài lòng với bài review của Joshi.</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/main/p1_01.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p1_02.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p1_03.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p1_04.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p1_05.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p1_06.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p3_63.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p3_66.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p3_69.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p4_96.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p4_99.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p6_131.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p6_135.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p6_139.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p6_143.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_147.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_149.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_151.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_154.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_156.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_158.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_162.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_166.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_169.png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_172.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_176(1).png | https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_176(2).png </t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_181(1).png | https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_181(2).png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_186(1).png | https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_186(2).png | https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_186(3).png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_191(1).png | https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_191(2).png | https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_191(3).png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_196(1).png | https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_196(2).png | https://raw.githubusercontent.com/bangvang1105-tech/Image-Test-1-ETS-2023/refs/heads/main/p7_196(3).png</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/14yGl8HQLGWVQRJ9wKb3tllrgH0prTzdC/view?usp=sharing</t>
+    <t>https://res.cloudinary.com/dhmq07vzk/video/upload/v1782455168/Test_1_ETS_2023_vfth4v.mp3</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458761/p1_01_TEST_1_2023_ucgyk7.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458762/p1_02_1_TEST_1_2023_dolohs.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458762/p1_03_TEST_1_2023_zrrqff.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458763/p1_04_TEST_1_2023_yo8ngp.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458762/p1_05_TEST_1_2023_qwnvqc.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458764/p1_06_TEST_1_2023_pcjhdq.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458763/p3_63_TEST_1_2023_ceizvb.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458764/p3_66_TEST_1_2023_am2aqa.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458764/p3_69_TEST_1_2023_dizo4n.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458765/p4_96_TEST_1_2023_qf2sov.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458766/p4_99_TEST_1_2023_okannw.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458766/p6_131_TEST_1_2023_cexxzd.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458767/p6_135_TEST_1_2023_mrrxxf.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458767/p6_139_TEST_1_2023_j6kmzj.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458768/p6_143_TEST_1_2023_z8o89q.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458769/p7_147_TEST_1_2023_lmkhip.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458769/p7_149_TEST_1_2023_s8vtob.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458770/p7_151_TEST_1_2023_nftbes.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458771/p7_154_TEST_1_2023_cjxafh.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458771/p7_156_TEST_1_2023_b3grmc.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458772/p7_158_TEST_1_2023_zpi9f2.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458772/p7_162_TEST_1_2023_dawwpa.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458773/p7_166_TEST_1_2023_q3ybno.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458774/p7_169_TEST_1_2023_txcpwm.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458774/p7_172_TEST_1_2023_y4z6nx.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458775/p7_176_1_TEST_1_2023_pnyl3i.png | https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458775/p7_176_2_TEST_1_2023_qi068t.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458776/p7_181_1_TEST_1_2023_rsoqhe.png | https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458777/p7_181_2_TEST_1_2023_gth3hp.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458777/p7_186_1_TEST_1_2023_eibrkr.png | https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458778/p7_186_2_TEST_1_2023_whucss.png | https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458778/p7_186_3_TEST_1_2023_vystwu.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458779/p7_191_1_TEST_1_2023_sxe8v9.png | https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458780/p7_191_2_TEST_1_2023_onmrvc.png | https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458780/p7_191_3_TEST_1_2023_kc7ifg.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458781/p7_196_1_TEST_1_2023_cmfmak.png | https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458782/p7_196_2_TEST_1_2023_kjianl.png | https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458782/p7_196_3_TEST_1_2023_vrlvt5.png</t>
   </si>
 </sst>
 </file>
@@ -4146,15 +4146,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4491,8 +4489,8 @@
       <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>1336</v>
+      <c r="C2" s="9" t="s">
+        <v>1306</v>
       </c>
       <c r="D2" s="2">
         <v>120</v>
@@ -4502,6 +4500,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4573,8 +4574,8 @@
         <v>20</v>
       </c>
       <c r="D2" s="5"/>
-      <c r="E2" s="8" t="s">
-        <v>1306</v>
+      <c r="E2" s="7" t="s">
+        <v>1307</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
@@ -4597,7 +4598,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -4608,8 +4609,8 @@
         <v>27</v>
       </c>
       <c r="D3" s="6"/>
-      <c r="E3" s="9" t="s">
-        <v>1307</v>
+      <c r="E3" s="8" t="s">
+        <v>1308</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -4632,7 +4633,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -4643,8 +4644,8 @@
         <v>34</v>
       </c>
       <c r="D4" s="5"/>
-      <c r="E4" s="8" t="s">
-        <v>1308</v>
+      <c r="E4" s="7" t="s">
+        <v>1309</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
@@ -4667,7 +4668,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -4678,8 +4679,8 @@
         <v>41</v>
       </c>
       <c r="D5" s="6"/>
-      <c r="E5" s="9" t="s">
-        <v>1309</v>
+      <c r="E5" s="8" t="s">
+        <v>1310</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
@@ -4702,7 +4703,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -4713,8 +4714,8 @@
         <v>47</v>
       </c>
       <c r="D6" s="5"/>
-      <c r="E6" s="8" t="s">
-        <v>1310</v>
+      <c r="E6" s="7" t="s">
+        <v>1311</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -4737,7 +4738,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -4748,8 +4749,8 @@
         <v>54</v>
       </c>
       <c r="D7" s="6"/>
-      <c r="E7" s="9" t="s">
-        <v>1311</v>
+      <c r="E7" s="8" t="s">
+        <v>1312</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
@@ -6678,7 +6679,7 @@
         <v>408</v>
       </c>
       <c r="D63" s="6"/>
-      <c r="E63" s="9"/>
+      <c r="E63" s="8"/>
       <c r="F63" s="6" t="s">
         <v>409</v>
       </c>
@@ -6704,7 +6705,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
         <v>63</v>
       </c>
@@ -6715,8 +6716,8 @@
         <v>408</v>
       </c>
       <c r="D64" s="5"/>
-      <c r="E64" s="8" t="s">
-        <v>1312</v>
+      <c r="E64" s="7" t="s">
+        <v>1313</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="5" t="s">
@@ -6813,7 +6814,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -6824,8 +6825,8 @@
         <v>427</v>
       </c>
       <c r="D67" s="6"/>
-      <c r="E67" s="9" t="s">
-        <v>1313</v>
+      <c r="E67" s="8" t="s">
+        <v>1314</v>
       </c>
       <c r="F67" s="6"/>
       <c r="G67" s="6" t="s">
@@ -6922,7 +6923,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
         <v>69</v>
       </c>
@@ -6933,8 +6934,8 @@
         <v>447</v>
       </c>
       <c r="D70" s="5"/>
-      <c r="E70" s="8" t="s">
-        <v>1314</v>
+      <c r="E70" s="7" t="s">
+        <v>1315</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="5" t="s">
@@ -7887,7 +7888,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="97" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>96</v>
       </c>
@@ -7898,8 +7899,8 @@
         <v>627</v>
       </c>
       <c r="D97" s="6"/>
-      <c r="E97" s="9" t="s">
-        <v>1315</v>
+      <c r="E97" s="8" t="s">
+        <v>1316</v>
       </c>
       <c r="F97" s="6"/>
       <c r="G97" s="6" t="s">
@@ -7996,7 +7997,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="100" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A100" s="4">
         <v>99</v>
       </c>
@@ -8007,8 +8008,8 @@
         <v>647</v>
       </c>
       <c r="D100" s="5"/>
-      <c r="E100" s="8" t="s">
-        <v>1316</v>
+      <c r="E100" s="7" t="s">
+        <v>1317</v>
       </c>
       <c r="F100" s="5"/>
       <c r="G100" s="5" t="s">
@@ -9129,8 +9130,8 @@
         <v>876</v>
       </c>
       <c r="D132" s="5"/>
-      <c r="E132" s="8" t="s">
-        <v>1317</v>
+      <c r="E132" s="7" t="s">
+        <v>1318</v>
       </c>
       <c r="F132" s="5"/>
       <c r="G132" s="5" t="s">
@@ -9260,7 +9261,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="136" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A136" s="4">
         <v>135</v>
       </c>
@@ -9271,8 +9272,8 @@
         <v>901</v>
       </c>
       <c r="D136" s="5"/>
-      <c r="E136" s="8" t="s">
-        <v>1318</v>
+      <c r="E136" s="7" t="s">
+        <v>1319</v>
       </c>
       <c r="F136" s="5"/>
       <c r="G136" s="5" t="s">
@@ -9402,7 +9403,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="140" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A140" s="4">
         <v>139</v>
       </c>
@@ -9413,8 +9414,8 @@
         <v>925</v>
       </c>
       <c r="D140" s="5"/>
-      <c r="E140" s="8" t="s">
-        <v>1319</v>
+      <c r="E140" s="7" t="s">
+        <v>1320</v>
       </c>
       <c r="F140" s="5"/>
       <c r="G140" s="5" t="s">
@@ -9544,7 +9545,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="144" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A144" s="4">
         <v>143</v>
       </c>
@@ -9555,8 +9556,8 @@
         <v>949</v>
       </c>
       <c r="D144" s="5"/>
-      <c r="E144" s="8" t="s">
-        <v>1320</v>
+      <c r="E144" s="7" t="s">
+        <v>1321</v>
       </c>
       <c r="F144" s="5"/>
       <c r="G144" s="5" t="s">
@@ -9686,7 +9687,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="148" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A148" s="4">
         <v>147</v>
       </c>
@@ -9697,8 +9698,8 @@
         <v>973</v>
       </c>
       <c r="D148" s="5"/>
-      <c r="E148" s="8" t="s">
-        <v>1321</v>
+      <c r="E148" s="7" t="s">
+        <v>1322</v>
       </c>
       <c r="F148" s="5"/>
       <c r="G148" s="5" t="s">
@@ -9758,7 +9759,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="150" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A150" s="4">
         <v>149</v>
       </c>
@@ -9769,8 +9770,8 @@
         <v>986</v>
       </c>
       <c r="D150" s="5"/>
-      <c r="E150" s="8" t="s">
-        <v>1322</v>
+      <c r="E150" s="7" t="s">
+        <v>1323</v>
       </c>
       <c r="F150" s="5"/>
       <c r="G150" s="5" t="s">
@@ -9830,7 +9831,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="152" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A152" s="4">
         <v>151</v>
       </c>
@@ -9841,8 +9842,8 @@
         <v>999</v>
       </c>
       <c r="D152" s="5"/>
-      <c r="E152" s="8" t="s">
-        <v>1323</v>
+      <c r="E152" s="7" t="s">
+        <v>1324</v>
       </c>
       <c r="F152" s="5"/>
       <c r="G152" s="5" t="s">
@@ -9937,7 +9938,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="155" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
         <v>154</v>
       </c>
@@ -9948,8 +9949,8 @@
         <v>1017</v>
       </c>
       <c r="D155" s="6"/>
-      <c r="E155" s="9" t="s">
-        <v>1324</v>
+      <c r="E155" s="8" t="s">
+        <v>1325</v>
       </c>
       <c r="F155" s="6"/>
       <c r="G155" s="6" t="s">
@@ -10009,7 +10010,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="157" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <v>156</v>
       </c>
@@ -10020,8 +10021,8 @@
         <v>1030</v>
       </c>
       <c r="D157" s="6"/>
-      <c r="E157" s="9" t="s">
-        <v>1325</v>
+      <c r="E157" s="8" t="s">
+        <v>1326</v>
       </c>
       <c r="F157" s="6"/>
       <c r="G157" s="6" t="s">
@@ -10081,7 +10082,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="159" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
         <v>158</v>
       </c>
@@ -10092,8 +10093,8 @@
         <v>1043</v>
       </c>
       <c r="D159" s="6"/>
-      <c r="E159" s="9" t="s">
-        <v>1326</v>
+      <c r="E159" s="8" t="s">
+        <v>1327</v>
       </c>
       <c r="F159" s="6"/>
       <c r="G159" s="6" t="s">
@@ -10223,7 +10224,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="163" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
         <v>162</v>
       </c>
@@ -10234,8 +10235,8 @@
         <v>1068</v>
       </c>
       <c r="D163" s="6"/>
-      <c r="E163" s="9" t="s">
-        <v>1327</v>
+      <c r="E163" s="8" t="s">
+        <v>1328</v>
       </c>
       <c r="F163" s="6"/>
       <c r="G163" s="6" t="s">
@@ -10365,7 +10366,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="167" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
         <v>166</v>
       </c>
@@ -10376,8 +10377,8 @@
         <v>1093</v>
       </c>
       <c r="D167" s="6"/>
-      <c r="E167" s="9" t="s">
-        <v>1328</v>
+      <c r="E167" s="8" t="s">
+        <v>1329</v>
       </c>
       <c r="F167" s="6"/>
       <c r="G167" s="6" t="s">
@@ -10472,7 +10473,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="170" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A170" s="4">
         <v>169</v>
       </c>
@@ -10483,8 +10484,8 @@
         <v>1112</v>
       </c>
       <c r="D170" s="5"/>
-      <c r="E170" s="8" t="s">
-        <v>1329</v>
+      <c r="E170" s="7" t="s">
+        <v>1330</v>
       </c>
       <c r="F170" s="5"/>
       <c r="G170" s="5" t="s">
@@ -10579,7 +10580,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="173" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
         <v>172</v>
       </c>
@@ -10590,8 +10591,8 @@
         <v>1131</v>
       </c>
       <c r="D173" s="6"/>
-      <c r="E173" s="9" t="s">
-        <v>1330</v>
+      <c r="E173" s="8" t="s">
+        <v>1331</v>
       </c>
       <c r="F173" s="6"/>
       <c r="G173" s="6" t="s">
@@ -10721,7 +10722,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="177" spans="1:13" ht="150" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
         <v>176</v>
       </c>
@@ -10732,8 +10733,8 @@
         <v>1152</v>
       </c>
       <c r="D177" s="6"/>
-      <c r="E177" s="6" t="s">
-        <v>1331</v>
+      <c r="E177" s="8" t="s">
+        <v>1332</v>
       </c>
       <c r="F177" s="6"/>
       <c r="G177" s="6" t="s">
@@ -10909,8 +10910,8 @@
         <v>1183</v>
       </c>
       <c r="D182" s="5"/>
-      <c r="E182" s="5" t="s">
-        <v>1332</v>
+      <c r="E182" s="7" t="s">
+        <v>1333</v>
       </c>
       <c r="F182" s="5"/>
       <c r="G182" s="5" t="s">
@@ -11087,7 +11088,7 @@
       </c>
       <c r="D187" s="6"/>
       <c r="E187" s="6" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="F187" s="6"/>
       <c r="G187" s="6" t="s">
@@ -11252,7 +11253,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="192" spans="1:13" ht="225" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:13" ht="210" x14ac:dyDescent="0.25">
       <c r="A192" s="4">
         <v>191</v>
       </c>
@@ -11264,7 +11265,7 @@
       </c>
       <c r="D192" s="5"/>
       <c r="E192" s="5" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="F192" s="5"/>
       <c r="G192" s="5" t="s">
@@ -11429,7 +11430,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="197" spans="1:13" ht="225" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:13" ht="210" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
         <v>196</v>
       </c>
@@ -11440,8 +11441,8 @@
         <v>1275</v>
       </c>
       <c r="D197" s="6"/>
-      <c r="E197" s="6" t="s">
-        <v>1335</v>
+      <c r="E197" s="8" t="s">
+        <v>1336</v>
       </c>
       <c r="F197" s="6"/>
       <c r="G197" s="6" t="s">
@@ -11616,22 +11617,26 @@
     <hyperlink ref="E7" r:id="rId6"/>
     <hyperlink ref="E64" r:id="rId7"/>
     <hyperlink ref="E67" r:id="rId8"/>
-    <hyperlink ref="E97" r:id="rId9"/>
-    <hyperlink ref="E100" r:id="rId10"/>
-    <hyperlink ref="E132" r:id="rId11"/>
-    <hyperlink ref="E136" r:id="rId12"/>
-    <hyperlink ref="E140" r:id="rId13"/>
-    <hyperlink ref="E144" r:id="rId14"/>
-    <hyperlink ref="E148" r:id="rId15"/>
-    <hyperlink ref="E150" r:id="rId16"/>
-    <hyperlink ref="E152" r:id="rId17"/>
-    <hyperlink ref="E155" r:id="rId18"/>
-    <hyperlink ref="E157" r:id="rId19"/>
-    <hyperlink ref="E159" r:id="rId20"/>
-    <hyperlink ref="E163" r:id="rId21"/>
-    <hyperlink ref="E167" r:id="rId22"/>
-    <hyperlink ref="E170" r:id="rId23"/>
-    <hyperlink ref="E173" r:id="rId24"/>
+    <hyperlink ref="E70" r:id="rId9"/>
+    <hyperlink ref="E97" r:id="rId10"/>
+    <hyperlink ref="E100" r:id="rId11"/>
+    <hyperlink ref="E132" r:id="rId12"/>
+    <hyperlink ref="E136" r:id="rId13"/>
+    <hyperlink ref="E140" r:id="rId14"/>
+    <hyperlink ref="E144" r:id="rId15"/>
+    <hyperlink ref="E148" r:id="rId16"/>
+    <hyperlink ref="E150" r:id="rId17"/>
+    <hyperlink ref="E152" r:id="rId18"/>
+    <hyperlink ref="E155" r:id="rId19"/>
+    <hyperlink ref="E157" r:id="rId20"/>
+    <hyperlink ref="E159" r:id="rId21"/>
+    <hyperlink ref="E163" r:id="rId22"/>
+    <hyperlink ref="E167" r:id="rId23"/>
+    <hyperlink ref="E170" r:id="rId24"/>
+    <hyperlink ref="E173" r:id="rId25"/>
+    <hyperlink ref="E177" r:id="rId26" display="https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458775/p7_176_1_TEST_1_2023_pnyl3i.png "/>
+    <hyperlink ref="E182" r:id="rId27" display="https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458776/p7_181_1_TEST_1_2023_rsoqhe.png"/>
+    <hyperlink ref="E197" r:id="rId28" display="https://res.cloudinary.com/dhmq07vzk/image/upload/v1782458781/p7_196_1_TEST_1_2023_cmfmak.png "/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
